--- a/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ce_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ce_calibrated.xlsx
@@ -11,14 +11,13 @@
     <sheet name="strategy_id-6003" sheetId="2" r:id="rId2"/>
     <sheet name="strategy_id-6004" sheetId="3" r:id="rId3"/>
     <sheet name="strategy_id-6005" sheetId="4" r:id="rId4"/>
-    <sheet name="strategy_id-6006" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="283">
   <si>
     <t>subsector</t>
   </si>
@@ -50725,7239 +50724,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BC47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:55">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:55">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2">
-        <v>58</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>0.002165315</v>
-      </c>
-      <c r="K2">
-        <v>0.002165315</v>
-      </c>
-      <c r="L2">
-        <v>0.002165315</v>
-      </c>
-      <c r="M2">
-        <v>0.002165315</v>
-      </c>
-      <c r="N2">
-        <v>0.002165315</v>
-      </c>
-      <c r="O2">
-        <v>0.002165315</v>
-      </c>
-      <c r="P2">
-        <v>0.002165315</v>
-      </c>
-      <c r="Q2">
-        <v>0.002165315</v>
-      </c>
-      <c r="R2">
-        <v>0.002165315</v>
-      </c>
-      <c r="S2">
-        <v>0.002165315</v>
-      </c>
-      <c r="T2">
-        <v>0.002165315</v>
-      </c>
-      <c r="U2">
-        <v>0.002103448857142857</v>
-      </c>
-      <c r="V2">
-        <v>0.002041582714285714</v>
-      </c>
-      <c r="W2">
-        <v>0.001979716571428571</v>
-      </c>
-      <c r="X2">
-        <v>0.001917850428571429</v>
-      </c>
-      <c r="Y2">
-        <v>0.001855984285714286</v>
-      </c>
-      <c r="Z2">
-        <v>0.001794118142857143</v>
-      </c>
-      <c r="AA2">
-        <v>0.001732252</v>
-      </c>
-      <c r="AB2">
-        <v>0.001670385857142857</v>
-      </c>
-      <c r="AC2">
-        <v>0.001608519714285714</v>
-      </c>
-      <c r="AD2">
-        <v>0.001546653571428572</v>
-      </c>
-      <c r="AE2">
-        <v>0.001484787428571429</v>
-      </c>
-      <c r="AF2">
-        <v>0.001422921285714286</v>
-      </c>
-      <c r="AG2">
-        <v>0.001361055142857143</v>
-      </c>
-      <c r="AH2">
-        <v>0.001299189</v>
-      </c>
-      <c r="AI2">
-        <v>0.001237322857142857</v>
-      </c>
-      <c r="AJ2">
-        <v>0.001175456714285714</v>
-      </c>
-      <c r="AK2">
-        <v>0.001113590571428571</v>
-      </c>
-      <c r="AL2">
-        <v>0.001051724428571429</v>
-      </c>
-      <c r="AM2">
-        <v>0.0009898582857142859</v>
-      </c>
-      <c r="AN2">
-        <v>0.000927992142857143</v>
-      </c>
-      <c r="AO2">
-        <v>0.000866126</v>
-      </c>
-      <c r="AP2">
-        <v>0.0008042598571428572</v>
-      </c>
-      <c r="AQ2">
-        <v>0.0007423937142857143</v>
-      </c>
-      <c r="AR2">
-        <v>0.0006805275714285715</v>
-      </c>
-      <c r="AS2">
-        <v>0.0006186614285714286</v>
-      </c>
-      <c r="AT2">
-        <v>0.0005567952857142857</v>
-      </c>
-      <c r="AU2">
-        <v>0.0004949291428571429</v>
-      </c>
-      <c r="AV2">
-        <v>0.0004330629999999999</v>
-      </c>
-      <c r="AW2">
-        <v>0.000371196857142857</v>
-      </c>
-      <c r="AX2">
-        <v>0.0003093307142857144</v>
-      </c>
-      <c r="AY2">
-        <v>0.0002474645714285715</v>
-      </c>
-      <c r="AZ2">
-        <v>0.0001855984285714287</v>
-      </c>
-      <c r="BA2">
-        <v>0.0001237322857142858</v>
-      </c>
-      <c r="BB2">
-        <v>6.186614285714288E-05</v>
-      </c>
-      <c r="BC2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:55">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3">
-        <v>58</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>0.002165315</v>
-      </c>
-      <c r="K3">
-        <v>0.002165315</v>
-      </c>
-      <c r="L3">
-        <v>0.002165315</v>
-      </c>
-      <c r="M3">
-        <v>0.002165315</v>
-      </c>
-      <c r="N3">
-        <v>0.002165315</v>
-      </c>
-      <c r="O3">
-        <v>0.002165315</v>
-      </c>
-      <c r="P3">
-        <v>0.002165315</v>
-      </c>
-      <c r="Q3">
-        <v>0.002165315</v>
-      </c>
-      <c r="R3">
-        <v>0.002165315</v>
-      </c>
-      <c r="S3">
-        <v>0.002165315</v>
-      </c>
-      <c r="T3">
-        <v>0.002165315</v>
-      </c>
-      <c r="U3">
-        <v>0.002103448857142857</v>
-      </c>
-      <c r="V3">
-        <v>0.002041582714285714</v>
-      </c>
-      <c r="W3">
-        <v>0.001979716571428571</v>
-      </c>
-      <c r="X3">
-        <v>0.001917850428571429</v>
-      </c>
-      <c r="Y3">
-        <v>0.001855984285714286</v>
-      </c>
-      <c r="Z3">
-        <v>0.001794118142857143</v>
-      </c>
-      <c r="AA3">
-        <v>0.001732252</v>
-      </c>
-      <c r="AB3">
-        <v>0.001670385857142857</v>
-      </c>
-      <c r="AC3">
-        <v>0.001608519714285714</v>
-      </c>
-      <c r="AD3">
-        <v>0.001546653571428572</v>
-      </c>
-      <c r="AE3">
-        <v>0.001484787428571429</v>
-      </c>
-      <c r="AF3">
-        <v>0.001422921285714286</v>
-      </c>
-      <c r="AG3">
-        <v>0.001361055142857143</v>
-      </c>
-      <c r="AH3">
-        <v>0.001299189</v>
-      </c>
-      <c r="AI3">
-        <v>0.001237322857142857</v>
-      </c>
-      <c r="AJ3">
-        <v>0.001175456714285714</v>
-      </c>
-      <c r="AK3">
-        <v>0.001113590571428571</v>
-      </c>
-      <c r="AL3">
-        <v>0.001051724428571429</v>
-      </c>
-      <c r="AM3">
-        <v>0.0009898582857142859</v>
-      </c>
-      <c r="AN3">
-        <v>0.000927992142857143</v>
-      </c>
-      <c r="AO3">
-        <v>0.000866126</v>
-      </c>
-      <c r="AP3">
-        <v>0.0008042598571428572</v>
-      </c>
-      <c r="AQ3">
-        <v>0.0007423937142857143</v>
-      </c>
-      <c r="AR3">
-        <v>0.0006805275714285715</v>
-      </c>
-      <c r="AS3">
-        <v>0.0006186614285714286</v>
-      </c>
-      <c r="AT3">
-        <v>0.0005567952857142857</v>
-      </c>
-      <c r="AU3">
-        <v>0.0004949291428571429</v>
-      </c>
-      <c r="AV3">
-        <v>0.0004330629999999999</v>
-      </c>
-      <c r="AW3">
-        <v>0.000371196857142857</v>
-      </c>
-      <c r="AX3">
-        <v>0.0003093307142857144</v>
-      </c>
-      <c r="AY3">
-        <v>0.0002474645714285715</v>
-      </c>
-      <c r="AZ3">
-        <v>0.0001855984285714287</v>
-      </c>
-      <c r="BA3">
-        <v>0.0001237322857142858</v>
-      </c>
-      <c r="BB3">
-        <v>6.186614285714288E-05</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:55">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4">
-        <v>58</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>0.495660399</v>
-      </c>
-      <c r="K4">
-        <v>0.495660399</v>
-      </c>
-      <c r="L4">
-        <v>0.495660399</v>
-      </c>
-      <c r="M4">
-        <v>0.495660399</v>
-      </c>
-      <c r="N4">
-        <v>0.495660399</v>
-      </c>
-      <c r="O4">
-        <v>0.495660399</v>
-      </c>
-      <c r="P4">
-        <v>0.495660399</v>
-      </c>
-      <c r="Q4">
-        <v>0.495660399</v>
-      </c>
-      <c r="R4">
-        <v>0.495660399</v>
-      </c>
-      <c r="S4">
-        <v>0.495660399</v>
-      </c>
-      <c r="T4">
-        <v>0.495660399</v>
-      </c>
-      <c r="U4">
-        <v>0.5100701018571429</v>
-      </c>
-      <c r="V4">
-        <v>0.5244798047142857</v>
-      </c>
-      <c r="W4">
-        <v>0.5388895075714285</v>
-      </c>
-      <c r="X4">
-        <v>0.5532992104285713</v>
-      </c>
-      <c r="Y4">
-        <v>0.5677089132857143</v>
-      </c>
-      <c r="Z4">
-        <v>0.5821186161428571</v>
-      </c>
-      <c r="AA4">
-        <v>0.5965283189999999</v>
-      </c>
-      <c r="AB4">
-        <v>0.6109380218571429</v>
-      </c>
-      <c r="AC4">
-        <v>0.6253477247142857</v>
-      </c>
-      <c r="AD4">
-        <v>0.6397574275714286</v>
-      </c>
-      <c r="AE4">
-        <v>0.6541671304285713</v>
-      </c>
-      <c r="AF4">
-        <v>0.6685768332857143</v>
-      </c>
-      <c r="AG4">
-        <v>0.6829865361428571</v>
-      </c>
-      <c r="AH4">
-        <v>0.6973962389999999</v>
-      </c>
-      <c r="AI4">
-        <v>0.7118059418571427</v>
-      </c>
-      <c r="AJ4">
-        <v>0.7262156447142857</v>
-      </c>
-      <c r="AK4">
-        <v>0.7406253475714285</v>
-      </c>
-      <c r="AL4">
-        <v>0.7550350504285714</v>
-      </c>
-      <c r="AM4">
-        <v>0.7694447532857142</v>
-      </c>
-      <c r="AN4">
-        <v>0.7838544561428571</v>
-      </c>
-      <c r="AO4">
-        <v>0.7982641589999999</v>
-      </c>
-      <c r="AP4">
-        <v>0.8126738618571427</v>
-      </c>
-      <c r="AQ4">
-        <v>0.8270835647142857</v>
-      </c>
-      <c r="AR4">
-        <v>0.8414932675714285</v>
-      </c>
-      <c r="AS4">
-        <v>0.8559029704285714</v>
-      </c>
-      <c r="AT4">
-        <v>0.8703126732857143</v>
-      </c>
-      <c r="AU4">
-        <v>0.8847223761428571</v>
-      </c>
-      <c r="AV4">
-        <v>0.8991320789999999</v>
-      </c>
-      <c r="AW4">
-        <v>0.9135417818571427</v>
-      </c>
-      <c r="AX4">
-        <v>0.9279514847142857</v>
-      </c>
-      <c r="AY4">
-        <v>0.9423611875714284</v>
-      </c>
-      <c r="AZ4">
-        <v>0.9567708904285713</v>
-      </c>
-      <c r="BA4">
-        <v>0.9711805932857142</v>
-      </c>
-      <c r="BB4">
-        <v>0.9855902961428571</v>
-      </c>
-      <c r="BC4">
-        <v>0.9999999989999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:55">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5">
-        <v>58</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>0.122491483</v>
-      </c>
-      <c r="K5">
-        <v>0.122491483</v>
-      </c>
-      <c r="L5">
-        <v>0.122491483</v>
-      </c>
-      <c r="M5">
-        <v>0.122491483</v>
-      </c>
-      <c r="N5">
-        <v>0.122491483</v>
-      </c>
-      <c r="O5">
-        <v>0.122491483</v>
-      </c>
-      <c r="P5">
-        <v>0.122491483</v>
-      </c>
-      <c r="Q5">
-        <v>0.122491483</v>
-      </c>
-      <c r="R5">
-        <v>0.122491483</v>
-      </c>
-      <c r="S5">
-        <v>0.122491483</v>
-      </c>
-      <c r="T5">
-        <v>0.122491483</v>
-      </c>
-      <c r="U5">
-        <v>0.1189917263428571</v>
-      </c>
-      <c r="V5">
-        <v>0.1154919696857143</v>
-      </c>
-      <c r="W5">
-        <v>0.1119922130285714</v>
-      </c>
-      <c r="X5">
-        <v>0.1084924563714286</v>
-      </c>
-      <c r="Y5">
-        <v>0.1049926997142857</v>
-      </c>
-      <c r="Z5">
-        <v>0.1014929430571428</v>
-      </c>
-      <c r="AA5">
-        <v>0.0979931864</v>
-      </c>
-      <c r="AB5">
-        <v>0.09449342974285714</v>
-      </c>
-      <c r="AC5">
-        <v>0.09099367308571429</v>
-      </c>
-      <c r="AD5">
-        <v>0.08749391642857143</v>
-      </c>
-      <c r="AE5">
-        <v>0.08399415977142857</v>
-      </c>
-      <c r="AF5">
-        <v>0.08049440311428571</v>
-      </c>
-      <c r="AG5">
-        <v>0.07699464645714285</v>
-      </c>
-      <c r="AH5">
-        <v>0.07349488979999999</v>
-      </c>
-      <c r="AI5">
-        <v>0.06999513314285714</v>
-      </c>
-      <c r="AJ5">
-        <v>0.0664953764857143</v>
-      </c>
-      <c r="AK5">
-        <v>0.06299561982857142</v>
-      </c>
-      <c r="AL5">
-        <v>0.05949586317142858</v>
-      </c>
-      <c r="AM5">
-        <v>0.05599610651428572</v>
-      </c>
-      <c r="AN5">
-        <v>0.05249634985714286</v>
-      </c>
-      <c r="AO5">
-        <v>0.0489965932</v>
-      </c>
-      <c r="AP5">
-        <v>0.04549683654285715</v>
-      </c>
-      <c r="AQ5">
-        <v>0.04199707988571429</v>
-      </c>
-      <c r="AR5">
-        <v>0.03849732322857143</v>
-      </c>
-      <c r="AS5">
-        <v>0.03499756657142857</v>
-      </c>
-      <c r="AT5">
-        <v>0.03149780991428571</v>
-      </c>
-      <c r="AU5">
-        <v>0.02799805325714285</v>
-      </c>
-      <c r="AV5">
-        <v>0.02449829659999999</v>
-      </c>
-      <c r="AW5">
-        <v>0.02099853994285714</v>
-      </c>
-      <c r="AX5">
-        <v>0.01749878328571429</v>
-      </c>
-      <c r="AY5">
-        <v>0.01399902662857143</v>
-      </c>
-      <c r="AZ5">
-        <v>0.01049926997142858</v>
-      </c>
-      <c r="BA5">
-        <v>0.006999513314285716</v>
-      </c>
-      <c r="BB5">
-        <v>0.003499756657142858</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:55">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6">
-        <v>58</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>0.377517487</v>
-      </c>
-      <c r="K6">
-        <v>0.377517487</v>
-      </c>
-      <c r="L6">
-        <v>0.377517487</v>
-      </c>
-      <c r="M6">
-        <v>0.377517487</v>
-      </c>
-      <c r="N6">
-        <v>0.377517487</v>
-      </c>
-      <c r="O6">
-        <v>0.377517487</v>
-      </c>
-      <c r="P6">
-        <v>0.377517487</v>
-      </c>
-      <c r="Q6">
-        <v>0.377517487</v>
-      </c>
-      <c r="R6">
-        <v>0.377517487</v>
-      </c>
-      <c r="S6">
-        <v>0.377517487</v>
-      </c>
-      <c r="T6">
-        <v>0.377517487</v>
-      </c>
-      <c r="U6">
-        <v>0.3667312730857143</v>
-      </c>
-      <c r="V6">
-        <v>0.3559450591714285</v>
-      </c>
-      <c r="W6">
-        <v>0.3451588452571429</v>
-      </c>
-      <c r="X6">
-        <v>0.3343726313428571</v>
-      </c>
-      <c r="Y6">
-        <v>0.3235864174285714</v>
-      </c>
-      <c r="Z6">
-        <v>0.3128002035142857</v>
-      </c>
-      <c r="AA6">
-        <v>0.3020139896</v>
-      </c>
-      <c r="AB6">
-        <v>0.2912277756857143</v>
-      </c>
-      <c r="AC6">
-        <v>0.2804415617714286</v>
-      </c>
-      <c r="AD6">
-        <v>0.2696553478571428</v>
-      </c>
-      <c r="AE6">
-        <v>0.2588691339428572</v>
-      </c>
-      <c r="AF6">
-        <v>0.2480829200285714</v>
-      </c>
-      <c r="AG6">
-        <v>0.2372967061142857</v>
-      </c>
-      <c r="AH6">
-        <v>0.2265104922</v>
-      </c>
-      <c r="AI6">
-        <v>0.2157242782857143</v>
-      </c>
-      <c r="AJ6">
-        <v>0.2049380643714286</v>
-      </c>
-      <c r="AK6">
-        <v>0.1941518504571428</v>
-      </c>
-      <c r="AL6">
-        <v>0.1833656365428571</v>
-      </c>
-      <c r="AM6">
-        <v>0.1725794226285714</v>
-      </c>
-      <c r="AN6">
-        <v>0.1617932087142857</v>
-      </c>
-      <c r="AO6">
-        <v>0.1510069948</v>
-      </c>
-      <c r="AP6">
-        <v>0.1402207808857143</v>
-      </c>
-      <c r="AQ6">
-        <v>0.1294345669714286</v>
-      </c>
-      <c r="AR6">
-        <v>0.1186483530571428</v>
-      </c>
-      <c r="AS6">
-        <v>0.1078621391428571</v>
-      </c>
-      <c r="AT6">
-        <v>0.09707592522857142</v>
-      </c>
-      <c r="AU6">
-        <v>0.0862897113142857</v>
-      </c>
-      <c r="AV6">
-        <v>0.07550349739999998</v>
-      </c>
-      <c r="AW6">
-        <v>0.06471728348571426</v>
-      </c>
-      <c r="AX6">
-        <v>0.05393106957142859</v>
-      </c>
-      <c r="AY6">
-        <v>0.04314485565714287</v>
-      </c>
-      <c r="AZ6">
-        <v>0.03235864174285715</v>
-      </c>
-      <c r="BA6">
-        <v>0.02157242782857144</v>
-      </c>
-      <c r="BB6">
-        <v>0.01078621391428572</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:55">
-      <c r="A7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7">
-        <v>59</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0.00857142857142857</v>
-      </c>
-      <c r="V7">
-        <v>0.01714285714285714</v>
-      </c>
-      <c r="W7">
-        <v>0.02571428571428571</v>
-      </c>
-      <c r="X7">
-        <v>0.03428571428571428</v>
-      </c>
-      <c r="Y7">
-        <v>0.04285714285714285</v>
-      </c>
-      <c r="Z7">
-        <v>0.05142857142857143</v>
-      </c>
-      <c r="AA7">
-        <v>0.06</v>
-      </c>
-      <c r="AB7">
-        <v>0.06857142857142856</v>
-      </c>
-      <c r="AC7">
-        <v>0.07714285714285714</v>
-      </c>
-      <c r="AD7">
-        <v>0.0857142857142857</v>
-      </c>
-      <c r="AE7">
-        <v>0.09428571428571428</v>
-      </c>
-      <c r="AF7">
-        <v>0.1028571428571429</v>
-      </c>
-      <c r="AG7">
-        <v>0.1114285714285714</v>
-      </c>
-      <c r="AH7">
-        <v>0.12</v>
-      </c>
-      <c r="AI7">
-        <v>0.1285714285714286</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AK7">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AL7">
-        <v>0.1542857142857143</v>
-      </c>
-      <c r="AM7">
-        <v>0.1628571428571428</v>
-      </c>
-      <c r="AN7">
-        <v>0.1714285714285714</v>
-      </c>
-      <c r="AO7">
-        <v>0.18</v>
-      </c>
-      <c r="AP7">
-        <v>0.1885714285714286</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1971428571428571</v>
-      </c>
-      <c r="AR7">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AS7">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="AT7">
-        <v>0.2228571428571429</v>
-      </c>
-      <c r="AU7">
-        <v>0.2314285714285714</v>
-      </c>
-      <c r="AV7">
-        <v>0.24</v>
-      </c>
-      <c r="AW7">
-        <v>0.2485714285714286</v>
-      </c>
-      <c r="AX7">
-        <v>0.2571428571428571</v>
-      </c>
-      <c r="AY7">
-        <v>0.2657142857142857</v>
-      </c>
-      <c r="AZ7">
-        <v>0.2742857142857142</v>
-      </c>
-      <c r="BA7">
-        <v>0.2828571428571429</v>
-      </c>
-      <c r="BB7">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="BC7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:55">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8">
-        <v>59</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0.00857142857142857</v>
-      </c>
-      <c r="V8">
-        <v>0.01714285714285714</v>
-      </c>
-      <c r="W8">
-        <v>0.02571428571428571</v>
-      </c>
-      <c r="X8">
-        <v>0.03428571428571428</v>
-      </c>
-      <c r="Y8">
-        <v>0.04285714285714285</v>
-      </c>
-      <c r="Z8">
-        <v>0.05142857142857143</v>
-      </c>
-      <c r="AA8">
-        <v>0.06</v>
-      </c>
-      <c r="AB8">
-        <v>0.06857142857142856</v>
-      </c>
-      <c r="AC8">
-        <v>0.07714285714285714</v>
-      </c>
-      <c r="AD8">
-        <v>0.0857142857142857</v>
-      </c>
-      <c r="AE8">
-        <v>0.09428571428571428</v>
-      </c>
-      <c r="AF8">
-        <v>0.1028571428571429</v>
-      </c>
-      <c r="AG8">
-        <v>0.1114285714285714</v>
-      </c>
-      <c r="AH8">
-        <v>0.12</v>
-      </c>
-      <c r="AI8">
-        <v>0.1285714285714286</v>
-      </c>
-      <c r="AJ8">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AK8">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AL8">
-        <v>0.1542857142857143</v>
-      </c>
-      <c r="AM8">
-        <v>0.1628571428571428</v>
-      </c>
-      <c r="AN8">
-        <v>0.1714285714285714</v>
-      </c>
-      <c r="AO8">
-        <v>0.18</v>
-      </c>
-      <c r="AP8">
-        <v>0.1885714285714286</v>
-      </c>
-      <c r="AQ8">
-        <v>0.1971428571428571</v>
-      </c>
-      <c r="AR8">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AS8">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="AT8">
-        <v>0.2228571428571429</v>
-      </c>
-      <c r="AU8">
-        <v>0.2314285714285714</v>
-      </c>
-      <c r="AV8">
-        <v>0.24</v>
-      </c>
-      <c r="AW8">
-        <v>0.2485714285714286</v>
-      </c>
-      <c r="AX8">
-        <v>0.2571428571428571</v>
-      </c>
-      <c r="AY8">
-        <v>0.2657142857142857</v>
-      </c>
-      <c r="AZ8">
-        <v>0.2742857142857142</v>
-      </c>
-      <c r="BA8">
-        <v>0.2828571428571429</v>
-      </c>
-      <c r="BB8">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="BC8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:55">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0.000228522</v>
-      </c>
-      <c r="K9">
-        <v>0.000228522</v>
-      </c>
-      <c r="L9">
-        <v>0.000228522</v>
-      </c>
-      <c r="M9">
-        <v>0.000228522</v>
-      </c>
-      <c r="N9">
-        <v>0.000228522</v>
-      </c>
-      <c r="O9">
-        <v>0.000228522</v>
-      </c>
-      <c r="P9">
-        <v>0.000228522</v>
-      </c>
-      <c r="Q9">
-        <v>0.000228522</v>
-      </c>
-      <c r="R9">
-        <v>0.000228522</v>
-      </c>
-      <c r="S9">
-        <v>0.000228522</v>
-      </c>
-      <c r="T9">
-        <v>0.000228522</v>
-      </c>
-      <c r="U9">
-        <v>0.0002219928</v>
-      </c>
-      <c r="V9">
-        <v>0.0002154636</v>
-      </c>
-      <c r="W9">
-        <v>0.0002089344</v>
-      </c>
-      <c r="X9">
-        <v>0.0002024052</v>
-      </c>
-      <c r="Y9">
-        <v>0.000195876</v>
-      </c>
-      <c r="Z9">
-        <v>0.0001893468</v>
-      </c>
-      <c r="AA9">
-        <v>0.0001828176</v>
-      </c>
-      <c r="AB9">
-        <v>0.0001762884</v>
-      </c>
-      <c r="AC9">
-        <v>0.0001697592</v>
-      </c>
-      <c r="AD9">
-        <v>0.00016323</v>
-      </c>
-      <c r="AE9">
-        <v>0.0001567008</v>
-      </c>
-      <c r="AF9">
-        <v>0.0001501716</v>
-      </c>
-      <c r="AG9">
-        <v>0.0001436424</v>
-      </c>
-      <c r="AH9">
-        <v>0.0001371132</v>
-      </c>
-      <c r="AI9">
-        <v>0.000130584</v>
-      </c>
-      <c r="AJ9">
-        <v>0.0001240548</v>
-      </c>
-      <c r="AK9">
-        <v>0.0001175256</v>
-      </c>
-      <c r="AL9">
-        <v>0.0001109964</v>
-      </c>
-      <c r="AM9">
-        <v>0.0001044672</v>
-      </c>
-      <c r="AN9">
-        <v>9.793800000000001E-05</v>
-      </c>
-      <c r="AO9">
-        <v>9.14088E-05</v>
-      </c>
-      <c r="AP9">
-        <v>8.48796E-05</v>
-      </c>
-      <c r="AQ9">
-        <v>7.835039999999999E-05</v>
-      </c>
-      <c r="AR9">
-        <v>7.182119999999999E-05</v>
-      </c>
-      <c r="AS9">
-        <v>6.5292E-05</v>
-      </c>
-      <c r="AT9">
-        <v>5.876279999999999E-05</v>
-      </c>
-      <c r="AU9">
-        <v>5.223359999999999E-05</v>
-      </c>
-      <c r="AV9">
-        <v>4.570439999999999E-05</v>
-      </c>
-      <c r="AW9">
-        <v>3.917519999999998E-05</v>
-      </c>
-      <c r="AX9">
-        <v>3.264600000000001E-05</v>
-      </c>
-      <c r="AY9">
-        <v>2.611680000000001E-05</v>
-      </c>
-      <c r="AZ9">
-        <v>1.958760000000001E-05</v>
-      </c>
-      <c r="BA9">
-        <v>1.30584E-05</v>
-      </c>
-      <c r="BB9">
-        <v>6.529200000000002E-06</v>
-      </c>
-      <c r="BC9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:55">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10">
-        <v>59</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>0.000228522</v>
-      </c>
-      <c r="K10">
-        <v>0.000228522</v>
-      </c>
-      <c r="L10">
-        <v>0.000228522</v>
-      </c>
-      <c r="M10">
-        <v>0.000228522</v>
-      </c>
-      <c r="N10">
-        <v>0.000228522</v>
-      </c>
-      <c r="O10">
-        <v>0.000228522</v>
-      </c>
-      <c r="P10">
-        <v>0.000228522</v>
-      </c>
-      <c r="Q10">
-        <v>0.000228522</v>
-      </c>
-      <c r="R10">
-        <v>0.000228522</v>
-      </c>
-      <c r="S10">
-        <v>0.000228522</v>
-      </c>
-      <c r="T10">
-        <v>0.000228522</v>
-      </c>
-      <c r="U10">
-        <v>0.0002219928</v>
-      </c>
-      <c r="V10">
-        <v>0.0002154636</v>
-      </c>
-      <c r="W10">
-        <v>0.0002089344</v>
-      </c>
-      <c r="X10">
-        <v>0.0002024052</v>
-      </c>
-      <c r="Y10">
-        <v>0.000195876</v>
-      </c>
-      <c r="Z10">
-        <v>0.0001893468</v>
-      </c>
-      <c r="AA10">
-        <v>0.0001828176</v>
-      </c>
-      <c r="AB10">
-        <v>0.0001762884</v>
-      </c>
-      <c r="AC10">
-        <v>0.0001697592</v>
-      </c>
-      <c r="AD10">
-        <v>0.00016323</v>
-      </c>
-      <c r="AE10">
-        <v>0.0001567008</v>
-      </c>
-      <c r="AF10">
-        <v>0.0001501716</v>
-      </c>
-      <c r="AG10">
-        <v>0.0001436424</v>
-      </c>
-      <c r="AH10">
-        <v>0.0001371132</v>
-      </c>
-      <c r="AI10">
-        <v>0.000130584</v>
-      </c>
-      <c r="AJ10">
-        <v>0.0001240548</v>
-      </c>
-      <c r="AK10">
-        <v>0.0001175256</v>
-      </c>
-      <c r="AL10">
-        <v>0.0001109964</v>
-      </c>
-      <c r="AM10">
-        <v>0.0001044672</v>
-      </c>
-      <c r="AN10">
-        <v>9.793800000000001E-05</v>
-      </c>
-      <c r="AO10">
-        <v>9.14088E-05</v>
-      </c>
-      <c r="AP10">
-        <v>8.48796E-05</v>
-      </c>
-      <c r="AQ10">
-        <v>7.835039999999999E-05</v>
-      </c>
-      <c r="AR10">
-        <v>7.182119999999999E-05</v>
-      </c>
-      <c r="AS10">
-        <v>6.5292E-05</v>
-      </c>
-      <c r="AT10">
-        <v>5.876279999999999E-05</v>
-      </c>
-      <c r="AU10">
-        <v>5.223359999999999E-05</v>
-      </c>
-      <c r="AV10">
-        <v>4.570439999999999E-05</v>
-      </c>
-      <c r="AW10">
-        <v>3.917519999999998E-05</v>
-      </c>
-      <c r="AX10">
-        <v>3.264600000000001E-05</v>
-      </c>
-      <c r="AY10">
-        <v>2.611680000000001E-05</v>
-      </c>
-      <c r="AZ10">
-        <v>1.958760000000001E-05</v>
-      </c>
-      <c r="BA10">
-        <v>1.30584E-05</v>
-      </c>
-      <c r="BB10">
-        <v>6.529200000000002E-06</v>
-      </c>
-      <c r="BC10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:55">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11">
-        <v>59</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0.004113394</v>
-      </c>
-      <c r="K11">
-        <v>0.004113394</v>
-      </c>
-      <c r="L11">
-        <v>0.004113394</v>
-      </c>
-      <c r="M11">
-        <v>0.004113394</v>
-      </c>
-      <c r="N11">
-        <v>0.004113394</v>
-      </c>
-      <c r="O11">
-        <v>0.004113394</v>
-      </c>
-      <c r="P11">
-        <v>0.004113394</v>
-      </c>
-      <c r="Q11">
-        <v>0.004113394</v>
-      </c>
-      <c r="R11">
-        <v>0.004113394</v>
-      </c>
-      <c r="S11">
-        <v>0.004113394</v>
-      </c>
-      <c r="T11">
-        <v>0.004113394</v>
-      </c>
-      <c r="U11">
-        <v>0.003995868457142857</v>
-      </c>
-      <c r="V11">
-        <v>0.003878342914285714</v>
-      </c>
-      <c r="W11">
-        <v>0.003760817371428572</v>
-      </c>
-      <c r="X11">
-        <v>0.003643291828571429</v>
-      </c>
-      <c r="Y11">
-        <v>0.003525766285714286</v>
-      </c>
-      <c r="Z11">
-        <v>0.003408240742857143</v>
-      </c>
-      <c r="AA11">
-        <v>0.003290715200000001</v>
-      </c>
-      <c r="AB11">
-        <v>0.003173189657142857</v>
-      </c>
-      <c r="AC11">
-        <v>0.003055664114285715</v>
-      </c>
-      <c r="AD11">
-        <v>0.002938138571428572</v>
-      </c>
-      <c r="AE11">
-        <v>0.002820613028571429</v>
-      </c>
-      <c r="AF11">
-        <v>0.002703087485714286</v>
-      </c>
-      <c r="AG11">
-        <v>0.002585561942857143</v>
-      </c>
-      <c r="AH11">
-        <v>0.0024680364</v>
-      </c>
-      <c r="AI11">
-        <v>0.002350510857142857</v>
-      </c>
-      <c r="AJ11">
-        <v>0.002232985314285715</v>
-      </c>
-      <c r="AK11">
-        <v>0.002115459771428571</v>
-      </c>
-      <c r="AL11">
-        <v>0.001997934228571429</v>
-      </c>
-      <c r="AM11">
-        <v>0.001880408685714286</v>
-      </c>
-      <c r="AN11">
-        <v>0.001762883142857143</v>
-      </c>
-      <c r="AO11">
-        <v>0.0016453576</v>
-      </c>
-      <c r="AP11">
-        <v>0.001527832057142857</v>
-      </c>
-      <c r="AQ11">
-        <v>0.001410306514285714</v>
-      </c>
-      <c r="AR11">
-        <v>0.001292780971428572</v>
-      </c>
-      <c r="AS11">
-        <v>0.001175255428571429</v>
-      </c>
-      <c r="AT11">
-        <v>0.001057729885714286</v>
-      </c>
-      <c r="AU11">
-        <v>0.0009402043428571428</v>
-      </c>
-      <c r="AV11">
-        <v>0.0008226787999999999</v>
-      </c>
-      <c r="AW11">
-        <v>0.000705153257142857</v>
-      </c>
-      <c r="AX11">
-        <v>0.0005876277142857145</v>
-      </c>
-      <c r="AY11">
-        <v>0.0004701021714285716</v>
-      </c>
-      <c r="AZ11">
-        <v>0.0003525766285714287</v>
-      </c>
-      <c r="BA11">
-        <v>0.0002350510857142858</v>
-      </c>
-      <c r="BB11">
-        <v>0.0001175255428571429</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:55">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12">
-        <v>59</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>0.261553696</v>
-      </c>
-      <c r="K12">
-        <v>0.261553696</v>
-      </c>
-      <c r="L12">
-        <v>0.261553696</v>
-      </c>
-      <c r="M12">
-        <v>0.261553696</v>
-      </c>
-      <c r="N12">
-        <v>0.261553696</v>
-      </c>
-      <c r="O12">
-        <v>0.261553696</v>
-      </c>
-      <c r="P12">
-        <v>0.261553696</v>
-      </c>
-      <c r="Q12">
-        <v>0.261553696</v>
-      </c>
-      <c r="R12">
-        <v>0.261553696</v>
-      </c>
-      <c r="S12">
-        <v>0.261553696</v>
-      </c>
-      <c r="T12">
-        <v>0.261553696</v>
-      </c>
-      <c r="U12">
-        <v>0.2597950189714286</v>
-      </c>
-      <c r="V12">
-        <v>0.2580363419428571</v>
-      </c>
-      <c r="W12">
-        <v>0.2562776649142857</v>
-      </c>
-      <c r="X12">
-        <v>0.2545189878857143</v>
-      </c>
-      <c r="Y12">
-        <v>0.2527603108571428</v>
-      </c>
-      <c r="Z12">
-        <v>0.2510016338285714</v>
-      </c>
-      <c r="AA12">
-        <v>0.2492429568</v>
-      </c>
-      <c r="AB12">
-        <v>0.2474842797714286</v>
-      </c>
-      <c r="AC12">
-        <v>0.2457256027428572</v>
-      </c>
-      <c r="AD12">
-        <v>0.2439669257142857</v>
-      </c>
-      <c r="AE12">
-        <v>0.2422082486857143</v>
-      </c>
-      <c r="AF12">
-        <v>0.2404495716571429</v>
-      </c>
-      <c r="AG12">
-        <v>0.2386908946285714</v>
-      </c>
-      <c r="AH12">
-        <v>0.2369322176</v>
-      </c>
-      <c r="AI12">
-        <v>0.2351735405714286</v>
-      </c>
-      <c r="AJ12">
-        <v>0.2334148635428572</v>
-      </c>
-      <c r="AK12">
-        <v>0.2316561865142857</v>
-      </c>
-      <c r="AL12">
-        <v>0.2298975094857143</v>
-      </c>
-      <c r="AM12">
-        <v>0.2281388324571429</v>
-      </c>
-      <c r="AN12">
-        <v>0.2263801554285714</v>
-      </c>
-      <c r="AO12">
-        <v>0.2246214784</v>
-      </c>
-      <c r="AP12">
-        <v>0.2228628013714286</v>
-      </c>
-      <c r="AQ12">
-        <v>0.2211041243428571</v>
-      </c>
-      <c r="AR12">
-        <v>0.2193454473142857</v>
-      </c>
-      <c r="AS12">
-        <v>0.2175867702857143</v>
-      </c>
-      <c r="AT12">
-        <v>0.2158280932571429</v>
-      </c>
-      <c r="AU12">
-        <v>0.2140694162285715</v>
-      </c>
-      <c r="AV12">
-        <v>0.2123107392</v>
-      </c>
-      <c r="AW12">
-        <v>0.2105520621714286</v>
-      </c>
-      <c r="AX12">
-        <v>0.2087933851428572</v>
-      </c>
-      <c r="AY12">
-        <v>0.2070347081142857</v>
-      </c>
-      <c r="AZ12">
-        <v>0.2052760310857143</v>
-      </c>
-      <c r="BA12">
-        <v>0.2035173540571429</v>
-      </c>
-      <c r="BB12">
-        <v>0.2017586770285714</v>
-      </c>
-      <c r="BC12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:55">
-      <c r="A13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13">
-        <v>59</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0.261553696</v>
-      </c>
-      <c r="K13">
-        <v>0.261553696</v>
-      </c>
-      <c r="L13">
-        <v>0.261553696</v>
-      </c>
-      <c r="M13">
-        <v>0.261553696</v>
-      </c>
-      <c r="N13">
-        <v>0.261553696</v>
-      </c>
-      <c r="O13">
-        <v>0.261553696</v>
-      </c>
-      <c r="P13">
-        <v>0.261553696</v>
-      </c>
-      <c r="Q13">
-        <v>0.261553696</v>
-      </c>
-      <c r="R13">
-        <v>0.261553696</v>
-      </c>
-      <c r="S13">
-        <v>0.261553696</v>
-      </c>
-      <c r="T13">
-        <v>0.261553696</v>
-      </c>
-      <c r="U13">
-        <v>0.2597950189714286</v>
-      </c>
-      <c r="V13">
-        <v>0.2580363419428571</v>
-      </c>
-      <c r="W13">
-        <v>0.2562776649142857</v>
-      </c>
-      <c r="X13">
-        <v>0.2545189878857143</v>
-      </c>
-      <c r="Y13">
-        <v>0.2527603108571428</v>
-      </c>
-      <c r="Z13">
-        <v>0.2510016338285714</v>
-      </c>
-      <c r="AA13">
-        <v>0.2492429568</v>
-      </c>
-      <c r="AB13">
-        <v>0.2474842797714286</v>
-      </c>
-      <c r="AC13">
-        <v>0.2457256027428572</v>
-      </c>
-      <c r="AD13">
-        <v>0.2439669257142857</v>
-      </c>
-      <c r="AE13">
-        <v>0.2422082486857143</v>
-      </c>
-      <c r="AF13">
-        <v>0.2404495716571429</v>
-      </c>
-      <c r="AG13">
-        <v>0.2386908946285714</v>
-      </c>
-      <c r="AH13">
-        <v>0.2369322176</v>
-      </c>
-      <c r="AI13">
-        <v>0.2351735405714286</v>
-      </c>
-      <c r="AJ13">
-        <v>0.2334148635428572</v>
-      </c>
-      <c r="AK13">
-        <v>0.2316561865142857</v>
-      </c>
-      <c r="AL13">
-        <v>0.2298975094857143</v>
-      </c>
-      <c r="AM13">
-        <v>0.2281388324571429</v>
-      </c>
-      <c r="AN13">
-        <v>0.2263801554285714</v>
-      </c>
-      <c r="AO13">
-        <v>0.2246214784</v>
-      </c>
-      <c r="AP13">
-        <v>0.2228628013714286</v>
-      </c>
-      <c r="AQ13">
-        <v>0.2211041243428571</v>
-      </c>
-      <c r="AR13">
-        <v>0.2193454473142857</v>
-      </c>
-      <c r="AS13">
-        <v>0.2175867702857143</v>
-      </c>
-      <c r="AT13">
-        <v>0.2158280932571429</v>
-      </c>
-      <c r="AU13">
-        <v>0.2140694162285715</v>
-      </c>
-      <c r="AV13">
-        <v>0.2123107392</v>
-      </c>
-      <c r="AW13">
-        <v>0.2105520621714286</v>
-      </c>
-      <c r="AX13">
-        <v>0.2087933851428572</v>
-      </c>
-      <c r="AY13">
-        <v>0.2070347081142857</v>
-      </c>
-      <c r="AZ13">
-        <v>0.2052760310857143</v>
-      </c>
-      <c r="BA13">
-        <v>0.2035173540571429</v>
-      </c>
-      <c r="BB13">
-        <v>0.2017586770285714</v>
-      </c>
-      <c r="BC13">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:55">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14">
-        <v>59</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>0.073899806</v>
-      </c>
-      <c r="K14">
-        <v>0.073899806</v>
-      </c>
-      <c r="L14">
-        <v>0.073899806</v>
-      </c>
-      <c r="M14">
-        <v>0.073899806</v>
-      </c>
-      <c r="N14">
-        <v>0.073899806</v>
-      </c>
-      <c r="O14">
-        <v>0.073899806</v>
-      </c>
-      <c r="P14">
-        <v>0.073899806</v>
-      </c>
-      <c r="Q14">
-        <v>0.073899806</v>
-      </c>
-      <c r="R14">
-        <v>0.073899806</v>
-      </c>
-      <c r="S14">
-        <v>0.073899806</v>
-      </c>
-      <c r="T14">
-        <v>0.073899806</v>
-      </c>
-      <c r="U14">
-        <v>0.07178838297142857</v>
-      </c>
-      <c r="V14">
-        <v>0.06967695994285714</v>
-      </c>
-      <c r="W14">
-        <v>0.06756553691428571</v>
-      </c>
-      <c r="X14">
-        <v>0.06545411388571429</v>
-      </c>
-      <c r="Y14">
-        <v>0.06334269085714286</v>
-      </c>
-      <c r="Z14">
-        <v>0.06123126782857143</v>
-      </c>
-      <c r="AA14">
-        <v>0.0591198448</v>
-      </c>
-      <c r="AB14">
-        <v>0.05700842177142857</v>
-      </c>
-      <c r="AC14">
-        <v>0.05489699874285715</v>
-      </c>
-      <c r="AD14">
-        <v>0.05278557571428572</v>
-      </c>
-      <c r="AE14">
-        <v>0.05067415268571428</v>
-      </c>
-      <c r="AF14">
-        <v>0.04856272965714285</v>
-      </c>
-      <c r="AG14">
-        <v>0.04645130662857143</v>
-      </c>
-      <c r="AH14">
-        <v>0.0443398836</v>
-      </c>
-      <c r="AI14">
-        <v>0.04222846057142857</v>
-      </c>
-      <c r="AJ14">
-        <v>0.04011703754285715</v>
-      </c>
-      <c r="AK14">
-        <v>0.03800561451428571</v>
-      </c>
-      <c r="AL14">
-        <v>0.03589419148571429</v>
-      </c>
-      <c r="AM14">
-        <v>0.03378276845714286</v>
-      </c>
-      <c r="AN14">
-        <v>0.03167134542857143</v>
-      </c>
-      <c r="AO14">
-        <v>0.0295599224</v>
-      </c>
-      <c r="AP14">
-        <v>0.02744849937142857</v>
-      </c>
-      <c r="AQ14">
-        <v>0.02533707634285714</v>
-      </c>
-      <c r="AR14">
-        <v>0.02322565331428571</v>
-      </c>
-      <c r="AS14">
-        <v>0.02111423028571428</v>
-      </c>
-      <c r="AT14">
-        <v>0.01900280725714286</v>
-      </c>
-      <c r="AU14">
-        <v>0.01689138422857142</v>
-      </c>
-      <c r="AV14">
-        <v>0.0147799612</v>
-      </c>
-      <c r="AW14">
-        <v>0.01266853817142857</v>
-      </c>
-      <c r="AX14">
-        <v>0.01055711514285715</v>
-      </c>
-      <c r="AY14">
-        <v>0.008445692114285717</v>
-      </c>
-      <c r="AZ14">
-        <v>0.006334269085714288</v>
-      </c>
-      <c r="BA14">
-        <v>0.004222846057142859</v>
-      </c>
-      <c r="BB14">
-        <v>0.002111423028571429</v>
-      </c>
-      <c r="BC14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:55">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15">
-        <v>59</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>0.398422364</v>
-      </c>
-      <c r="K15">
-        <v>0.398422364</v>
-      </c>
-      <c r="L15">
-        <v>0.398422364</v>
-      </c>
-      <c r="M15">
-        <v>0.398422364</v>
-      </c>
-      <c r="N15">
-        <v>0.398422364</v>
-      </c>
-      <c r="O15">
-        <v>0.398422364</v>
-      </c>
-      <c r="P15">
-        <v>0.398422364</v>
-      </c>
-      <c r="Q15">
-        <v>0.398422364</v>
-      </c>
-      <c r="R15">
-        <v>0.398422364</v>
-      </c>
-      <c r="S15">
-        <v>0.398422364</v>
-      </c>
-      <c r="T15">
-        <v>0.398422364</v>
-      </c>
-      <c r="U15">
-        <v>0.3870388678857142</v>
-      </c>
-      <c r="V15">
-        <v>0.3756553717714285</v>
-      </c>
-      <c r="W15">
-        <v>0.3642718756571428</v>
-      </c>
-      <c r="X15">
-        <v>0.3528883795428571</v>
-      </c>
-      <c r="Y15">
-        <v>0.3415048834285714</v>
-      </c>
-      <c r="Z15">
-        <v>0.3301213873142857</v>
-      </c>
-      <c r="AA15">
-        <v>0.3187378912</v>
-      </c>
-      <c r="AB15">
-        <v>0.3073543950857143</v>
-      </c>
-      <c r="AC15">
-        <v>0.2959708989714286</v>
-      </c>
-      <c r="AD15">
-        <v>0.2845874028571428</v>
-      </c>
-      <c r="AE15">
-        <v>0.2732039067428571</v>
-      </c>
-      <c r="AF15">
-        <v>0.2618204106285714</v>
-      </c>
-      <c r="AG15">
-        <v>0.2504369145142857</v>
-      </c>
-      <c r="AH15">
-        <v>0.2390534184</v>
-      </c>
-      <c r="AI15">
-        <v>0.2276699222857143</v>
-      </c>
-      <c r="AJ15">
-        <v>0.2162864261714286</v>
-      </c>
-      <c r="AK15">
-        <v>0.2049029300571428</v>
-      </c>
-      <c r="AL15">
-        <v>0.1935194339428571</v>
-      </c>
-      <c r="AM15">
-        <v>0.1821359378285714</v>
-      </c>
-      <c r="AN15">
-        <v>0.1707524417142857</v>
-      </c>
-      <c r="AO15">
-        <v>0.1593689456</v>
-      </c>
-      <c r="AP15">
-        <v>0.1479854494857143</v>
-      </c>
-      <c r="AQ15">
-        <v>0.1366019533714286</v>
-      </c>
-      <c r="AR15">
-        <v>0.1252184572571428</v>
-      </c>
-      <c r="AS15">
-        <v>0.1138349611428571</v>
-      </c>
-      <c r="AT15">
-        <v>0.1024514650285714</v>
-      </c>
-      <c r="AU15">
-        <v>0.09106796891428569</v>
-      </c>
-      <c r="AV15">
-        <v>0.07968447279999998</v>
-      </c>
-      <c r="AW15">
-        <v>0.06830097668571426</v>
-      </c>
-      <c r="AX15">
-        <v>0.05691748057142858</v>
-      </c>
-      <c r="AY15">
-        <v>0.04553398445714287</v>
-      </c>
-      <c r="AZ15">
-        <v>0.03415048834285715</v>
-      </c>
-      <c r="BA15">
-        <v>0.02276699222857144</v>
-      </c>
-      <c r="BB15">
-        <v>0.01138349611428572</v>
-      </c>
-      <c r="BC15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:55">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16">
-        <v>60</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0.02285714285714286</v>
-      </c>
-      <c r="V16">
-        <v>0.04571428571428571</v>
-      </c>
-      <c r="W16">
-        <v>0.06857142857142857</v>
-      </c>
-      <c r="X16">
-        <v>0.09142857142857143</v>
-      </c>
-      <c r="Y16">
-        <v>0.1142857142857143</v>
-      </c>
-      <c r="Z16">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AA16">
-        <v>0.16</v>
-      </c>
-      <c r="AB16">
-        <v>0.1828571428571429</v>
-      </c>
-      <c r="AC16">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AD16">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE16">
-        <v>0.2514285714285714</v>
-      </c>
-      <c r="AF16">
-        <v>0.2742857142857143</v>
-      </c>
-      <c r="AG16">
-        <v>0.2971428571428572</v>
-      </c>
-      <c r="AH16">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AI16">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AJ16">
-        <v>0.3657142857142857</v>
-      </c>
-      <c r="AK16">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AL16">
-        <v>0.4114285714285714</v>
-      </c>
-      <c r="AM16">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="AN16">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="AO16">
-        <v>0.48</v>
-      </c>
-      <c r="AP16">
-        <v>0.5028571428571429</v>
-      </c>
-      <c r="AQ16">
-        <v>0.5257142857142857</v>
-      </c>
-      <c r="AR16">
-        <v>0.5485714285714286</v>
-      </c>
-      <c r="AS16">
-        <v>0.5714285714285715</v>
-      </c>
-      <c r="AT16">
-        <v>0.5942857142857143</v>
-      </c>
-      <c r="AU16">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="AV16">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="AW16">
-        <v>0.6628571428571429</v>
-      </c>
-      <c r="AX16">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AY16">
-        <v>0.7085714285714286</v>
-      </c>
-      <c r="AZ16">
-        <v>0.7314285714285714</v>
-      </c>
-      <c r="BA16">
-        <v>0.7542857142857143</v>
-      </c>
-      <c r="BB16">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BC16">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:55">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17">
-        <v>60</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>0.004570438</v>
-      </c>
-      <c r="K17">
-        <v>0.004570438</v>
-      </c>
-      <c r="L17">
-        <v>0.004570438</v>
-      </c>
-      <c r="M17">
-        <v>0.004570438</v>
-      </c>
-      <c r="N17">
-        <v>0.004570438</v>
-      </c>
-      <c r="O17">
-        <v>0.004570438</v>
-      </c>
-      <c r="P17">
-        <v>0.004570438</v>
-      </c>
-      <c r="Q17">
-        <v>0.004570438</v>
-      </c>
-      <c r="R17">
-        <v>0.004570438</v>
-      </c>
-      <c r="S17">
-        <v>0.004570438</v>
-      </c>
-      <c r="T17">
-        <v>0.004570438</v>
-      </c>
-      <c r="U17">
-        <v>0.004439854057142856</v>
-      </c>
-      <c r="V17">
-        <v>0.004309270114285714</v>
-      </c>
-      <c r="W17">
-        <v>0.004178686171428571</v>
-      </c>
-      <c r="X17">
-        <v>0.004048102228571428</v>
-      </c>
-      <c r="Y17">
-        <v>0.003917518285714286</v>
-      </c>
-      <c r="Z17">
-        <v>0.003786934342857142</v>
-      </c>
-      <c r="AA17">
-        <v>0.0036563504</v>
-      </c>
-      <c r="AB17">
-        <v>0.003525766457142857</v>
-      </c>
-      <c r="AC17">
-        <v>0.003395182514285714</v>
-      </c>
-      <c r="AD17">
-        <v>0.003264598571428571</v>
-      </c>
-      <c r="AE17">
-        <v>0.003134014628571428</v>
-      </c>
-      <c r="AF17">
-        <v>0.003003430685714285</v>
-      </c>
-      <c r="AG17">
-        <v>0.002872846742857143</v>
-      </c>
-      <c r="AH17">
-        <v>0.002742262799999999</v>
-      </c>
-      <c r="AI17">
-        <v>0.002611678857142857</v>
-      </c>
-      <c r="AJ17">
-        <v>0.002481094914285715</v>
-      </c>
-      <c r="AK17">
-        <v>0.002350510971428571</v>
-      </c>
-      <c r="AL17">
-        <v>0.002219927028571429</v>
-      </c>
-      <c r="AM17">
-        <v>0.002089343085714286</v>
-      </c>
-      <c r="AN17">
-        <v>0.001958759142857143</v>
-      </c>
-      <c r="AO17">
-        <v>0.0018281752</v>
-      </c>
-      <c r="AP17">
-        <v>0.001697591257142857</v>
-      </c>
-      <c r="AQ17">
-        <v>0.001567007314285714</v>
-      </c>
-      <c r="AR17">
-        <v>0.001436423371428571</v>
-      </c>
-      <c r="AS17">
-        <v>0.001305839428571428</v>
-      </c>
-      <c r="AT17">
-        <v>0.001175255485714285</v>
-      </c>
-      <c r="AU17">
-        <v>0.001044671542857143</v>
-      </c>
-      <c r="AV17">
-        <v>0.0009140875999999997</v>
-      </c>
-      <c r="AW17">
-        <v>0.0007835036571428568</v>
-      </c>
-      <c r="AX17">
-        <v>0.0006529197142857144</v>
-      </c>
-      <c r="AY17">
-        <v>0.0005223357714285716</v>
-      </c>
-      <c r="AZ17">
-        <v>0.0003917518285714287</v>
-      </c>
-      <c r="BA17">
-        <v>0.0002611678857142858</v>
-      </c>
-      <c r="BB17">
-        <v>0.0001305839428571429</v>
-      </c>
-      <c r="BC17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:55">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18">
-        <v>60</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>0.261553696</v>
-      </c>
-      <c r="K18">
-        <v>0.261553696</v>
-      </c>
-      <c r="L18">
-        <v>0.261553696</v>
-      </c>
-      <c r="M18">
-        <v>0.261553696</v>
-      </c>
-      <c r="N18">
-        <v>0.261553696</v>
-      </c>
-      <c r="O18">
-        <v>0.261553696</v>
-      </c>
-      <c r="P18">
-        <v>0.261553696</v>
-      </c>
-      <c r="Q18">
-        <v>0.261553696</v>
-      </c>
-      <c r="R18">
-        <v>0.261553696</v>
-      </c>
-      <c r="S18">
-        <v>0.261553696</v>
-      </c>
-      <c r="T18">
-        <v>0.261553696</v>
-      </c>
-      <c r="U18">
-        <v>0.2569378761142857</v>
-      </c>
-      <c r="V18">
-        <v>0.2523220562285714</v>
-      </c>
-      <c r="W18">
-        <v>0.2477062363428571</v>
-      </c>
-      <c r="X18">
-        <v>0.2430904164571429</v>
-      </c>
-      <c r="Y18">
-        <v>0.2384745965714286</v>
-      </c>
-      <c r="Z18">
-        <v>0.2338587766857143</v>
-      </c>
-      <c r="AA18">
-        <v>0.2292429568</v>
-      </c>
-      <c r="AB18">
-        <v>0.2246271369142857</v>
-      </c>
-      <c r="AC18">
-        <v>0.2200113170285714</v>
-      </c>
-      <c r="AD18">
-        <v>0.2153954971428572</v>
-      </c>
-      <c r="AE18">
-        <v>0.2107796772571429</v>
-      </c>
-      <c r="AF18">
-        <v>0.2061638573714286</v>
-      </c>
-      <c r="AG18">
-        <v>0.2015480374857143</v>
-      </c>
-      <c r="AH18">
-        <v>0.1969322176</v>
-      </c>
-      <c r="AI18">
-        <v>0.1923163977142857</v>
-      </c>
-      <c r="AJ18">
-        <v>0.1877005778285714</v>
-      </c>
-      <c r="AK18">
-        <v>0.1830847579428571</v>
-      </c>
-      <c r="AL18">
-        <v>0.1784689380571429</v>
-      </c>
-      <c r="AM18">
-        <v>0.1738531181714286</v>
-      </c>
-      <c r="AN18">
-        <v>0.1692372982857143</v>
-      </c>
-      <c r="AO18">
-        <v>0.1646214784</v>
-      </c>
-      <c r="AP18">
-        <v>0.1600056585142857</v>
-      </c>
-      <c r="AQ18">
-        <v>0.1553898386285714</v>
-      </c>
-      <c r="AR18">
-        <v>0.1507740187428571</v>
-      </c>
-      <c r="AS18">
-        <v>0.1461581988571429</v>
-      </c>
-      <c r="AT18">
-        <v>0.1415423789714286</v>
-      </c>
-      <c r="AU18">
-        <v>0.1369265590857143</v>
-      </c>
-      <c r="AV18">
-        <v>0.1323107392</v>
-      </c>
-      <c r="AW18">
-        <v>0.1276949193142857</v>
-      </c>
-      <c r="AX18">
-        <v>0.1230790994285714</v>
-      </c>
-      <c r="AY18">
-        <v>0.1184632795428572</v>
-      </c>
-      <c r="AZ18">
-        <v>0.1138474596571429</v>
-      </c>
-      <c r="BA18">
-        <v>0.1092316397714286</v>
-      </c>
-      <c r="BB18">
-        <v>0.1046158198857143</v>
-      </c>
-      <c r="BC18">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:55">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19">
-        <v>60</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>0.261553696</v>
-      </c>
-      <c r="K19">
-        <v>0.261553696</v>
-      </c>
-      <c r="L19">
-        <v>0.261553696</v>
-      </c>
-      <c r="M19">
-        <v>0.261553696</v>
-      </c>
-      <c r="N19">
-        <v>0.261553696</v>
-      </c>
-      <c r="O19">
-        <v>0.261553696</v>
-      </c>
-      <c r="P19">
-        <v>0.261553696</v>
-      </c>
-      <c r="Q19">
-        <v>0.261553696</v>
-      </c>
-      <c r="R19">
-        <v>0.261553696</v>
-      </c>
-      <c r="S19">
-        <v>0.261553696</v>
-      </c>
-      <c r="T19">
-        <v>0.261553696</v>
-      </c>
-      <c r="U19">
-        <v>0.2569378761142857</v>
-      </c>
-      <c r="V19">
-        <v>0.2523220562285714</v>
-      </c>
-      <c r="W19">
-        <v>0.2477062363428571</v>
-      </c>
-      <c r="X19">
-        <v>0.2430904164571429</v>
-      </c>
-      <c r="Y19">
-        <v>0.2384745965714286</v>
-      </c>
-      <c r="Z19">
-        <v>0.2338587766857143</v>
-      </c>
-      <c r="AA19">
-        <v>0.2292429568</v>
-      </c>
-      <c r="AB19">
-        <v>0.2246271369142857</v>
-      </c>
-      <c r="AC19">
-        <v>0.2200113170285714</v>
-      </c>
-      <c r="AD19">
-        <v>0.2153954971428572</v>
-      </c>
-      <c r="AE19">
-        <v>0.2107796772571429</v>
-      </c>
-      <c r="AF19">
-        <v>0.2061638573714286</v>
-      </c>
-      <c r="AG19">
-        <v>0.2015480374857143</v>
-      </c>
-      <c r="AH19">
-        <v>0.1969322176</v>
-      </c>
-      <c r="AI19">
-        <v>0.1923163977142857</v>
-      </c>
-      <c r="AJ19">
-        <v>0.1877005778285714</v>
-      </c>
-      <c r="AK19">
-        <v>0.1830847579428571</v>
-      </c>
-      <c r="AL19">
-        <v>0.1784689380571429</v>
-      </c>
-      <c r="AM19">
-        <v>0.1738531181714286</v>
-      </c>
-      <c r="AN19">
-        <v>0.1692372982857143</v>
-      </c>
-      <c r="AO19">
-        <v>0.1646214784</v>
-      </c>
-      <c r="AP19">
-        <v>0.1600056585142857</v>
-      </c>
-      <c r="AQ19">
-        <v>0.1553898386285714</v>
-      </c>
-      <c r="AR19">
-        <v>0.1507740187428571</v>
-      </c>
-      <c r="AS19">
-        <v>0.1461581988571429</v>
-      </c>
-      <c r="AT19">
-        <v>0.1415423789714286</v>
-      </c>
-      <c r="AU19">
-        <v>0.1369265590857143</v>
-      </c>
-      <c r="AV19">
-        <v>0.1323107392</v>
-      </c>
-      <c r="AW19">
-        <v>0.1276949193142857</v>
-      </c>
-      <c r="AX19">
-        <v>0.1230790994285714</v>
-      </c>
-      <c r="AY19">
-        <v>0.1184632795428572</v>
-      </c>
-      <c r="AZ19">
-        <v>0.1138474596571429</v>
-      </c>
-      <c r="BA19">
-        <v>0.1092316397714286</v>
-      </c>
-      <c r="BB19">
-        <v>0.1046158198857143</v>
-      </c>
-      <c r="BC19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:55">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20">
-        <v>60</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>0.073899806</v>
-      </c>
-      <c r="K20">
-        <v>0.073899806</v>
-      </c>
-      <c r="L20">
-        <v>0.073899806</v>
-      </c>
-      <c r="M20">
-        <v>0.073899806</v>
-      </c>
-      <c r="N20">
-        <v>0.073899806</v>
-      </c>
-      <c r="O20">
-        <v>0.073899806</v>
-      </c>
-      <c r="P20">
-        <v>0.073899806</v>
-      </c>
-      <c r="Q20">
-        <v>0.073899806</v>
-      </c>
-      <c r="R20">
-        <v>0.073899806</v>
-      </c>
-      <c r="S20">
-        <v>0.073899806</v>
-      </c>
-      <c r="T20">
-        <v>0.073899806</v>
-      </c>
-      <c r="U20">
-        <v>0.07178838297142857</v>
-      </c>
-      <c r="V20">
-        <v>0.06967695994285714</v>
-      </c>
-      <c r="W20">
-        <v>0.06756553691428571</v>
-      </c>
-      <c r="X20">
-        <v>0.06545411388571429</v>
-      </c>
-      <c r="Y20">
-        <v>0.06334269085714286</v>
-      </c>
-      <c r="Z20">
-        <v>0.06123126782857143</v>
-      </c>
-      <c r="AA20">
-        <v>0.0591198448</v>
-      </c>
-      <c r="AB20">
-        <v>0.05700842177142857</v>
-      </c>
-      <c r="AC20">
-        <v>0.05489699874285715</v>
-      </c>
-      <c r="AD20">
-        <v>0.05278557571428572</v>
-      </c>
-      <c r="AE20">
-        <v>0.05067415268571428</v>
-      </c>
-      <c r="AF20">
-        <v>0.04856272965714285</v>
-      </c>
-      <c r="AG20">
-        <v>0.04645130662857143</v>
-      </c>
-      <c r="AH20">
-        <v>0.0443398836</v>
-      </c>
-      <c r="AI20">
-        <v>0.04222846057142857</v>
-      </c>
-      <c r="AJ20">
-        <v>0.04011703754285715</v>
-      </c>
-      <c r="AK20">
-        <v>0.03800561451428571</v>
-      </c>
-      <c r="AL20">
-        <v>0.03589419148571429</v>
-      </c>
-      <c r="AM20">
-        <v>0.03378276845714286</v>
-      </c>
-      <c r="AN20">
-        <v>0.03167134542857143</v>
-      </c>
-      <c r="AO20">
-        <v>0.0295599224</v>
-      </c>
-      <c r="AP20">
-        <v>0.02744849937142857</v>
-      </c>
-      <c r="AQ20">
-        <v>0.02533707634285714</v>
-      </c>
-      <c r="AR20">
-        <v>0.02322565331428571</v>
-      </c>
-      <c r="AS20">
-        <v>0.02111423028571428</v>
-      </c>
-      <c r="AT20">
-        <v>0.01900280725714286</v>
-      </c>
-      <c r="AU20">
-        <v>0.01689138422857142</v>
-      </c>
-      <c r="AV20">
-        <v>0.0147799612</v>
-      </c>
-      <c r="AW20">
-        <v>0.01266853817142857</v>
-      </c>
-      <c r="AX20">
-        <v>0.01055711514285715</v>
-      </c>
-      <c r="AY20">
-        <v>0.008445692114285717</v>
-      </c>
-      <c r="AZ20">
-        <v>0.006334269085714288</v>
-      </c>
-      <c r="BA20">
-        <v>0.004222846057142859</v>
-      </c>
-      <c r="BB20">
-        <v>0.002111423028571429</v>
-      </c>
-      <c r="BC20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:55">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21">
-        <v>60</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>0.398422364</v>
-      </c>
-      <c r="K21">
-        <v>0.398422364</v>
-      </c>
-      <c r="L21">
-        <v>0.398422364</v>
-      </c>
-      <c r="M21">
-        <v>0.398422364</v>
-      </c>
-      <c r="N21">
-        <v>0.398422364</v>
-      </c>
-      <c r="O21">
-        <v>0.398422364</v>
-      </c>
-      <c r="P21">
-        <v>0.398422364</v>
-      </c>
-      <c r="Q21">
-        <v>0.398422364</v>
-      </c>
-      <c r="R21">
-        <v>0.398422364</v>
-      </c>
-      <c r="S21">
-        <v>0.398422364</v>
-      </c>
-      <c r="T21">
-        <v>0.398422364</v>
-      </c>
-      <c r="U21">
-        <v>0.3870388678857142</v>
-      </c>
-      <c r="V21">
-        <v>0.3756553717714285</v>
-      </c>
-      <c r="W21">
-        <v>0.3642718756571428</v>
-      </c>
-      <c r="X21">
-        <v>0.3528883795428571</v>
-      </c>
-      <c r="Y21">
-        <v>0.3415048834285714</v>
-      </c>
-      <c r="Z21">
-        <v>0.3301213873142857</v>
-      </c>
-      <c r="AA21">
-        <v>0.3187378912</v>
-      </c>
-      <c r="AB21">
-        <v>0.3073543950857143</v>
-      </c>
-      <c r="AC21">
-        <v>0.2959708989714286</v>
-      </c>
-      <c r="AD21">
-        <v>0.2845874028571428</v>
-      </c>
-      <c r="AE21">
-        <v>0.2732039067428571</v>
-      </c>
-      <c r="AF21">
-        <v>0.2618204106285714</v>
-      </c>
-      <c r="AG21">
-        <v>0.2504369145142857</v>
-      </c>
-      <c r="AH21">
-        <v>0.2390534184</v>
-      </c>
-      <c r="AI21">
-        <v>0.2276699222857143</v>
-      </c>
-      <c r="AJ21">
-        <v>0.2162864261714286</v>
-      </c>
-      <c r="AK21">
-        <v>0.2049029300571428</v>
-      </c>
-      <c r="AL21">
-        <v>0.1935194339428571</v>
-      </c>
-      <c r="AM21">
-        <v>0.1821359378285714</v>
-      </c>
-      <c r="AN21">
-        <v>0.1707524417142857</v>
-      </c>
-      <c r="AO21">
-        <v>0.1593689456</v>
-      </c>
-      <c r="AP21">
-        <v>0.1479854494857143</v>
-      </c>
-      <c r="AQ21">
-        <v>0.1366019533714286</v>
-      </c>
-      <c r="AR21">
-        <v>0.1252184572571428</v>
-      </c>
-      <c r="AS21">
-        <v>0.1138349611428571</v>
-      </c>
-      <c r="AT21">
-        <v>0.1024514650285714</v>
-      </c>
-      <c r="AU21">
-        <v>0.09106796891428569</v>
-      </c>
-      <c r="AV21">
-        <v>0.07968447279999998</v>
-      </c>
-      <c r="AW21">
-        <v>0.06830097668571426</v>
-      </c>
-      <c r="AX21">
-        <v>0.05691748057142858</v>
-      </c>
-      <c r="AY21">
-        <v>0.04553398445714287</v>
-      </c>
-      <c r="AZ21">
-        <v>0.03415048834285715</v>
-      </c>
-      <c r="BA21">
-        <v>0.02276699222857144</v>
-      </c>
-      <c r="BB21">
-        <v>0.01138349611428572</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:55">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="S22">
-        <v>1</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22">
-        <v>0.9871428571428571</v>
-      </c>
-      <c r="V22">
-        <v>0.9742857142857143</v>
-      </c>
-      <c r="W22">
-        <v>0.9614285714285714</v>
-      </c>
-      <c r="X22">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="Y22">
-        <v>0.9357142857142857</v>
-      </c>
-      <c r="Z22">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AA22">
-        <v>0.91</v>
-      </c>
-      <c r="AB22">
-        <v>0.8971428571428572</v>
-      </c>
-      <c r="AC22">
-        <v>0.8842857142857143</v>
-      </c>
-      <c r="AD22">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AE22">
-        <v>0.8585714285714285</v>
-      </c>
-      <c r="AF22">
-        <v>0.8457142857142858</v>
-      </c>
-      <c r="AG22">
-        <v>0.8328571428571429</v>
-      </c>
-      <c r="AH22">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AI22">
-        <v>0.8071428571428572</v>
-      </c>
-      <c r="AJ22">
-        <v>0.7942857142857144</v>
-      </c>
-      <c r="AK22">
-        <v>0.7814285714285714</v>
-      </c>
-      <c r="AL22">
-        <v>0.7685714285714287</v>
-      </c>
-      <c r="AM22">
-        <v>0.7557142857142858</v>
-      </c>
-      <c r="AN22">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AO22">
-        <v>0.73</v>
-      </c>
-      <c r="AP22">
-        <v>0.7171428571428572</v>
-      </c>
-      <c r="AQ22">
-        <v>0.7042857142857143</v>
-      </c>
-      <c r="AR22">
-        <v>0.6914285714285715</v>
-      </c>
-      <c r="AS22">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="AT22">
-        <v>0.6657142857142857</v>
-      </c>
-      <c r="AU22">
-        <v>0.6528571428571428</v>
-      </c>
-      <c r="AV22">
-        <v>0.64</v>
-      </c>
-      <c r="AW22">
-        <v>0.6271428571428572</v>
-      </c>
-      <c r="AX22">
-        <v>0.6142857142857143</v>
-      </c>
-      <c r="AY22">
-        <v>0.6014285714285714</v>
-      </c>
-      <c r="AZ22">
-        <v>0.5885714285714286</v>
-      </c>
-      <c r="BA22">
-        <v>0.5757142857142857</v>
-      </c>
-      <c r="BB22">
-        <v>0.5628571428571429</v>
-      </c>
-      <c r="BC22">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:55">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>0.02</v>
-      </c>
-      <c r="K23">
-        <v>0.02</v>
-      </c>
-      <c r="L23">
-        <v>0.02</v>
-      </c>
-      <c r="M23">
-        <v>0.02</v>
-      </c>
-      <c r="N23">
-        <v>0.02</v>
-      </c>
-      <c r="O23">
-        <v>0.02</v>
-      </c>
-      <c r="P23">
-        <v>0.02</v>
-      </c>
-      <c r="Q23">
-        <v>0.02</v>
-      </c>
-      <c r="R23">
-        <v>0.02</v>
-      </c>
-      <c r="S23">
-        <v>0.02</v>
-      </c>
-      <c r="T23">
-        <v>0.02</v>
-      </c>
-      <c r="U23">
-        <v>0.033</v>
-      </c>
-      <c r="V23">
-        <v>0.046</v>
-      </c>
-      <c r="W23">
-        <v>0.059</v>
-      </c>
-      <c r="X23">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="Y23">
-        <v>0.08499999999999999</v>
-      </c>
-      <c r="Z23">
-        <v>0.09799999999999999</v>
-      </c>
-      <c r="AA23">
-        <v>0.111</v>
-      </c>
-      <c r="AB23">
-        <v>0.124</v>
-      </c>
-      <c r="AC23">
-        <v>0.137</v>
-      </c>
-      <c r="AD23">
-        <v>0.15</v>
-      </c>
-      <c r="AE23">
-        <v>0.163</v>
-      </c>
-      <c r="AF23">
-        <v>0.176</v>
-      </c>
-      <c r="AG23">
-        <v>0.189</v>
-      </c>
-      <c r="AH23">
-        <v>0.202</v>
-      </c>
-      <c r="AI23">
-        <v>0.215</v>
-      </c>
-      <c r="AJ23">
-        <v>0.228</v>
-      </c>
-      <c r="AK23">
-        <v>0.241</v>
-      </c>
-      <c r="AL23">
-        <v>0.2539999999999999</v>
-      </c>
-      <c r="AM23">
-        <v>0.267</v>
-      </c>
-      <c r="AN23">
-        <v>0.28</v>
-      </c>
-      <c r="AO23">
-        <v>0.293</v>
-      </c>
-      <c r="AP23">
-        <v>0.306</v>
-      </c>
-      <c r="AQ23">
-        <v>0.319</v>
-      </c>
-      <c r="AR23">
-        <v>0.332</v>
-      </c>
-      <c r="AS23">
-        <v>0.345</v>
-      </c>
-      <c r="AT23">
-        <v>0.358</v>
-      </c>
-      <c r="AU23">
-        <v>0.371</v>
-      </c>
-      <c r="AV23">
-        <v>0.384</v>
-      </c>
-      <c r="AW23">
-        <v>0.397</v>
-      </c>
-      <c r="AX23">
-        <v>0.4099999999999999</v>
-      </c>
-      <c r="AY23">
-        <v>0.4229999999999999</v>
-      </c>
-      <c r="AZ23">
-        <v>0.436</v>
-      </c>
-      <c r="BA23">
-        <v>0.449</v>
-      </c>
-      <c r="BB23">
-        <v>0.462</v>
-      </c>
-      <c r="BC23">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="24" spans="1:55">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>157</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>0.4</v>
-      </c>
-      <c r="K24">
-        <v>0.4</v>
-      </c>
-      <c r="L24">
-        <v>0.4</v>
-      </c>
-      <c r="M24">
-        <v>0.4</v>
-      </c>
-      <c r="N24">
-        <v>0.4</v>
-      </c>
-      <c r="O24">
-        <v>0.4</v>
-      </c>
-      <c r="P24">
-        <v>0.4</v>
-      </c>
-      <c r="Q24">
-        <v>0.4</v>
-      </c>
-      <c r="R24">
-        <v>0.4</v>
-      </c>
-      <c r="S24">
-        <v>0.4</v>
-      </c>
-      <c r="T24">
-        <v>0.4</v>
-      </c>
-      <c r="U24">
-        <v>0.4021428571428571</v>
-      </c>
-      <c r="V24">
-        <v>0.4042857142857143</v>
-      </c>
-      <c r="W24">
-        <v>0.4064285714285714</v>
-      </c>
-      <c r="X24">
-        <v>0.4085714285714286</v>
-      </c>
-      <c r="Y24">
-        <v>0.4107142857142858</v>
-      </c>
-      <c r="Z24">
-        <v>0.4128571428571428</v>
-      </c>
-      <c r="AA24">
-        <v>0.415</v>
-      </c>
-      <c r="AB24">
-        <v>0.4171428571428571</v>
-      </c>
-      <c r="AC24">
-        <v>0.4192857142857143</v>
-      </c>
-      <c r="AD24">
-        <v>0.4214285714285715</v>
-      </c>
-      <c r="AE24">
-        <v>0.4235714285714286</v>
-      </c>
-      <c r="AF24">
-        <v>0.4257142857142857</v>
-      </c>
-      <c r="AG24">
-        <v>0.4278571428571429</v>
-      </c>
-      <c r="AH24">
-        <v>0.43</v>
-      </c>
-      <c r="AI24">
-        <v>0.4321428571428571</v>
-      </c>
-      <c r="AJ24">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="AK24">
-        <v>0.4364285714285714</v>
-      </c>
-      <c r="AL24">
-        <v>0.4385714285714286</v>
-      </c>
-      <c r="AM24">
-        <v>0.4407142857142857</v>
-      </c>
-      <c r="AN24">
-        <v>0.4428571428571428</v>
-      </c>
-      <c r="AO24">
-        <v>0.445</v>
-      </c>
-      <c r="AP24">
-        <v>0.4471428571428571</v>
-      </c>
-      <c r="AQ24">
-        <v>0.4492857142857143</v>
-      </c>
-      <c r="AR24">
-        <v>0.4514285714285714</v>
-      </c>
-      <c r="AS24">
-        <v>0.4535714285714286</v>
-      </c>
-      <c r="AT24">
-        <v>0.4557142857142857</v>
-      </c>
-      <c r="AU24">
-        <v>0.4578571428571429</v>
-      </c>
-      <c r="AV24">
-        <v>0.46</v>
-      </c>
-      <c r="AW24">
-        <v>0.4621428571428571</v>
-      </c>
-      <c r="AX24">
-        <v>0.4642857142857142</v>
-      </c>
-      <c r="AY24">
-        <v>0.4664285714285714</v>
-      </c>
-      <c r="AZ24">
-        <v>0.4685714285714286</v>
-      </c>
-      <c r="BA24">
-        <v>0.4707142857142857</v>
-      </c>
-      <c r="BB24">
-        <v>0.4728571428571429</v>
-      </c>
-      <c r="BC24">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="25" spans="1:55">
-      <c r="A25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>0.02</v>
-      </c>
-      <c r="K25">
-        <v>0.02</v>
-      </c>
-      <c r="L25">
-        <v>0.02</v>
-      </c>
-      <c r="M25">
-        <v>0.02</v>
-      </c>
-      <c r="N25">
-        <v>0.02</v>
-      </c>
-      <c r="O25">
-        <v>0.02</v>
-      </c>
-      <c r="P25">
-        <v>0.02</v>
-      </c>
-      <c r="Q25">
-        <v>0.02</v>
-      </c>
-      <c r="R25">
-        <v>0.02</v>
-      </c>
-      <c r="S25">
-        <v>0.02</v>
-      </c>
-      <c r="T25">
-        <v>0.02</v>
-      </c>
-      <c r="U25">
-        <v>0.033</v>
-      </c>
-      <c r="V25">
-        <v>0.046</v>
-      </c>
-      <c r="W25">
-        <v>0.059</v>
-      </c>
-      <c r="X25">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="Y25">
-        <v>0.08499999999999999</v>
-      </c>
-      <c r="Z25">
-        <v>0.09799999999999999</v>
-      </c>
-      <c r="AA25">
-        <v>0.111</v>
-      </c>
-      <c r="AB25">
-        <v>0.124</v>
-      </c>
-      <c r="AC25">
-        <v>0.137</v>
-      </c>
-      <c r="AD25">
-        <v>0.15</v>
-      </c>
-      <c r="AE25">
-        <v>0.163</v>
-      </c>
-      <c r="AF25">
-        <v>0.176</v>
-      </c>
-      <c r="AG25">
-        <v>0.189</v>
-      </c>
-      <c r="AH25">
-        <v>0.202</v>
-      </c>
-      <c r="AI25">
-        <v>0.215</v>
-      </c>
-      <c r="AJ25">
-        <v>0.228</v>
-      </c>
-      <c r="AK25">
-        <v>0.241</v>
-      </c>
-      <c r="AL25">
-        <v>0.2539999999999999</v>
-      </c>
-      <c r="AM25">
-        <v>0.267</v>
-      </c>
-      <c r="AN25">
-        <v>0.28</v>
-      </c>
-      <c r="AO25">
-        <v>0.293</v>
-      </c>
-      <c r="AP25">
-        <v>0.306</v>
-      </c>
-      <c r="AQ25">
-        <v>0.319</v>
-      </c>
-      <c r="AR25">
-        <v>0.332</v>
-      </c>
-      <c r="AS25">
-        <v>0.345</v>
-      </c>
-      <c r="AT25">
-        <v>0.358</v>
-      </c>
-      <c r="AU25">
-        <v>0.371</v>
-      </c>
-      <c r="AV25">
-        <v>0.384</v>
-      </c>
-      <c r="AW25">
-        <v>0.397</v>
-      </c>
-      <c r="AX25">
-        <v>0.4099999999999999</v>
-      </c>
-      <c r="AY25">
-        <v>0.4229999999999999</v>
-      </c>
-      <c r="AZ25">
-        <v>0.436</v>
-      </c>
-      <c r="BA25">
-        <v>0.449</v>
-      </c>
-      <c r="BB25">
-        <v>0.462</v>
-      </c>
-      <c r="BC25">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="26" spans="1:55">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" t="s">
-        <v>159</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>0.015196443</v>
-      </c>
-      <c r="K26">
-        <v>0.015196443</v>
-      </c>
-      <c r="L26">
-        <v>0.015196443</v>
-      </c>
-      <c r="M26">
-        <v>0.015196443</v>
-      </c>
-      <c r="N26">
-        <v>0.015196443</v>
-      </c>
-      <c r="O26">
-        <v>0.015196443</v>
-      </c>
-      <c r="P26">
-        <v>0.015196443</v>
-      </c>
-      <c r="Q26">
-        <v>0.015196443</v>
-      </c>
-      <c r="R26">
-        <v>0.015196443</v>
-      </c>
-      <c r="S26">
-        <v>0.015196443</v>
-      </c>
-      <c r="T26">
-        <v>0.015196443</v>
-      </c>
-      <c r="U26">
-        <v>0.02833368748571428</v>
-      </c>
-      <c r="V26">
-        <v>0.04147093197142857</v>
-      </c>
-      <c r="W26">
-        <v>0.05460817645714285</v>
-      </c>
-      <c r="X26">
-        <v>0.06774542094285714</v>
-      </c>
-      <c r="Y26">
-        <v>0.08088266542857142</v>
-      </c>
-      <c r="Z26">
-        <v>0.0940199099142857</v>
-      </c>
-      <c r="AA26">
-        <v>0.1071571544</v>
-      </c>
-      <c r="AB26">
-        <v>0.1202943988857143</v>
-      </c>
-      <c r="AC26">
-        <v>0.1334316433714285</v>
-      </c>
-      <c r="AD26">
-        <v>0.1465688878571428</v>
-      </c>
-      <c r="AE26">
-        <v>0.1597061323428571</v>
-      </c>
-      <c r="AF26">
-        <v>0.1728433768285714</v>
-      </c>
-      <c r="AG26">
-        <v>0.1859806213142857</v>
-      </c>
-      <c r="AH26">
-        <v>0.1991178658</v>
-      </c>
-      <c r="AI26">
-        <v>0.2122551102857143</v>
-      </c>
-      <c r="AJ26">
-        <v>0.2253923547714286</v>
-      </c>
-      <c r="AK26">
-        <v>0.2385295992571428</v>
-      </c>
-      <c r="AL26">
-        <v>0.2516668437428571</v>
-      </c>
-      <c r="AM26">
-        <v>0.2648040882285714</v>
-      </c>
-      <c r="AN26">
-        <v>0.2779413327142857</v>
-      </c>
-      <c r="AO26">
-        <v>0.2910785772</v>
-      </c>
-      <c r="AP26">
-        <v>0.3042158216857143</v>
-      </c>
-      <c r="AQ26">
-        <v>0.3173530661714286</v>
-      </c>
-      <c r="AR26">
-        <v>0.3304903106571428</v>
-      </c>
-      <c r="AS26">
-        <v>0.3436275551428571</v>
-      </c>
-      <c r="AT26">
-        <v>0.3567647996285714</v>
-      </c>
-      <c r="AU26">
-        <v>0.3699020441142857</v>
-      </c>
-      <c r="AV26">
-        <v>0.3830392886</v>
-      </c>
-      <c r="AW26">
-        <v>0.3961765330857143</v>
-      </c>
-      <c r="AX26">
-        <v>0.4093137775714285</v>
-      </c>
-      <c r="AY26">
-        <v>0.4224510220571428</v>
-      </c>
-      <c r="AZ26">
-        <v>0.4355882665428571</v>
-      </c>
-      <c r="BA26">
-        <v>0.4487255110285714</v>
-      </c>
-      <c r="BB26">
-        <v>0.4618627555142857</v>
-      </c>
-      <c r="BC26">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="27" spans="1:55">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>0.015196443</v>
-      </c>
-      <c r="K27">
-        <v>0.015196443</v>
-      </c>
-      <c r="L27">
-        <v>0.015196443</v>
-      </c>
-      <c r="M27">
-        <v>0.015196443</v>
-      </c>
-      <c r="N27">
-        <v>0.015196443</v>
-      </c>
-      <c r="O27">
-        <v>0.015196443</v>
-      </c>
-      <c r="P27">
-        <v>0.015196443</v>
-      </c>
-      <c r="Q27">
-        <v>0.015196443</v>
-      </c>
-      <c r="R27">
-        <v>0.015196443</v>
-      </c>
-      <c r="S27">
-        <v>0.015196443</v>
-      </c>
-      <c r="T27">
-        <v>0.015196443</v>
-      </c>
-      <c r="U27">
-        <v>0.02833368748571428</v>
-      </c>
-      <c r="V27">
-        <v>0.04147093197142857</v>
-      </c>
-      <c r="W27">
-        <v>0.05460817645714285</v>
-      </c>
-      <c r="X27">
-        <v>0.06774542094285714</v>
-      </c>
-      <c r="Y27">
-        <v>0.08088266542857142</v>
-      </c>
-      <c r="Z27">
-        <v>0.0940199099142857</v>
-      </c>
-      <c r="AA27">
-        <v>0.1071571544</v>
-      </c>
-      <c r="AB27">
-        <v>0.1202943988857143</v>
-      </c>
-      <c r="AC27">
-        <v>0.1334316433714285</v>
-      </c>
-      <c r="AD27">
-        <v>0.1465688878571428</v>
-      </c>
-      <c r="AE27">
-        <v>0.1597061323428571</v>
-      </c>
-      <c r="AF27">
-        <v>0.1728433768285714</v>
-      </c>
-      <c r="AG27">
-        <v>0.1859806213142857</v>
-      </c>
-      <c r="AH27">
-        <v>0.1991178658</v>
-      </c>
-      <c r="AI27">
-        <v>0.2122551102857143</v>
-      </c>
-      <c r="AJ27">
-        <v>0.2253923547714286</v>
-      </c>
-      <c r="AK27">
-        <v>0.2385295992571428</v>
-      </c>
-      <c r="AL27">
-        <v>0.2516668437428571</v>
-      </c>
-      <c r="AM27">
-        <v>0.2648040882285714</v>
-      </c>
-      <c r="AN27">
-        <v>0.2779413327142857</v>
-      </c>
-      <c r="AO27">
-        <v>0.2910785772</v>
-      </c>
-      <c r="AP27">
-        <v>0.3042158216857143</v>
-      </c>
-      <c r="AQ27">
-        <v>0.3173530661714286</v>
-      </c>
-      <c r="AR27">
-        <v>0.3304903106571428</v>
-      </c>
-      <c r="AS27">
-        <v>0.3436275551428571</v>
-      </c>
-      <c r="AT27">
-        <v>0.3567647996285714</v>
-      </c>
-      <c r="AU27">
-        <v>0.3699020441142857</v>
-      </c>
-      <c r="AV27">
-        <v>0.3830392886</v>
-      </c>
-      <c r="AW27">
-        <v>0.3961765330857143</v>
-      </c>
-      <c r="AX27">
-        <v>0.4093137775714285</v>
-      </c>
-      <c r="AY27">
-        <v>0.4224510220571428</v>
-      </c>
-      <c r="AZ27">
-        <v>0.4355882665428571</v>
-      </c>
-      <c r="BA27">
-        <v>0.4487255110285714</v>
-      </c>
-      <c r="BB27">
-        <v>0.4618627555142857</v>
-      </c>
-      <c r="BC27">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="28" spans="1:55">
-      <c r="A28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" t="s">
-        <v>162</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>0.015196443</v>
-      </c>
-      <c r="K28">
-        <v>0.015196443</v>
-      </c>
-      <c r="L28">
-        <v>0.015196443</v>
-      </c>
-      <c r="M28">
-        <v>0.015196443</v>
-      </c>
-      <c r="N28">
-        <v>0.015196443</v>
-      </c>
-      <c r="O28">
-        <v>0.015196443</v>
-      </c>
-      <c r="P28">
-        <v>0.015196443</v>
-      </c>
-      <c r="Q28">
-        <v>0.015196443</v>
-      </c>
-      <c r="R28">
-        <v>0.015196443</v>
-      </c>
-      <c r="S28">
-        <v>0.015196443</v>
-      </c>
-      <c r="T28">
-        <v>0.015196443</v>
-      </c>
-      <c r="U28">
-        <v>0.02833368748571428</v>
-      </c>
-      <c r="V28">
-        <v>0.04147093197142857</v>
-      </c>
-      <c r="W28">
-        <v>0.05460817645714285</v>
-      </c>
-      <c r="X28">
-        <v>0.06774542094285714</v>
-      </c>
-      <c r="Y28">
-        <v>0.08088266542857142</v>
-      </c>
-      <c r="Z28">
-        <v>0.0940199099142857</v>
-      </c>
-      <c r="AA28">
-        <v>0.1071571544</v>
-      </c>
-      <c r="AB28">
-        <v>0.1202943988857143</v>
-      </c>
-      <c r="AC28">
-        <v>0.1334316433714285</v>
-      </c>
-      <c r="AD28">
-        <v>0.1465688878571428</v>
-      </c>
-      <c r="AE28">
-        <v>0.1597061323428571</v>
-      </c>
-      <c r="AF28">
-        <v>0.1728433768285714</v>
-      </c>
-      <c r="AG28">
-        <v>0.1859806213142857</v>
-      </c>
-      <c r="AH28">
-        <v>0.1991178658</v>
-      </c>
-      <c r="AI28">
-        <v>0.2122551102857143</v>
-      </c>
-      <c r="AJ28">
-        <v>0.2253923547714286</v>
-      </c>
-      <c r="AK28">
-        <v>0.2385295992571428</v>
-      </c>
-      <c r="AL28">
-        <v>0.2516668437428571</v>
-      </c>
-      <c r="AM28">
-        <v>0.2648040882285714</v>
-      </c>
-      <c r="AN28">
-        <v>0.2779413327142857</v>
-      </c>
-      <c r="AO28">
-        <v>0.2910785772</v>
-      </c>
-      <c r="AP28">
-        <v>0.3042158216857143</v>
-      </c>
-      <c r="AQ28">
-        <v>0.3173530661714286</v>
-      </c>
-      <c r="AR28">
-        <v>0.3304903106571428</v>
-      </c>
-      <c r="AS28">
-        <v>0.3436275551428571</v>
-      </c>
-      <c r="AT28">
-        <v>0.3567647996285714</v>
-      </c>
-      <c r="AU28">
-        <v>0.3699020441142857</v>
-      </c>
-      <c r="AV28">
-        <v>0.3830392886</v>
-      </c>
-      <c r="AW28">
-        <v>0.3961765330857143</v>
-      </c>
-      <c r="AX28">
-        <v>0.4093137775714285</v>
-      </c>
-      <c r="AY28">
-        <v>0.4224510220571428</v>
-      </c>
-      <c r="AZ28">
-        <v>0.4355882665428571</v>
-      </c>
-      <c r="BA28">
-        <v>0.4487255110285714</v>
-      </c>
-      <c r="BB28">
-        <v>0.4618627555142857</v>
-      </c>
-      <c r="BC28">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="29" spans="1:55">
-      <c r="A29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" t="s">
-        <v>189</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>0.048754849</v>
-      </c>
-      <c r="K29">
-        <v>0.048754849</v>
-      </c>
-      <c r="L29">
-        <v>0.048754849</v>
-      </c>
-      <c r="M29">
-        <v>0.048754849</v>
-      </c>
-      <c r="N29">
-        <v>0.048754849</v>
-      </c>
-      <c r="O29">
-        <v>0.048754849</v>
-      </c>
-      <c r="P29">
-        <v>0.048754849</v>
-      </c>
-      <c r="Q29">
-        <v>0.048754849</v>
-      </c>
-      <c r="R29">
-        <v>0.048754849</v>
-      </c>
-      <c r="S29">
-        <v>0.048754849</v>
-      </c>
-      <c r="T29">
-        <v>0.048754849</v>
-      </c>
-      <c r="U29">
-        <v>0.0716475676</v>
-      </c>
-      <c r="V29">
-        <v>0.0945402862</v>
-      </c>
-      <c r="W29">
-        <v>0.1174330048</v>
-      </c>
-      <c r="X29">
-        <v>0.1403257234</v>
-      </c>
-      <c r="Y29">
-        <v>0.163218442</v>
-      </c>
-      <c r="Z29">
-        <v>0.1861111606</v>
-      </c>
-      <c r="AA29">
-        <v>0.2090038792</v>
-      </c>
-      <c r="AB29">
-        <v>0.2318965978</v>
-      </c>
-      <c r="AC29">
-        <v>0.2547893164</v>
-      </c>
-      <c r="AD29">
-        <v>0.277682035</v>
-      </c>
-      <c r="AE29">
-        <v>0.3005747536</v>
-      </c>
-      <c r="AF29">
-        <v>0.3234674722</v>
-      </c>
-      <c r="AG29">
-        <v>0.3463601908</v>
-      </c>
-      <c r="AH29">
-        <v>0.3692529094</v>
-      </c>
-      <c r="AI29">
-        <v>0.392145628</v>
-      </c>
-      <c r="AJ29">
-        <v>0.4150383466</v>
-      </c>
-      <c r="AK29">
-        <v>0.4379310652</v>
-      </c>
-      <c r="AL29">
-        <v>0.4608237838</v>
-      </c>
-      <c r="AM29">
-        <v>0.4837165023999999</v>
-      </c>
-      <c r="AN29">
-        <v>0.5066092209999999</v>
-      </c>
-      <c r="AO29">
-        <v>0.5295019396</v>
-      </c>
-      <c r="AP29">
-        <v>0.5523946582</v>
-      </c>
-      <c r="AQ29">
-        <v>0.5752873768000001</v>
-      </c>
-      <c r="AR29">
-        <v>0.5981800953999999</v>
-      </c>
-      <c r="AS29">
-        <v>0.6210728139999999</v>
-      </c>
-      <c r="AT29">
-        <v>0.6439655326</v>
-      </c>
-      <c r="AU29">
-        <v>0.6668582512</v>
-      </c>
-      <c r="AV29">
-        <v>0.6897509698000001</v>
-      </c>
-      <c r="AW29">
-        <v>0.7126436884</v>
-      </c>
-      <c r="AX29">
-        <v>0.735536407</v>
-      </c>
-      <c r="AY29">
-        <v>0.7584291256</v>
-      </c>
-      <c r="AZ29">
-        <v>0.7813218441999999</v>
-      </c>
-      <c r="BA29">
-        <v>0.8042145627999999</v>
-      </c>
-      <c r="BB29">
-        <v>0.8271072814</v>
-      </c>
-      <c r="BC29">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:55">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" t="s">
-        <v>190</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>0.745</v>
-      </c>
-      <c r="K30">
-        <v>0.745</v>
-      </c>
-      <c r="L30">
-        <v>0.745</v>
-      </c>
-      <c r="M30">
-        <v>0.745</v>
-      </c>
-      <c r="N30">
-        <v>0.745</v>
-      </c>
-      <c r="O30">
-        <v>0.745</v>
-      </c>
-      <c r="P30">
-        <v>0.745</v>
-      </c>
-      <c r="Q30">
-        <v>0.745</v>
-      </c>
-      <c r="R30">
-        <v>0.745</v>
-      </c>
-      <c r="S30">
-        <v>0.745</v>
-      </c>
-      <c r="T30">
-        <v>0.745</v>
-      </c>
-      <c r="U30">
-        <v>0.748</v>
-      </c>
-      <c r="V30">
-        <v>0.751</v>
-      </c>
-      <c r="W30">
-        <v>0.754</v>
-      </c>
-      <c r="X30">
-        <v>0.7569999999999999</v>
-      </c>
-      <c r="Y30">
-        <v>0.76</v>
-      </c>
-      <c r="Z30">
-        <v>0.7629999999999999</v>
-      </c>
-      <c r="AA30">
-        <v>0.766</v>
-      </c>
-      <c r="AB30">
-        <v>0.769</v>
-      </c>
-      <c r="AC30">
-        <v>0.772</v>
-      </c>
-      <c r="AD30">
-        <v>0.7749999999999999</v>
-      </c>
-      <c r="AE30">
-        <v>0.778</v>
-      </c>
-      <c r="AF30">
-        <v>0.7809999999999999</v>
-      </c>
-      <c r="AG30">
-        <v>0.784</v>
-      </c>
-      <c r="AH30">
-        <v>0.787</v>
-      </c>
-      <c r="AI30">
-        <v>0.79</v>
-      </c>
-      <c r="AJ30">
-        <v>0.793</v>
-      </c>
-      <c r="AK30">
-        <v>0.796</v>
-      </c>
-      <c r="AL30">
-        <v>0.7989999999999999</v>
-      </c>
-      <c r="AM30">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AN30">
-        <v>0.8049999999999999</v>
-      </c>
-      <c r="AO30">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="AP30">
-        <v>0.8109999999999999</v>
-      </c>
-      <c r="AQ30">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AR30">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="AS30">
-        <v>0.82</v>
-      </c>
-      <c r="AT30">
-        <v>0.823</v>
-      </c>
-      <c r="AU30">
-        <v>0.826</v>
-      </c>
-      <c r="AV30">
-        <v>0.829</v>
-      </c>
-      <c r="AW30">
-        <v>0.832</v>
-      </c>
-      <c r="AX30">
-        <v>0.835</v>
-      </c>
-      <c r="AY30">
-        <v>0.838</v>
-      </c>
-      <c r="AZ30">
-        <v>0.841</v>
-      </c>
-      <c r="BA30">
-        <v>0.844</v>
-      </c>
-      <c r="BB30">
-        <v>0.847</v>
-      </c>
-      <c r="BC30">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" t="s">
-        <v>191</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0.02428571428571429</v>
-      </c>
-      <c r="V31">
-        <v>0.04857142857142857</v>
-      </c>
-      <c r="W31">
-        <v>0.07285714285714286</v>
-      </c>
-      <c r="X31">
-        <v>0.09714285714285714</v>
-      </c>
-      <c r="Y31">
-        <v>0.1214285714285714</v>
-      </c>
-      <c r="Z31">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AA31">
-        <v>0.17</v>
-      </c>
-      <c r="AB31">
-        <v>0.1942857142857143</v>
-      </c>
-      <c r="AC31">
-        <v>0.2185714285714286</v>
-      </c>
-      <c r="AD31">
-        <v>0.2428571428571428</v>
-      </c>
-      <c r="AE31">
-        <v>0.2671428571428571</v>
-      </c>
-      <c r="AF31">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="AG31">
-        <v>0.3157142857142857</v>
-      </c>
-      <c r="AH31">
-        <v>0.34</v>
-      </c>
-      <c r="AI31">
-        <v>0.3642857142857143</v>
-      </c>
-      <c r="AJ31">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AK31">
-        <v>0.4128571428571429</v>
-      </c>
-      <c r="AL31">
-        <v>0.4371428571428571</v>
-      </c>
-      <c r="AM31">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AN31">
-        <v>0.4857142857142857</v>
-      </c>
-      <c r="AO31">
-        <v>0.51</v>
-      </c>
-      <c r="AP31">
-        <v>0.5342857142857143</v>
-      </c>
-      <c r="AQ31">
-        <v>0.5585714285714286</v>
-      </c>
-      <c r="AR31">
-        <v>0.5828571428571429</v>
-      </c>
-      <c r="AS31">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="AT31">
-        <v>0.6314285714285715</v>
-      </c>
-      <c r="AU31">
-        <v>0.6557142857142857</v>
-      </c>
-      <c r="AV31">
-        <v>0.68</v>
-      </c>
-      <c r="AW31">
-        <v>0.7042857142857143</v>
-      </c>
-      <c r="AX31">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="AY31">
-        <v>0.7528571428571428</v>
-      </c>
-      <c r="AZ31">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BA31">
-        <v>0.8014285714285714</v>
-      </c>
-      <c r="BB31">
-        <v>0.8257142857142857</v>
-      </c>
-      <c r="BC31">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:55">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>192</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>0.048754849</v>
-      </c>
-      <c r="K32">
-        <v>0.048754849</v>
-      </c>
-      <c r="L32">
-        <v>0.048754849</v>
-      </c>
-      <c r="M32">
-        <v>0.048754849</v>
-      </c>
-      <c r="N32">
-        <v>0.048754849</v>
-      </c>
-      <c r="O32">
-        <v>0.048754849</v>
-      </c>
-      <c r="P32">
-        <v>0.048754849</v>
-      </c>
-      <c r="Q32">
-        <v>0.048754849</v>
-      </c>
-      <c r="R32">
-        <v>0.048754849</v>
-      </c>
-      <c r="S32">
-        <v>0.048754849</v>
-      </c>
-      <c r="T32">
-        <v>0.048754849</v>
-      </c>
-      <c r="U32">
-        <v>0.0716475676</v>
-      </c>
-      <c r="V32">
-        <v>0.0945402862</v>
-      </c>
-      <c r="W32">
-        <v>0.1174330048</v>
-      </c>
-      <c r="X32">
-        <v>0.1403257234</v>
-      </c>
-      <c r="Y32">
-        <v>0.163218442</v>
-      </c>
-      <c r="Z32">
-        <v>0.1861111606</v>
-      </c>
-      <c r="AA32">
-        <v>0.2090038792</v>
-      </c>
-      <c r="AB32">
-        <v>0.2318965978</v>
-      </c>
-      <c r="AC32">
-        <v>0.2547893164</v>
-      </c>
-      <c r="AD32">
-        <v>0.277682035</v>
-      </c>
-      <c r="AE32">
-        <v>0.3005747536</v>
-      </c>
-      <c r="AF32">
-        <v>0.3234674722</v>
-      </c>
-      <c r="AG32">
-        <v>0.3463601908</v>
-      </c>
-      <c r="AH32">
-        <v>0.3692529094</v>
-      </c>
-      <c r="AI32">
-        <v>0.392145628</v>
-      </c>
-      <c r="AJ32">
-        <v>0.4150383466</v>
-      </c>
-      <c r="AK32">
-        <v>0.4379310652</v>
-      </c>
-      <c r="AL32">
-        <v>0.4608237838</v>
-      </c>
-      <c r="AM32">
-        <v>0.4837165023999999</v>
-      </c>
-      <c r="AN32">
-        <v>0.5066092209999999</v>
-      </c>
-      <c r="AO32">
-        <v>0.5295019396</v>
-      </c>
-      <c r="AP32">
-        <v>0.5523946582</v>
-      </c>
-      <c r="AQ32">
-        <v>0.5752873768000001</v>
-      </c>
-      <c r="AR32">
-        <v>0.5981800953999999</v>
-      </c>
-      <c r="AS32">
-        <v>0.6210728139999999</v>
-      </c>
-      <c r="AT32">
-        <v>0.6439655326</v>
-      </c>
-      <c r="AU32">
-        <v>0.6668582512</v>
-      </c>
-      <c r="AV32">
-        <v>0.6897509698000001</v>
-      </c>
-      <c r="AW32">
-        <v>0.7126436884</v>
-      </c>
-      <c r="AX32">
-        <v>0.735536407</v>
-      </c>
-      <c r="AY32">
-        <v>0.7584291256</v>
-      </c>
-      <c r="AZ32">
-        <v>0.7813218441999999</v>
-      </c>
-      <c r="BA32">
-        <v>0.8042145627999999</v>
-      </c>
-      <c r="BB32">
-        <v>0.8271072814</v>
-      </c>
-      <c r="BC32">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:55">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33">
-        <v>63</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0.0144881164</v>
-      </c>
-      <c r="V33">
-        <v>0.0289762328</v>
-      </c>
-      <c r="W33">
-        <v>0.0434643492</v>
-      </c>
-      <c r="X33">
-        <v>0.0579524656</v>
-      </c>
-      <c r="Y33">
-        <v>0.07244058199999999</v>
-      </c>
-      <c r="Z33">
-        <v>0.0869286984</v>
-      </c>
-      <c r="AA33">
-        <v>0.1014168148</v>
-      </c>
-      <c r="AB33">
-        <v>0.1159049312</v>
-      </c>
-      <c r="AC33">
-        <v>0.1303930476</v>
-      </c>
-      <c r="AD33">
-        <v>0.144881164</v>
-      </c>
-      <c r="AE33">
-        <v>0.1593692804</v>
-      </c>
-      <c r="AF33">
-        <v>0.1738573968</v>
-      </c>
-      <c r="AG33">
-        <v>0.1883455132</v>
-      </c>
-      <c r="AH33">
-        <v>0.2028336296</v>
-      </c>
-      <c r="AI33">
-        <v>0.217321746</v>
-      </c>
-      <c r="AJ33">
-        <v>0.2318098624</v>
-      </c>
-      <c r="AK33">
-        <v>0.2462979788</v>
-      </c>
-      <c r="AL33">
-        <v>0.2607860952</v>
-      </c>
-      <c r="AM33">
-        <v>0.2752742116</v>
-      </c>
-      <c r="AN33">
-        <v>0.289762328</v>
-      </c>
-      <c r="AO33">
-        <v>0.3042504444</v>
-      </c>
-      <c r="AP33">
-        <v>0.3187385608</v>
-      </c>
-      <c r="AQ33">
-        <v>0.3332266772</v>
-      </c>
-      <c r="AR33">
-        <v>0.3477147936</v>
-      </c>
-      <c r="AS33">
-        <v>0.36220291</v>
-      </c>
-      <c r="AT33">
-        <v>0.3766910264</v>
-      </c>
-      <c r="AU33">
-        <v>0.3911791428</v>
-      </c>
-      <c r="AV33">
-        <v>0.4056672592</v>
-      </c>
-      <c r="AW33">
-        <v>0.4201553756</v>
-      </c>
-      <c r="AX33">
-        <v>0.434643492</v>
-      </c>
-      <c r="AY33">
-        <v>0.4491316084</v>
-      </c>
-      <c r="AZ33">
-        <v>0.4636197248</v>
-      </c>
-      <c r="BA33">
-        <v>0.4781078412</v>
-      </c>
-      <c r="BB33">
-        <v>0.4925959576</v>
-      </c>
-      <c r="BC33">
-        <v>0.507084074</v>
-      </c>
-    </row>
-    <row r="34" spans="1:55">
-      <c r="A34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" t="s">
-        <v>195</v>
-      </c>
-      <c r="C34">
-        <v>63</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>0.507084074</v>
-      </c>
-      <c r="K34">
-        <v>0.507084074</v>
-      </c>
-      <c r="L34">
-        <v>0.507084074</v>
-      </c>
-      <c r="M34">
-        <v>0.507084074</v>
-      </c>
-      <c r="N34">
-        <v>0.507084074</v>
-      </c>
-      <c r="O34">
-        <v>0.507084074</v>
-      </c>
-      <c r="P34">
-        <v>0.507084074</v>
-      </c>
-      <c r="Q34">
-        <v>0.507084074</v>
-      </c>
-      <c r="R34">
-        <v>0.507084074</v>
-      </c>
-      <c r="S34">
-        <v>0.507084074</v>
-      </c>
-      <c r="T34">
-        <v>0.507084074</v>
-      </c>
-      <c r="U34">
-        <v>0.4925959576</v>
-      </c>
-      <c r="V34">
-        <v>0.4781078412</v>
-      </c>
-      <c r="W34">
-        <v>0.4636197248</v>
-      </c>
-      <c r="X34">
-        <v>0.4491316084</v>
-      </c>
-      <c r="Y34">
-        <v>0.434643492</v>
-      </c>
-      <c r="Z34">
-        <v>0.4201553756</v>
-      </c>
-      <c r="AA34">
-        <v>0.4056672592</v>
-      </c>
-      <c r="AB34">
-        <v>0.3911791428</v>
-      </c>
-      <c r="AC34">
-        <v>0.3766910264</v>
-      </c>
-      <c r="AD34">
-        <v>0.36220291</v>
-      </c>
-      <c r="AE34">
-        <v>0.3477147936</v>
-      </c>
-      <c r="AF34">
-        <v>0.3332266772</v>
-      </c>
-      <c r="AG34">
-        <v>0.3187385608</v>
-      </c>
-      <c r="AH34">
-        <v>0.3042504444</v>
-      </c>
-      <c r="AI34">
-        <v>0.289762328</v>
-      </c>
-      <c r="AJ34">
-        <v>0.2752742116</v>
-      </c>
-      <c r="AK34">
-        <v>0.2607860952</v>
-      </c>
-      <c r="AL34">
-        <v>0.2462979788</v>
-      </c>
-      <c r="AM34">
-        <v>0.2318098624</v>
-      </c>
-      <c r="AN34">
-        <v>0.217321746</v>
-      </c>
-      <c r="AO34">
-        <v>0.2028336296</v>
-      </c>
-      <c r="AP34">
-        <v>0.1883455132</v>
-      </c>
-      <c r="AQ34">
-        <v>0.1738573968</v>
-      </c>
-      <c r="AR34">
-        <v>0.1593692804</v>
-      </c>
-      <c r="AS34">
-        <v>0.144881164</v>
-      </c>
-      <c r="AT34">
-        <v>0.1303930476</v>
-      </c>
-      <c r="AU34">
-        <v>0.1159049312</v>
-      </c>
-      <c r="AV34">
-        <v>0.1014168148</v>
-      </c>
-      <c r="AW34">
-        <v>0.08692869839999998</v>
-      </c>
-      <c r="AX34">
-        <v>0.07244058200000002</v>
-      </c>
-      <c r="AY34">
-        <v>0.05795246560000002</v>
-      </c>
-      <c r="AZ34">
-        <v>0.04346434920000002</v>
-      </c>
-      <c r="BA34">
-        <v>0.02897623280000001</v>
-      </c>
-      <c r="BB34">
-        <v>0.0144881164</v>
-      </c>
-      <c r="BC34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:55">
-      <c r="A35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" t="s">
-        <v>196</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>0.05</v>
-      </c>
-      <c r="K35">
-        <v>0.05</v>
-      </c>
-      <c r="L35">
-        <v>0.05</v>
-      </c>
-      <c r="M35">
-        <v>0.05</v>
-      </c>
-      <c r="N35">
-        <v>0.05</v>
-      </c>
-      <c r="O35">
-        <v>0.05</v>
-      </c>
-      <c r="P35">
-        <v>0.05</v>
-      </c>
-      <c r="Q35">
-        <v>0.05</v>
-      </c>
-      <c r="R35">
-        <v>0.05</v>
-      </c>
-      <c r="S35">
-        <v>0.05</v>
-      </c>
-      <c r="T35">
-        <v>0.05</v>
-      </c>
-      <c r="U35">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V35">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W35">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X35">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y35">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z35">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA35">
-        <v>0.23</v>
-      </c>
-      <c r="AB35">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC35">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD35">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE35">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF35">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG35">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH35">
-        <v>0.41</v>
-      </c>
-      <c r="AI35">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ35">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK35">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL35">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM35">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN35">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO35">
-        <v>0.59</v>
-      </c>
-      <c r="AP35">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ35">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR35">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS35">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT35">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU35">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV35">
-        <v>0.77</v>
-      </c>
-      <c r="AW35">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX35">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY35">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ35">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA35">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB35">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC35">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:55">
-      <c r="A36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36">
-        <v>0.05</v>
-      </c>
-      <c r="K36">
-        <v>0.05</v>
-      </c>
-      <c r="L36">
-        <v>0.05</v>
-      </c>
-      <c r="M36">
-        <v>0.05</v>
-      </c>
-      <c r="N36">
-        <v>0.05</v>
-      </c>
-      <c r="O36">
-        <v>0.05</v>
-      </c>
-      <c r="P36">
-        <v>0.05</v>
-      </c>
-      <c r="Q36">
-        <v>0.05</v>
-      </c>
-      <c r="R36">
-        <v>0.05</v>
-      </c>
-      <c r="S36">
-        <v>0.05</v>
-      </c>
-      <c r="T36">
-        <v>0.05</v>
-      </c>
-      <c r="U36">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V36">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W36">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X36">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y36">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z36">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA36">
-        <v>0.23</v>
-      </c>
-      <c r="AB36">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC36">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD36">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE36">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF36">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG36">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH36">
-        <v>0.41</v>
-      </c>
-      <c r="AI36">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ36">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK36">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL36">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM36">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN36">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO36">
-        <v>0.59</v>
-      </c>
-      <c r="AP36">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ36">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR36">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS36">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT36">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU36">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV36">
-        <v>0.77</v>
-      </c>
-      <c r="AW36">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX36">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY36">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ36">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA36">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB36">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC36">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:55">
-      <c r="A37" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" t="s">
-        <v>198</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>0.05</v>
-      </c>
-      <c r="K37">
-        <v>0.05</v>
-      </c>
-      <c r="L37">
-        <v>0.05</v>
-      </c>
-      <c r="M37">
-        <v>0.05</v>
-      </c>
-      <c r="N37">
-        <v>0.05</v>
-      </c>
-      <c r="O37">
-        <v>0.05</v>
-      </c>
-      <c r="P37">
-        <v>0.05</v>
-      </c>
-      <c r="Q37">
-        <v>0.05</v>
-      </c>
-      <c r="R37">
-        <v>0.05</v>
-      </c>
-      <c r="S37">
-        <v>0.05</v>
-      </c>
-      <c r="T37">
-        <v>0.05</v>
-      </c>
-      <c r="U37">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V37">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W37">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X37">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y37">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z37">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA37">
-        <v>0.23</v>
-      </c>
-      <c r="AB37">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC37">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD37">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE37">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF37">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG37">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH37">
-        <v>0.41</v>
-      </c>
-      <c r="AI37">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ37">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK37">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL37">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM37">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN37">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO37">
-        <v>0.59</v>
-      </c>
-      <c r="AP37">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ37">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR37">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS37">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT37">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU37">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV37">
-        <v>0.77</v>
-      </c>
-      <c r="AW37">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX37">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY37">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ37">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA37">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB37">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC37">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:55">
-      <c r="A38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <v>0.05</v>
-      </c>
-      <c r="K38">
-        <v>0.05</v>
-      </c>
-      <c r="L38">
-        <v>0.05</v>
-      </c>
-      <c r="M38">
-        <v>0.05</v>
-      </c>
-      <c r="N38">
-        <v>0.05</v>
-      </c>
-      <c r="O38">
-        <v>0.05</v>
-      </c>
-      <c r="P38">
-        <v>0.05</v>
-      </c>
-      <c r="Q38">
-        <v>0.05</v>
-      </c>
-      <c r="R38">
-        <v>0.05</v>
-      </c>
-      <c r="S38">
-        <v>0.05</v>
-      </c>
-      <c r="T38">
-        <v>0.05</v>
-      </c>
-      <c r="U38">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V38">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W38">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X38">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y38">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z38">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA38">
-        <v>0.23</v>
-      </c>
-      <c r="AB38">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC38">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD38">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE38">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF38">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG38">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH38">
-        <v>0.41</v>
-      </c>
-      <c r="AI38">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ38">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK38">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL38">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM38">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN38">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO38">
-        <v>0.59</v>
-      </c>
-      <c r="AP38">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ38">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR38">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS38">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT38">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU38">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV38">
-        <v>0.77</v>
-      </c>
-      <c r="AW38">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX38">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY38">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ38">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA38">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB38">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC38">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:55">
-      <c r="A39" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" t="s">
-        <v>200</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39">
-        <v>0.05</v>
-      </c>
-      <c r="K39">
-        <v>0.05</v>
-      </c>
-      <c r="L39">
-        <v>0.05</v>
-      </c>
-      <c r="M39">
-        <v>0.05</v>
-      </c>
-      <c r="N39">
-        <v>0.05</v>
-      </c>
-      <c r="O39">
-        <v>0.05</v>
-      </c>
-      <c r="P39">
-        <v>0.05</v>
-      </c>
-      <c r="Q39">
-        <v>0.05</v>
-      </c>
-      <c r="R39">
-        <v>0.05</v>
-      </c>
-      <c r="S39">
-        <v>0.05</v>
-      </c>
-      <c r="T39">
-        <v>0.05</v>
-      </c>
-      <c r="U39">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V39">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W39">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X39">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y39">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z39">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA39">
-        <v>0.23</v>
-      </c>
-      <c r="AB39">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC39">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD39">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE39">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF39">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG39">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH39">
-        <v>0.41</v>
-      </c>
-      <c r="AI39">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ39">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK39">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL39">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM39">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN39">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO39">
-        <v>0.59</v>
-      </c>
-      <c r="AP39">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ39">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR39">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS39">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT39">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU39">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV39">
-        <v>0.77</v>
-      </c>
-      <c r="AW39">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX39">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY39">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ39">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA39">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB39">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC39">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:55">
-      <c r="A40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" t="s">
-        <v>201</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40">
-        <v>0.05</v>
-      </c>
-      <c r="K40">
-        <v>0.05</v>
-      </c>
-      <c r="L40">
-        <v>0.05</v>
-      </c>
-      <c r="M40">
-        <v>0.05</v>
-      </c>
-      <c r="N40">
-        <v>0.05</v>
-      </c>
-      <c r="O40">
-        <v>0.05</v>
-      </c>
-      <c r="P40">
-        <v>0.05</v>
-      </c>
-      <c r="Q40">
-        <v>0.05</v>
-      </c>
-      <c r="R40">
-        <v>0.05</v>
-      </c>
-      <c r="S40">
-        <v>0.05</v>
-      </c>
-      <c r="T40">
-        <v>0.05</v>
-      </c>
-      <c r="U40">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V40">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W40">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X40">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y40">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z40">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA40">
-        <v>0.23</v>
-      </c>
-      <c r="AB40">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC40">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD40">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE40">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF40">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG40">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH40">
-        <v>0.41</v>
-      </c>
-      <c r="AI40">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ40">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK40">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL40">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM40">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN40">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO40">
-        <v>0.59</v>
-      </c>
-      <c r="AP40">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ40">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR40">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS40">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT40">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU40">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV40">
-        <v>0.77</v>
-      </c>
-      <c r="AW40">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX40">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY40">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ40">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA40">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB40">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC40">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:55">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" t="s">
-        <v>202</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41">
-        <v>0.05</v>
-      </c>
-      <c r="K41">
-        <v>0.05</v>
-      </c>
-      <c r="L41">
-        <v>0.05</v>
-      </c>
-      <c r="M41">
-        <v>0.05</v>
-      </c>
-      <c r="N41">
-        <v>0.05</v>
-      </c>
-      <c r="O41">
-        <v>0.05</v>
-      </c>
-      <c r="P41">
-        <v>0.05</v>
-      </c>
-      <c r="Q41">
-        <v>0.05</v>
-      </c>
-      <c r="R41">
-        <v>0.05</v>
-      </c>
-      <c r="S41">
-        <v>0.05</v>
-      </c>
-      <c r="T41">
-        <v>0.05</v>
-      </c>
-      <c r="U41">
-        <v>0.07571428571428571</v>
-      </c>
-      <c r="V41">
-        <v>0.1014285714285714</v>
-      </c>
-      <c r="W41">
-        <v>0.1271428571428571</v>
-      </c>
-      <c r="X41">
-        <v>0.1528571428571429</v>
-      </c>
-      <c r="Y41">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="Z41">
-        <v>0.2042857142857143</v>
-      </c>
-      <c r="AA41">
-        <v>0.23</v>
-      </c>
-      <c r="AB41">
-        <v>0.2557142857142857</v>
-      </c>
-      <c r="AC41">
-        <v>0.2814285714285714</v>
-      </c>
-      <c r="AD41">
-        <v>0.3071428571428571</v>
-      </c>
-      <c r="AE41">
-        <v>0.3328571428571429</v>
-      </c>
-      <c r="AF41">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AG41">
-        <v>0.3842857142857143</v>
-      </c>
-      <c r="AH41">
-        <v>0.41</v>
-      </c>
-      <c r="AI41">
-        <v>0.4357142857142857</v>
-      </c>
-      <c r="AJ41">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AK41">
-        <v>0.4871428571428571</v>
-      </c>
-      <c r="AL41">
-        <v>0.5128571428571428</v>
-      </c>
-      <c r="AM41">
-        <v>0.5385714285714286</v>
-      </c>
-      <c r="AN41">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AO41">
-        <v>0.59</v>
-      </c>
-      <c r="AP41">
-        <v>0.6157142857142857</v>
-      </c>
-      <c r="AQ41">
-        <v>0.6414285714285713</v>
-      </c>
-      <c r="AR41">
-        <v>0.667142857142857</v>
-      </c>
-      <c r="AS41">
-        <v>0.6928571428571428</v>
-      </c>
-      <c r="AT41">
-        <v>0.7185714285714286</v>
-      </c>
-      <c r="AU41">
-        <v>0.7442857142857143</v>
-      </c>
-      <c r="AV41">
-        <v>0.77</v>
-      </c>
-      <c r="AW41">
-        <v>0.7957142857142857</v>
-      </c>
-      <c r="AX41">
-        <v>0.8214285714285713</v>
-      </c>
-      <c r="AY41">
-        <v>0.847142857142857</v>
-      </c>
-      <c r="AZ41">
-        <v>0.8728571428571429</v>
-      </c>
-      <c r="BA41">
-        <v>0.8985714285714286</v>
-      </c>
-      <c r="BB41">
-        <v>0.9242857142857143</v>
-      </c>
-      <c r="BC41">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:55">
-      <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" t="s">
-        <v>203</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="J42">
-        <v>0.95</v>
-      </c>
-      <c r="K42">
-        <v>0.95</v>
-      </c>
-      <c r="L42">
-        <v>0.95</v>
-      </c>
-      <c r="M42">
-        <v>0.95</v>
-      </c>
-      <c r="N42">
-        <v>0.95</v>
-      </c>
-      <c r="O42">
-        <v>0.95</v>
-      </c>
-      <c r="P42">
-        <v>0.95</v>
-      </c>
-      <c r="Q42">
-        <v>0.95</v>
-      </c>
-      <c r="R42">
-        <v>0.95</v>
-      </c>
-      <c r="S42">
-        <v>0.95</v>
-      </c>
-      <c r="T42">
-        <v>0.95</v>
-      </c>
-      <c r="U42">
-        <v>0.95</v>
-      </c>
-      <c r="V42">
-        <v>0.95</v>
-      </c>
-      <c r="W42">
-        <v>0.95</v>
-      </c>
-      <c r="X42">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="Y42">
-        <v>0.95</v>
-      </c>
-      <c r="Z42">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="AA42">
-        <v>0.95</v>
-      </c>
-      <c r="AB42">
-        <v>0.95</v>
-      </c>
-      <c r="AC42">
-        <v>0.95</v>
-      </c>
-      <c r="AD42">
-        <v>0.95</v>
-      </c>
-      <c r="AE42">
-        <v>0.95</v>
-      </c>
-      <c r="AF42">
-        <v>0.95</v>
-      </c>
-      <c r="AG42">
-        <v>0.95</v>
-      </c>
-      <c r="AH42">
-        <v>0.95</v>
-      </c>
-      <c r="AI42">
-        <v>0.95</v>
-      </c>
-      <c r="AJ42">
-        <v>0.9500000000000001</v>
-      </c>
-      <c r="AK42">
-        <v>0.95</v>
-      </c>
-      <c r="AL42">
-        <v>0.95</v>
-      </c>
-      <c r="AM42">
-        <v>0.95</v>
-      </c>
-      <c r="AN42">
-        <v>0.95</v>
-      </c>
-      <c r="AO42">
-        <v>0.95</v>
-      </c>
-      <c r="AP42">
-        <v>0.95</v>
-      </c>
-      <c r="AQ42">
-        <v>0.95</v>
-      </c>
-      <c r="AR42">
-        <v>0.95</v>
-      </c>
-      <c r="AS42">
-        <v>0.95</v>
-      </c>
-      <c r="AT42">
-        <v>0.95</v>
-      </c>
-      <c r="AU42">
-        <v>0.95</v>
-      </c>
-      <c r="AV42">
-        <v>0.95</v>
-      </c>
-      <c r="AW42">
-        <v>0.95</v>
-      </c>
-      <c r="AX42">
-        <v>0.95</v>
-      </c>
-      <c r="AY42">
-        <v>0.95</v>
-      </c>
-      <c r="AZ42">
-        <v>0.95</v>
-      </c>
-      <c r="BA42">
-        <v>0.95</v>
-      </c>
-      <c r="BB42">
-        <v>0.95</v>
-      </c>
-      <c r="BC42">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:55">
-      <c r="A43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" t="s">
-        <v>236</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43">
-        <v>0.5</v>
-      </c>
-      <c r="K43">
-        <v>0.5</v>
-      </c>
-      <c r="L43">
-        <v>0.5</v>
-      </c>
-      <c r="M43">
-        <v>0.5</v>
-      </c>
-      <c r="N43">
-        <v>0.5</v>
-      </c>
-      <c r="O43">
-        <v>0.5</v>
-      </c>
-      <c r="P43">
-        <v>0.5</v>
-      </c>
-      <c r="Q43">
-        <v>0.5</v>
-      </c>
-      <c r="R43">
-        <v>0.5</v>
-      </c>
-      <c r="S43">
-        <v>0.5</v>
-      </c>
-      <c r="T43">
-        <v>0.5</v>
-      </c>
-      <c r="U43">
-        <v>0.5114285714285715</v>
-      </c>
-      <c r="V43">
-        <v>0.5228571428571428</v>
-      </c>
-      <c r="W43">
-        <v>0.5342857142857143</v>
-      </c>
-      <c r="X43">
-        <v>0.5457142857142857</v>
-      </c>
-      <c r="Y43">
-        <v>0.5571428571428572</v>
-      </c>
-      <c r="Z43">
-        <v>0.5685714285714285</v>
-      </c>
-      <c r="AA43">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="AB43">
-        <v>0.5914285714285714</v>
-      </c>
-      <c r="AC43">
-        <v>0.6028571428571429</v>
-      </c>
-      <c r="AD43">
-        <v>0.6142857142857143</v>
-      </c>
-      <c r="AE43">
-        <v>0.6257142857142857</v>
-      </c>
-      <c r="AF43">
-        <v>0.6371428571428572</v>
-      </c>
-      <c r="AG43">
-        <v>0.6485714285714286</v>
-      </c>
-      <c r="AH43">
-        <v>0.66</v>
-      </c>
-      <c r="AI43">
-        <v>0.6714285714285714</v>
-      </c>
-      <c r="AJ43">
-        <v>0.6828571428571428</v>
-      </c>
-      <c r="AK43">
-        <v>0.6942857142857143</v>
-      </c>
-      <c r="AL43">
-        <v>0.7057142857142857</v>
-      </c>
-      <c r="AM43">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="AN43">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="AO43">
-        <v>0.74</v>
-      </c>
-      <c r="AP43">
-        <v>0.7514285714285714</v>
-      </c>
-      <c r="AQ43">
-        <v>0.7628571428571429</v>
-      </c>
-      <c r="AR43">
-        <v>0.7742857142857144</v>
-      </c>
-      <c r="AS43">
-        <v>0.7857142857142858</v>
-      </c>
-      <c r="AT43">
-        <v>0.7971428571428572</v>
-      </c>
-      <c r="AU43">
-        <v>0.8085714285714285</v>
-      </c>
-      <c r="AV43">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AW43">
-        <v>0.8314285714285714</v>
-      </c>
-      <c r="AX43">
-        <v>0.8428571428571427</v>
-      </c>
-      <c r="AY43">
-        <v>0.8542857142857143</v>
-      </c>
-      <c r="AZ43">
-        <v>0.8657142857142857</v>
-      </c>
-      <c r="BA43">
-        <v>0.8771428571428571</v>
-      </c>
-      <c r="BB43">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="BC43">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:55">
-      <c r="A44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" t="s">
-        <v>267</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0.02428571428571429</v>
-      </c>
-      <c r="V44">
-        <v>0.04857142857142857</v>
-      </c>
-      <c r="W44">
-        <v>0.07285714285714286</v>
-      </c>
-      <c r="X44">
-        <v>0.09714285714285714</v>
-      </c>
-      <c r="Y44">
-        <v>0.1214285714285714</v>
-      </c>
-      <c r="Z44">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AA44">
-        <v>0.17</v>
-      </c>
-      <c r="AB44">
-        <v>0.1942857142857143</v>
-      </c>
-      <c r="AC44">
-        <v>0.2185714285714286</v>
-      </c>
-      <c r="AD44">
-        <v>0.2428571428571428</v>
-      </c>
-      <c r="AE44">
-        <v>0.2671428571428571</v>
-      </c>
-      <c r="AF44">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="AG44">
-        <v>0.3157142857142857</v>
-      </c>
-      <c r="AH44">
-        <v>0.34</v>
-      </c>
-      <c r="AI44">
-        <v>0.3642857142857143</v>
-      </c>
-      <c r="AJ44">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AK44">
-        <v>0.4128571428571429</v>
-      </c>
-      <c r="AL44">
-        <v>0.4371428571428571</v>
-      </c>
-      <c r="AM44">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AN44">
-        <v>0.4857142857142857</v>
-      </c>
-      <c r="AO44">
-        <v>0.51</v>
-      </c>
-      <c r="AP44">
-        <v>0.5342857142857143</v>
-      </c>
-      <c r="AQ44">
-        <v>0.5585714285714286</v>
-      </c>
-      <c r="AR44">
-        <v>0.5828571428571429</v>
-      </c>
-      <c r="AS44">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="AT44">
-        <v>0.6314285714285715</v>
-      </c>
-      <c r="AU44">
-        <v>0.6557142857142857</v>
-      </c>
-      <c r="AV44">
-        <v>0.68</v>
-      </c>
-      <c r="AW44">
-        <v>0.7042857142857143</v>
-      </c>
-      <c r="AX44">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="AY44">
-        <v>0.7528571428571428</v>
-      </c>
-      <c r="AZ44">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BA44">
-        <v>0.8014285714285714</v>
-      </c>
-      <c r="BB44">
-        <v>0.8257142857142857</v>
-      </c>
-      <c r="BC44">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:55">
-      <c r="A45" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" t="s">
-        <v>268</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0.02428571428571429</v>
-      </c>
-      <c r="V45">
-        <v>0.04857142857142857</v>
-      </c>
-      <c r="W45">
-        <v>0.07285714285714286</v>
-      </c>
-      <c r="X45">
-        <v>0.09714285714285714</v>
-      </c>
-      <c r="Y45">
-        <v>0.1214285714285714</v>
-      </c>
-      <c r="Z45">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AA45">
-        <v>0.17</v>
-      </c>
-      <c r="AB45">
-        <v>0.1942857142857143</v>
-      </c>
-      <c r="AC45">
-        <v>0.2185714285714286</v>
-      </c>
-      <c r="AD45">
-        <v>0.2428571428571428</v>
-      </c>
-      <c r="AE45">
-        <v>0.2671428571428571</v>
-      </c>
-      <c r="AF45">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="AG45">
-        <v>0.3157142857142857</v>
-      </c>
-      <c r="AH45">
-        <v>0.34</v>
-      </c>
-      <c r="AI45">
-        <v>0.3642857142857143</v>
-      </c>
-      <c r="AJ45">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AK45">
-        <v>0.4128571428571429</v>
-      </c>
-      <c r="AL45">
-        <v>0.4371428571428571</v>
-      </c>
-      <c r="AM45">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AN45">
-        <v>0.4857142857142857</v>
-      </c>
-      <c r="AO45">
-        <v>0.51</v>
-      </c>
-      <c r="AP45">
-        <v>0.5342857142857143</v>
-      </c>
-      <c r="AQ45">
-        <v>0.5585714285714286</v>
-      </c>
-      <c r="AR45">
-        <v>0.5828571428571429</v>
-      </c>
-      <c r="AS45">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="AT45">
-        <v>0.6314285714285715</v>
-      </c>
-      <c r="AU45">
-        <v>0.6557142857142857</v>
-      </c>
-      <c r="AV45">
-        <v>0.68</v>
-      </c>
-      <c r="AW45">
-        <v>0.7042857142857143</v>
-      </c>
-      <c r="AX45">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="AY45">
-        <v>0.7528571428571428</v>
-      </c>
-      <c r="AZ45">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BA45">
-        <v>0.8014285714285714</v>
-      </c>
-      <c r="BB45">
-        <v>0.8257142857142857</v>
-      </c>
-      <c r="BC45">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:55">
-      <c r="A46" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" t="s">
-        <v>269</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0.02428571428571429</v>
-      </c>
-      <c r="V46">
-        <v>0.04857142857142857</v>
-      </c>
-      <c r="W46">
-        <v>0.07285714285714286</v>
-      </c>
-      <c r="X46">
-        <v>0.09714285714285714</v>
-      </c>
-      <c r="Y46">
-        <v>0.1214285714285714</v>
-      </c>
-      <c r="Z46">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AA46">
-        <v>0.17</v>
-      </c>
-      <c r="AB46">
-        <v>0.1942857142857143</v>
-      </c>
-      <c r="AC46">
-        <v>0.2185714285714286</v>
-      </c>
-      <c r="AD46">
-        <v>0.2428571428571428</v>
-      </c>
-      <c r="AE46">
-        <v>0.2671428571428571</v>
-      </c>
-      <c r="AF46">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="AG46">
-        <v>0.3157142857142857</v>
-      </c>
-      <c r="AH46">
-        <v>0.34</v>
-      </c>
-      <c r="AI46">
-        <v>0.3642857142857143</v>
-      </c>
-      <c r="AJ46">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AK46">
-        <v>0.4128571428571429</v>
-      </c>
-      <c r="AL46">
-        <v>0.4371428571428571</v>
-      </c>
-      <c r="AM46">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AN46">
-        <v>0.4857142857142857</v>
-      </c>
-      <c r="AO46">
-        <v>0.51</v>
-      </c>
-      <c r="AP46">
-        <v>0.5342857142857143</v>
-      </c>
-      <c r="AQ46">
-        <v>0.5585714285714286</v>
-      </c>
-      <c r="AR46">
-        <v>0.5828571428571429</v>
-      </c>
-      <c r="AS46">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="AT46">
-        <v>0.6314285714285715</v>
-      </c>
-      <c r="AU46">
-        <v>0.6557142857142857</v>
-      </c>
-      <c r="AV46">
-        <v>0.68</v>
-      </c>
-      <c r="AW46">
-        <v>0.7042857142857143</v>
-      </c>
-      <c r="AX46">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="AY46">
-        <v>0.7528571428571428</v>
-      </c>
-      <c r="AZ46">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BA46">
-        <v>0.8014285714285714</v>
-      </c>
-      <c r="BB46">
-        <v>0.8257142857142857</v>
-      </c>
-      <c r="BC46">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:55">
-      <c r="A47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" t="s">
-        <v>270</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0.02428571428571429</v>
-      </c>
-      <c r="V47">
-        <v>0.04857142857142857</v>
-      </c>
-      <c r="W47">
-        <v>0.07285714285714286</v>
-      </c>
-      <c r="X47">
-        <v>0.09714285714285714</v>
-      </c>
-      <c r="Y47">
-        <v>0.1214285714285714</v>
-      </c>
-      <c r="Z47">
-        <v>0.1457142857142857</v>
-      </c>
-      <c r="AA47">
-        <v>0.17</v>
-      </c>
-      <c r="AB47">
-        <v>0.1942857142857143</v>
-      </c>
-      <c r="AC47">
-        <v>0.2185714285714286</v>
-      </c>
-      <c r="AD47">
-        <v>0.2428571428571428</v>
-      </c>
-      <c r="AE47">
-        <v>0.2671428571428571</v>
-      </c>
-      <c r="AF47">
-        <v>0.2914285714285714</v>
-      </c>
-      <c r="AG47">
-        <v>0.3157142857142857</v>
-      </c>
-      <c r="AH47">
-        <v>0.34</v>
-      </c>
-      <c r="AI47">
-        <v>0.3642857142857143</v>
-      </c>
-      <c r="AJ47">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AK47">
-        <v>0.4128571428571429</v>
-      </c>
-      <c r="AL47">
-        <v>0.4371428571428571</v>
-      </c>
-      <c r="AM47">
-        <v>0.4614285714285714</v>
-      </c>
-      <c r="AN47">
-        <v>0.4857142857142857</v>
-      </c>
-      <c r="AO47">
-        <v>0.51</v>
-      </c>
-      <c r="AP47">
-        <v>0.5342857142857143</v>
-      </c>
-      <c r="AQ47">
-        <v>0.5585714285714286</v>
-      </c>
-      <c r="AR47">
-        <v>0.5828571428571429</v>
-      </c>
-      <c r="AS47">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="AT47">
-        <v>0.6314285714285715</v>
-      </c>
-      <c r="AU47">
-        <v>0.6557142857142857</v>
-      </c>
-      <c r="AV47">
-        <v>0.68</v>
-      </c>
-      <c r="AW47">
-        <v>0.7042857142857143</v>
-      </c>
-      <c r="AX47">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="AY47">
-        <v>0.7528571428571428</v>
-      </c>
-      <c r="AZ47">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BA47">
-        <v>0.8014285714285714</v>
-      </c>
-      <c r="BB47">
-        <v>0.8257142857142857</v>
-      </c>
-      <c r="BC47">
-        <v>0.85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ce_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ce_calibrated.xlsx
@@ -38648,106 +38648,106 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W16">
-        <v>0.02424242424242425</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X16">
-        <v>0.04848484848484849</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y16">
-        <v>0.07272727272727274</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z16">
-        <v>0.09696969696969698</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA16">
-        <v>0.1212121212121212</v>
+        <v>0.16</v>
       </c>
       <c r="AB16">
-        <v>0.1454545454545455</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC16">
-        <v>0.1696969696969697</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD16">
-        <v>0.193939393939394</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE16">
-        <v>0.2181818181818182</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF16">
-        <v>0.2424242424242424</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG16">
-        <v>0.2666666666666667</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH16">
-        <v>0.290909090909091</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI16">
-        <v>0.3151515151515152</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ16">
-        <v>0.3393939393939394</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK16">
-        <v>0.3636363636363636</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL16">
-        <v>0.3878787878787879</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM16">
-        <v>0.4121212121212121</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN16">
-        <v>0.4363636363636363</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO16">
-        <v>0.4606060606060607</v>
+        <v>0.48</v>
       </c>
       <c r="AP16">
-        <v>0.4848484848484849</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ16">
-        <v>0.5090909090909091</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR16">
-        <v>0.5333333333333333</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS16">
-        <v>0.5575757575757576</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT16">
-        <v>0.5818181818181819</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU16">
-        <v>0.6060606060606061</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV16">
-        <v>0.6303030303030304</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW16">
-        <v>0.6545454545454547</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX16">
-        <v>0.6787878787878788</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY16">
-        <v>0.7030303030303031</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ16">
-        <v>0.7272727272727273</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA16">
-        <v>0.7515151515151516</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB16">
-        <v>0.7757575757575759</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC16">
         <v>0.8</v>
@@ -38803,106 +38803,106 @@
         <v>0.004570438</v>
       </c>
       <c r="U17">
-        <v>0.004570438</v>
+        <v>0.004439854057142856</v>
       </c>
       <c r="V17">
-        <v>0.004570438</v>
+        <v>0.004309270114285714</v>
       </c>
       <c r="W17">
-        <v>0.004431939878787879</v>
+        <v>0.004178686171428571</v>
       </c>
       <c r="X17">
-        <v>0.004293441757575758</v>
+        <v>0.004048102228571428</v>
       </c>
       <c r="Y17">
-        <v>0.004154943636363636</v>
+        <v>0.003917518285714286</v>
       </c>
       <c r="Z17">
-        <v>0.004016445515151515</v>
+        <v>0.003786934342857142</v>
       </c>
       <c r="AA17">
-        <v>0.003877947393939394</v>
+        <v>0.0036563504</v>
       </c>
       <c r="AB17">
-        <v>0.003739449272727272</v>
+        <v>0.003525766457142857</v>
       </c>
       <c r="AC17">
-        <v>0.003600951151515151</v>
+        <v>0.003395182514285714</v>
       </c>
       <c r="AD17">
-        <v>0.00346245303030303</v>
+        <v>0.003264598571428571</v>
       </c>
       <c r="AE17">
-        <v>0.003323954909090909</v>
+        <v>0.003134014628571428</v>
       </c>
       <c r="AF17">
-        <v>0.003185456787878788</v>
+        <v>0.003003430685714285</v>
       </c>
       <c r="AG17">
-        <v>0.003046958666666667</v>
+        <v>0.002872846742857143</v>
       </c>
       <c r="AH17">
-        <v>0.002908460545454545</v>
+        <v>0.002742262799999999</v>
       </c>
       <c r="AI17">
-        <v>0.002769962424242424</v>
+        <v>0.002611678857142857</v>
       </c>
       <c r="AJ17">
-        <v>0.002631464303030303</v>
+        <v>0.002481094914285715</v>
       </c>
       <c r="AK17">
-        <v>0.002492966181818181</v>
+        <v>0.002350510971428571</v>
       </c>
       <c r="AL17">
-        <v>0.00235446806060606</v>
+        <v>0.002219927028571429</v>
       </c>
       <c r="AM17">
-        <v>0.002215969939393939</v>
+        <v>0.002089343085714286</v>
       </c>
       <c r="AN17">
-        <v>0.002077471818181818</v>
+        <v>0.001958759142857143</v>
       </c>
       <c r="AO17">
-        <v>0.001938973696969697</v>
+        <v>0.0018281752</v>
       </c>
       <c r="AP17">
-        <v>0.001800475575757575</v>
+        <v>0.001697591257142857</v>
       </c>
       <c r="AQ17">
-        <v>0.001661977454545454</v>
+        <v>0.001567007314285714</v>
       </c>
       <c r="AR17">
-        <v>0.001523479333333333</v>
+        <v>0.001436423371428571</v>
       </c>
       <c r="AS17">
-        <v>0.001384981212121212</v>
+        <v>0.001305839428571428</v>
       </c>
       <c r="AT17">
-        <v>0.001246483090909091</v>
+        <v>0.001175255485714285</v>
       </c>
       <c r="AU17">
-        <v>0.00110798496969697</v>
+        <v>0.001044671542857143</v>
       </c>
       <c r="AV17">
-        <v>0.0009694868484848486</v>
+        <v>0.0009140875999999997</v>
       </c>
       <c r="AW17">
-        <v>0.000830988727272727</v>
+        <v>0.0007835036571428568</v>
       </c>
       <c r="AX17">
-        <v>0.0006924906060606059</v>
+        <v>0.0006529197142857144</v>
       </c>
       <c r="AY17">
-        <v>0.0005539924848484848</v>
+        <v>0.0005223357714285716</v>
       </c>
       <c r="AZ17">
-        <v>0.0004154943636363637</v>
+        <v>0.0003917518285714287</v>
       </c>
       <c r="BA17">
-        <v>0.0002769962424242421</v>
+        <v>0.0002611678857142858</v>
       </c>
       <c r="BB17">
-        <v>0.0001384981212121211</v>
+        <v>0.0001305839428571429</v>
       </c>
       <c r="BC17">
         <v>0</v>
@@ -38958,106 +38958,106 @@
         <v>0.261553696</v>
       </c>
       <c r="U18">
-        <v>0.261553696</v>
+        <v>0.2569378761142857</v>
       </c>
       <c r="V18">
-        <v>0.261553696</v>
+        <v>0.2523220562285714</v>
       </c>
       <c r="W18">
-        <v>0.2566581294545455</v>
+        <v>0.2477062363428571</v>
       </c>
       <c r="X18">
-        <v>0.2517625629090909</v>
+        <v>0.2430904164571429</v>
       </c>
       <c r="Y18">
-        <v>0.2468669963636363</v>
+        <v>0.2384745965714286</v>
       </c>
       <c r="Z18">
-        <v>0.2419714298181818</v>
+        <v>0.2338587766857143</v>
       </c>
       <c r="AA18">
-        <v>0.2370758632727273</v>
+        <v>0.2292429568</v>
       </c>
       <c r="AB18">
-        <v>0.2321802967272727</v>
+        <v>0.2246271369142857</v>
       </c>
       <c r="AC18">
-        <v>0.2272847301818182</v>
+        <v>0.2200113170285714</v>
       </c>
       <c r="AD18">
-        <v>0.2223891636363636</v>
+        <v>0.2153954971428572</v>
       </c>
       <c r="AE18">
-        <v>0.2174935970909091</v>
+        <v>0.2107796772571429</v>
       </c>
       <c r="AF18">
-        <v>0.2125980305454546</v>
+        <v>0.2061638573714286</v>
       </c>
       <c r="AG18">
-        <v>0.207702464</v>
+        <v>0.2015480374857143</v>
       </c>
       <c r="AH18">
-        <v>0.2028068974545455</v>
+        <v>0.1969322176</v>
       </c>
       <c r="AI18">
-        <v>0.1979113309090909</v>
+        <v>0.1923163977142857</v>
       </c>
       <c r="AJ18">
-        <v>0.1930157643636363</v>
+        <v>0.1877005778285714</v>
       </c>
       <c r="AK18">
-        <v>0.1881201978181818</v>
+        <v>0.1830847579428571</v>
       </c>
       <c r="AL18">
-        <v>0.1832246312727273</v>
+        <v>0.1784689380571429</v>
       </c>
       <c r="AM18">
-        <v>0.1783290647272727</v>
+        <v>0.1738531181714286</v>
       </c>
       <c r="AN18">
-        <v>0.1734334981818182</v>
+        <v>0.1692372982857143</v>
       </c>
       <c r="AO18">
-        <v>0.1685379316363636</v>
+        <v>0.1646214784</v>
       </c>
       <c r="AP18">
-        <v>0.1636423650909091</v>
+        <v>0.1600056585142857</v>
       </c>
       <c r="AQ18">
-        <v>0.1587467985454545</v>
+        <v>0.1553898386285714</v>
       </c>
       <c r="AR18">
-        <v>0.153851232</v>
+        <v>0.1507740187428571</v>
       </c>
       <c r="AS18">
-        <v>0.1489556654545454</v>
+        <v>0.1461581988571429</v>
       </c>
       <c r="AT18">
-        <v>0.1440600989090909</v>
+        <v>0.1415423789714286</v>
       </c>
       <c r="AU18">
-        <v>0.1391645323636364</v>
+        <v>0.1369265590857143</v>
       </c>
       <c r="AV18">
-        <v>0.1342689658181818</v>
+        <v>0.1323107392</v>
       </c>
       <c r="AW18">
-        <v>0.1293733992727273</v>
+        <v>0.1276949193142857</v>
       </c>
       <c r="AX18">
-        <v>0.1244778327272727</v>
+        <v>0.1230790994285714</v>
       </c>
       <c r="AY18">
-        <v>0.1195822661818182</v>
+        <v>0.1184632795428572</v>
       </c>
       <c r="AZ18">
-        <v>0.1146866996363636</v>
+        <v>0.1138474596571429</v>
       </c>
       <c r="BA18">
-        <v>0.1097911330909091</v>
+        <v>0.1092316397714286</v>
       </c>
       <c r="BB18">
-        <v>0.1048955665454546</v>
+        <v>0.1046158198857143</v>
       </c>
       <c r="BC18">
         <v>0.1</v>
@@ -39113,106 +39113,106 @@
         <v>0.261553696</v>
       </c>
       <c r="U19">
-        <v>0.261553696</v>
+        <v>0.2569378761142857</v>
       </c>
       <c r="V19">
-        <v>0.261553696</v>
+        <v>0.2523220562285714</v>
       </c>
       <c r="W19">
-        <v>0.2566581294545455</v>
+        <v>0.2477062363428571</v>
       </c>
       <c r="X19">
-        <v>0.2517625629090909</v>
+        <v>0.2430904164571429</v>
       </c>
       <c r="Y19">
-        <v>0.2468669963636363</v>
+        <v>0.2384745965714286</v>
       </c>
       <c r="Z19">
-        <v>0.2419714298181818</v>
+        <v>0.2338587766857143</v>
       </c>
       <c r="AA19">
-        <v>0.2370758632727273</v>
+        <v>0.2292429568</v>
       </c>
       <c r="AB19">
-        <v>0.2321802967272727</v>
+        <v>0.2246271369142857</v>
       </c>
       <c r="AC19">
-        <v>0.2272847301818182</v>
+        <v>0.2200113170285714</v>
       </c>
       <c r="AD19">
-        <v>0.2223891636363636</v>
+        <v>0.2153954971428572</v>
       </c>
       <c r="AE19">
-        <v>0.2174935970909091</v>
+        <v>0.2107796772571429</v>
       </c>
       <c r="AF19">
-        <v>0.2125980305454546</v>
+        <v>0.2061638573714286</v>
       </c>
       <c r="AG19">
-        <v>0.207702464</v>
+        <v>0.2015480374857143</v>
       </c>
       <c r="AH19">
-        <v>0.2028068974545455</v>
+        <v>0.1969322176</v>
       </c>
       <c r="AI19">
-        <v>0.1979113309090909</v>
+        <v>0.1923163977142857</v>
       </c>
       <c r="AJ19">
-        <v>0.1930157643636363</v>
+        <v>0.1877005778285714</v>
       </c>
       <c r="AK19">
-        <v>0.1881201978181818</v>
+        <v>0.1830847579428571</v>
       </c>
       <c r="AL19">
-        <v>0.1832246312727273</v>
+        <v>0.1784689380571429</v>
       </c>
       <c r="AM19">
-        <v>0.1783290647272727</v>
+        <v>0.1738531181714286</v>
       </c>
       <c r="AN19">
-        <v>0.1734334981818182</v>
+        <v>0.1692372982857143</v>
       </c>
       <c r="AO19">
-        <v>0.1685379316363636</v>
+        <v>0.1646214784</v>
       </c>
       <c r="AP19">
-        <v>0.1636423650909091</v>
+        <v>0.1600056585142857</v>
       </c>
       <c r="AQ19">
-        <v>0.1587467985454545</v>
+        <v>0.1553898386285714</v>
       </c>
       <c r="AR19">
-        <v>0.153851232</v>
+        <v>0.1507740187428571</v>
       </c>
       <c r="AS19">
-        <v>0.1489556654545454</v>
+        <v>0.1461581988571429</v>
       </c>
       <c r="AT19">
-        <v>0.1440600989090909</v>
+        <v>0.1415423789714286</v>
       </c>
       <c r="AU19">
-        <v>0.1391645323636364</v>
+        <v>0.1369265590857143</v>
       </c>
       <c r="AV19">
-        <v>0.1342689658181818</v>
+        <v>0.1323107392</v>
       </c>
       <c r="AW19">
-        <v>0.1293733992727273</v>
+        <v>0.1276949193142857</v>
       </c>
       <c r="AX19">
-        <v>0.1244778327272727</v>
+        <v>0.1230790994285714</v>
       </c>
       <c r="AY19">
-        <v>0.1195822661818182</v>
+        <v>0.1184632795428572</v>
       </c>
       <c r="AZ19">
-        <v>0.1146866996363636</v>
+        <v>0.1138474596571429</v>
       </c>
       <c r="BA19">
-        <v>0.1097911330909091</v>
+        <v>0.1092316397714286</v>
       </c>
       <c r="BB19">
-        <v>0.1048955665454546</v>
+        <v>0.1046158198857143</v>
       </c>
       <c r="BC19">
         <v>0.1</v>
@@ -39268,106 +39268,106 @@
         <v>0.073899806</v>
       </c>
       <c r="U20">
-        <v>0.073899806</v>
+        <v>0.07178838297142857</v>
       </c>
       <c r="V20">
-        <v>0.073899806</v>
+        <v>0.06967695994285714</v>
       </c>
       <c r="W20">
-        <v>0.07166041793939394</v>
+        <v>0.06756553691428571</v>
       </c>
       <c r="X20">
-        <v>0.06942102987878788</v>
+        <v>0.06545411388571429</v>
       </c>
       <c r="Y20">
-        <v>0.06718164181818181</v>
+        <v>0.06334269085714286</v>
       </c>
       <c r="Z20">
-        <v>0.06494225375757576</v>
+        <v>0.06123126782857143</v>
       </c>
       <c r="AA20">
-        <v>0.0627028656969697</v>
+        <v>0.0591198448</v>
       </c>
       <c r="AB20">
-        <v>0.06046347763636363</v>
+        <v>0.05700842177142857</v>
       </c>
       <c r="AC20">
-        <v>0.05822408957575757</v>
+        <v>0.05489699874285715</v>
       </c>
       <c r="AD20">
-        <v>0.05598470151515152</v>
+        <v>0.05278557571428572</v>
       </c>
       <c r="AE20">
-        <v>0.05374531345454545</v>
+        <v>0.05067415268571428</v>
       </c>
       <c r="AF20">
-        <v>0.0515059253939394</v>
+        <v>0.04856272965714285</v>
       </c>
       <c r="AG20">
-        <v>0.04926653733333334</v>
+        <v>0.04645130662857143</v>
       </c>
       <c r="AH20">
-        <v>0.04702714927272727</v>
+        <v>0.0443398836</v>
       </c>
       <c r="AI20">
-        <v>0.04478776121212121</v>
+        <v>0.04222846057142857</v>
       </c>
       <c r="AJ20">
-        <v>0.04254837315151515</v>
+        <v>0.04011703754285715</v>
       </c>
       <c r="AK20">
-        <v>0.04030898509090908</v>
+        <v>0.03800561451428571</v>
       </c>
       <c r="AL20">
-        <v>0.03806959703030303</v>
+        <v>0.03589419148571429</v>
       </c>
       <c r="AM20">
-        <v>0.03583020896969697</v>
+        <v>0.03378276845714286</v>
       </c>
       <c r="AN20">
-        <v>0.03359082090909091</v>
+        <v>0.03167134542857143</v>
       </c>
       <c r="AO20">
-        <v>0.03135143284848484</v>
+        <v>0.0295599224</v>
       </c>
       <c r="AP20">
-        <v>0.02911204478787879</v>
+        <v>0.02744849937142857</v>
       </c>
       <c r="AQ20">
-        <v>0.02687265672727273</v>
+        <v>0.02533707634285714</v>
       </c>
       <c r="AR20">
-        <v>0.02463326866666667</v>
+        <v>0.02322565331428571</v>
       </c>
       <c r="AS20">
-        <v>0.0223938806060606</v>
+        <v>0.02111423028571428</v>
       </c>
       <c r="AT20">
-        <v>0.02015449254545454</v>
+        <v>0.01900280725714286</v>
       </c>
       <c r="AU20">
-        <v>0.01791510448484849</v>
+        <v>0.01689138422857142</v>
       </c>
       <c r="AV20">
-        <v>0.01567571642424243</v>
+        <v>0.0147799612</v>
       </c>
       <c r="AW20">
-        <v>0.01343632836363636</v>
+        <v>0.01266853817142857</v>
       </c>
       <c r="AX20">
-        <v>0.0111969403030303</v>
+        <v>0.01055711514285715</v>
       </c>
       <c r="AY20">
-        <v>0.008957552242424243</v>
+        <v>0.008445692114285717</v>
       </c>
       <c r="AZ20">
-        <v>0.006718164181818184</v>
+        <v>0.006334269085714288</v>
       </c>
       <c r="BA20">
-        <v>0.004478776121212117</v>
+        <v>0.004222846057142859</v>
       </c>
       <c r="BB20">
-        <v>0.002239388060606059</v>
+        <v>0.002111423028571429</v>
       </c>
       <c r="BC20">
         <v>0</v>
@@ -39423,106 +39423,106 @@
         <v>0.398422364</v>
       </c>
       <c r="U21">
-        <v>0.398422364</v>
+        <v>0.3870388678857142</v>
       </c>
       <c r="V21">
-        <v>0.398422364</v>
+        <v>0.3756553717714285</v>
       </c>
       <c r="W21">
-        <v>0.386348959030303</v>
+        <v>0.3642718756571428</v>
       </c>
       <c r="X21">
-        <v>0.374275554060606</v>
+        <v>0.3528883795428571</v>
       </c>
       <c r="Y21">
-        <v>0.362202149090909</v>
+        <v>0.3415048834285714</v>
       </c>
       <c r="Z21">
-        <v>0.3501287441212121</v>
+        <v>0.3301213873142857</v>
       </c>
       <c r="AA21">
-        <v>0.3380553391515151</v>
+        <v>0.3187378912</v>
       </c>
       <c r="AB21">
-        <v>0.3259819341818181</v>
+        <v>0.3073543950857143</v>
       </c>
       <c r="AC21">
-        <v>0.3139085292121212</v>
+        <v>0.2959708989714286</v>
       </c>
       <c r="AD21">
-        <v>0.3018351242424242</v>
+        <v>0.2845874028571428</v>
       </c>
       <c r="AE21">
-        <v>0.2897617192727273</v>
+        <v>0.2732039067428571</v>
       </c>
       <c r="AF21">
-        <v>0.2776883143030303</v>
+        <v>0.2618204106285714</v>
       </c>
       <c r="AG21">
-        <v>0.2656149093333334</v>
+        <v>0.2504369145142857</v>
       </c>
       <c r="AH21">
-        <v>0.2535415043636363</v>
+        <v>0.2390534184</v>
       </c>
       <c r="AI21">
-        <v>0.2414680993939394</v>
+        <v>0.2276699222857143</v>
       </c>
       <c r="AJ21">
-        <v>0.2293946944242424</v>
+        <v>0.2162864261714286</v>
       </c>
       <c r="AK21">
-        <v>0.2173212894545454</v>
+        <v>0.2049029300571428</v>
       </c>
       <c r="AL21">
-        <v>0.2052478844848485</v>
+        <v>0.1935194339428571</v>
       </c>
       <c r="AM21">
-        <v>0.1931744795151515</v>
+        <v>0.1821359378285714</v>
       </c>
       <c r="AN21">
-        <v>0.1811010745454545</v>
+        <v>0.1707524417142857</v>
       </c>
       <c r="AO21">
-        <v>0.1690276695757575</v>
+        <v>0.1593689456</v>
       </c>
       <c r="AP21">
-        <v>0.1569542646060606</v>
+        <v>0.1479854494857143</v>
       </c>
       <c r="AQ21">
-        <v>0.1448808596363636</v>
+        <v>0.1366019533714286</v>
       </c>
       <c r="AR21">
-        <v>0.1328074546666667</v>
+        <v>0.1252184572571428</v>
       </c>
       <c r="AS21">
-        <v>0.1207340496969697</v>
+        <v>0.1138349611428571</v>
       </c>
       <c r="AT21">
-        <v>0.1086606447272727</v>
+        <v>0.1024514650285714</v>
       </c>
       <c r="AU21">
-        <v>0.09658723975757576</v>
+        <v>0.09106796891428569</v>
       </c>
       <c r="AV21">
-        <v>0.0845138347878788</v>
+        <v>0.07968447279999998</v>
       </c>
       <c r="AW21">
-        <v>0.07244042981818179</v>
+        <v>0.06830097668571426</v>
       </c>
       <c r="AX21">
-        <v>0.06036702484848484</v>
+        <v>0.05691748057142858</v>
       </c>
       <c r="AY21">
-        <v>0.04829361987878788</v>
+        <v>0.04553398445714287</v>
       </c>
       <c r="AZ21">
-        <v>0.03622021490909092</v>
+        <v>0.03415048834285715</v>
       </c>
       <c r="BA21">
-        <v>0.02414680993939392</v>
+        <v>0.02276699222857144</v>
       </c>
       <c r="BB21">
-        <v>0.01207340496969696</v>
+        <v>0.01138349611428572</v>
       </c>
       <c r="BC21">
         <v>0</v>
@@ -39727,106 +39727,106 @@
         <v>0.02</v>
       </c>
       <c r="U23">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="V23">
-        <v>0.02</v>
+        <v>0.046</v>
       </c>
       <c r="W23">
-        <v>0.03378787878787878</v>
+        <v>0.059</v>
       </c>
       <c r="X23">
-        <v>0.04757575757575758</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y23">
-        <v>0.06136363636363636</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="Z23">
-        <v>0.07515151515151515</v>
+        <v>0.09799999999999999</v>
       </c>
       <c r="AA23">
-        <v>0.08893939393939394</v>
+        <v>0.111</v>
       </c>
       <c r="AB23">
-        <v>0.1027272727272727</v>
+        <v>0.124</v>
       </c>
       <c r="AC23">
-        <v>0.1165151515151515</v>
+        <v>0.137</v>
       </c>
       <c r="AD23">
-        <v>0.1303030303030303</v>
+        <v>0.15</v>
       </c>
       <c r="AE23">
-        <v>0.1440909090909091</v>
+        <v>0.163</v>
       </c>
       <c r="AF23">
-        <v>0.1578787878787879</v>
+        <v>0.176</v>
       </c>
       <c r="AG23">
-        <v>0.1716666666666667</v>
+        <v>0.189</v>
       </c>
       <c r="AH23">
-        <v>0.1854545454545455</v>
+        <v>0.202</v>
       </c>
       <c r="AI23">
-        <v>0.1992424242424242</v>
+        <v>0.215</v>
       </c>
       <c r="AJ23">
-        <v>0.213030303030303</v>
+        <v>0.228</v>
       </c>
       <c r="AK23">
-        <v>0.2268181818181818</v>
+        <v>0.241</v>
       </c>
       <c r="AL23">
-        <v>0.2406060606060606</v>
+        <v>0.2539999999999999</v>
       </c>
       <c r="AM23">
-        <v>0.2543939393939394</v>
+        <v>0.267</v>
       </c>
       <c r="AN23">
-        <v>0.2681818181818181</v>
+        <v>0.28</v>
       </c>
       <c r="AO23">
-        <v>0.281969696969697</v>
+        <v>0.293</v>
       </c>
       <c r="AP23">
-        <v>0.2957575757575758</v>
+        <v>0.306</v>
       </c>
       <c r="AQ23">
-        <v>0.3095454545454545</v>
+        <v>0.319</v>
       </c>
       <c r="AR23">
-        <v>0.3233333333333333</v>
+        <v>0.332</v>
       </c>
       <c r="AS23">
-        <v>0.3371212121212121</v>
+        <v>0.345</v>
       </c>
       <c r="AT23">
-        <v>0.3509090909090909</v>
+        <v>0.358</v>
       </c>
       <c r="AU23">
-        <v>0.3646969696969696</v>
+        <v>0.371</v>
       </c>
       <c r="AV23">
-        <v>0.3784848484848485</v>
+        <v>0.384</v>
       </c>
       <c r="AW23">
-        <v>0.3922727272727273</v>
+        <v>0.397</v>
       </c>
       <c r="AX23">
-        <v>0.4060606060606061</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="AY23">
-        <v>0.4198484848484849</v>
+        <v>0.4229999999999999</v>
       </c>
       <c r="AZ23">
-        <v>0.4336363636363636</v>
+        <v>0.436</v>
       </c>
       <c r="BA23">
-        <v>0.4474242424242424</v>
+        <v>0.449</v>
       </c>
       <c r="BB23">
-        <v>0.4612121212121212</v>
+        <v>0.462</v>
       </c>
       <c r="BC23">
         <v>0.475</v>
@@ -39879,106 +39879,106 @@
         <v>0.4</v>
       </c>
       <c r="U24">
-        <v>0.4</v>
+        <v>0.4021428571428571</v>
       </c>
       <c r="V24">
-        <v>0.4</v>
+        <v>0.4042857142857143</v>
       </c>
       <c r="W24">
-        <v>0.4022727272727273</v>
+        <v>0.4064285714285714</v>
       </c>
       <c r="X24">
-        <v>0.4045454545454546</v>
+        <v>0.4085714285714286</v>
       </c>
       <c r="Y24">
-        <v>0.4068181818181819</v>
+        <v>0.4107142857142858</v>
       </c>
       <c r="Z24">
-        <v>0.4090909090909091</v>
+        <v>0.4128571428571428</v>
       </c>
       <c r="AA24">
-        <v>0.4113636363636364</v>
+        <v>0.415</v>
       </c>
       <c r="AB24">
-        <v>0.4136363636363636</v>
+        <v>0.4171428571428571</v>
       </c>
       <c r="AC24">
-        <v>0.415909090909091</v>
+        <v>0.4192857142857143</v>
       </c>
       <c r="AD24">
-        <v>0.4181818181818182</v>
+        <v>0.4214285714285715</v>
       </c>
       <c r="AE24">
-        <v>0.4204545454545455</v>
+        <v>0.4235714285714286</v>
       </c>
       <c r="AF24">
-        <v>0.4227272727272727</v>
+        <v>0.4257142857142857</v>
       </c>
       <c r="AG24">
-        <v>0.425</v>
+        <v>0.4278571428571429</v>
       </c>
       <c r="AH24">
-        <v>0.4272727272727273</v>
+        <v>0.43</v>
       </c>
       <c r="AI24">
-        <v>0.4295454545454546</v>
+        <v>0.4321428571428571</v>
       </c>
       <c r="AJ24">
-        <v>0.4318181818181818</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AK24">
-        <v>0.4340909090909091</v>
+        <v>0.4364285714285714</v>
       </c>
       <c r="AL24">
-        <v>0.4363636363636363</v>
+        <v>0.4385714285714286</v>
       </c>
       <c r="AM24">
-        <v>0.4386363636363637</v>
+        <v>0.4407142857142857</v>
       </c>
       <c r="AN24">
-        <v>0.4409090909090909</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="AO24">
-        <v>0.4431818181818182</v>
+        <v>0.445</v>
       </c>
       <c r="AP24">
-        <v>0.4454545454545455</v>
+        <v>0.4471428571428571</v>
       </c>
       <c r="AQ24">
-        <v>0.4477272727272728</v>
+        <v>0.4492857142857143</v>
       </c>
       <c r="AR24">
-        <v>0.45</v>
+        <v>0.4514285714285714</v>
       </c>
       <c r="AS24">
-        <v>0.4522727272727273</v>
+        <v>0.4535714285714286</v>
       </c>
       <c r="AT24">
-        <v>0.4545454545454545</v>
+        <v>0.4557142857142857</v>
       </c>
       <c r="AU24">
-        <v>0.4568181818181818</v>
+        <v>0.4578571428571429</v>
       </c>
       <c r="AV24">
-        <v>0.4590909090909091</v>
+        <v>0.46</v>
       </c>
       <c r="AW24">
-        <v>0.4613636363636364</v>
+        <v>0.4621428571428571</v>
       </c>
       <c r="AX24">
-        <v>0.4636363636363636</v>
+        <v>0.4642857142857142</v>
       </c>
       <c r="AY24">
-        <v>0.4659090909090909</v>
+        <v>0.4664285714285714</v>
       </c>
       <c r="AZ24">
-        <v>0.4681818181818181</v>
+        <v>0.4685714285714286</v>
       </c>
       <c r="BA24">
-        <v>0.4704545454545455</v>
+        <v>0.4707142857142857</v>
       </c>
       <c r="BB24">
-        <v>0.4727272727272727</v>
+        <v>0.4728571428571429</v>
       </c>
       <c r="BC24">
         <v>0.475</v>
@@ -40031,106 +40031,106 @@
         <v>0.02</v>
       </c>
       <c r="U25">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="V25">
-        <v>0.02</v>
+        <v>0.046</v>
       </c>
       <c r="W25">
-        <v>0.03378787878787878</v>
+        <v>0.059</v>
       </c>
       <c r="X25">
-        <v>0.04757575757575758</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y25">
-        <v>0.06136363636363636</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="Z25">
-        <v>0.07515151515151515</v>
+        <v>0.09799999999999999</v>
       </c>
       <c r="AA25">
-        <v>0.08893939393939394</v>
+        <v>0.111</v>
       </c>
       <c r="AB25">
-        <v>0.1027272727272727</v>
+        <v>0.124</v>
       </c>
       <c r="AC25">
-        <v>0.1165151515151515</v>
+        <v>0.137</v>
       </c>
       <c r="AD25">
-        <v>0.1303030303030303</v>
+        <v>0.15</v>
       </c>
       <c r="AE25">
-        <v>0.1440909090909091</v>
+        <v>0.163</v>
       </c>
       <c r="AF25">
-        <v>0.1578787878787879</v>
+        <v>0.176</v>
       </c>
       <c r="AG25">
-        <v>0.1716666666666667</v>
+        <v>0.189</v>
       </c>
       <c r="AH25">
-        <v>0.1854545454545455</v>
+        <v>0.202</v>
       </c>
       <c r="AI25">
-        <v>0.1992424242424242</v>
+        <v>0.215</v>
       </c>
       <c r="AJ25">
-        <v>0.213030303030303</v>
+        <v>0.228</v>
       </c>
       <c r="AK25">
-        <v>0.2268181818181818</v>
+        <v>0.241</v>
       </c>
       <c r="AL25">
-        <v>0.2406060606060606</v>
+        <v>0.2539999999999999</v>
       </c>
       <c r="AM25">
-        <v>0.2543939393939394</v>
+        <v>0.267</v>
       </c>
       <c r="AN25">
-        <v>0.2681818181818181</v>
+        <v>0.28</v>
       </c>
       <c r="AO25">
-        <v>0.281969696969697</v>
+        <v>0.293</v>
       </c>
       <c r="AP25">
-        <v>0.2957575757575758</v>
+        <v>0.306</v>
       </c>
       <c r="AQ25">
-        <v>0.3095454545454545</v>
+        <v>0.319</v>
       </c>
       <c r="AR25">
-        <v>0.3233333333333333</v>
+        <v>0.332</v>
       </c>
       <c r="AS25">
-        <v>0.3371212121212121</v>
+        <v>0.345</v>
       </c>
       <c r="AT25">
-        <v>0.3509090909090909</v>
+        <v>0.358</v>
       </c>
       <c r="AU25">
-        <v>0.3646969696969696</v>
+        <v>0.371</v>
       </c>
       <c r="AV25">
-        <v>0.3784848484848485</v>
+        <v>0.384</v>
       </c>
       <c r="AW25">
-        <v>0.3922727272727273</v>
+        <v>0.397</v>
       </c>
       <c r="AX25">
-        <v>0.4060606060606061</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="AY25">
-        <v>0.4198484848484849</v>
+        <v>0.4229999999999999</v>
       </c>
       <c r="AZ25">
-        <v>0.4336363636363636</v>
+        <v>0.436</v>
       </c>
       <c r="BA25">
-        <v>0.4474242424242424</v>
+        <v>0.449</v>
       </c>
       <c r="BB25">
-        <v>0.4612121212121212</v>
+        <v>0.462</v>
       </c>
       <c r="BC25">
         <v>0.475</v>
@@ -40183,106 +40183,106 @@
         <v>0.015196443</v>
       </c>
       <c r="U26">
-        <v>0.015196443</v>
+        <v>0.02833368748571428</v>
       </c>
       <c r="V26">
-        <v>0.015196443</v>
+        <v>0.04147093197142857</v>
       </c>
       <c r="W26">
-        <v>0.02912988412121212</v>
+        <v>0.05460817645714285</v>
       </c>
       <c r="X26">
-        <v>0.04306332524242424</v>
+        <v>0.06774542094285714</v>
       </c>
       <c r="Y26">
-        <v>0.05699676636363636</v>
+        <v>0.08088266542857142</v>
       </c>
       <c r="Z26">
-        <v>0.07093020748484848</v>
+        <v>0.0940199099142857</v>
       </c>
       <c r="AA26">
-        <v>0.08486364860606062</v>
+        <v>0.1071571544</v>
       </c>
       <c r="AB26">
-        <v>0.09879708972727273</v>
+        <v>0.1202943988857143</v>
       </c>
       <c r="AC26">
-        <v>0.1127305308484848</v>
+        <v>0.1334316433714285</v>
       </c>
       <c r="AD26">
-        <v>0.126663971969697</v>
+        <v>0.1465688878571428</v>
       </c>
       <c r="AE26">
-        <v>0.1405974130909091</v>
+        <v>0.1597061323428571</v>
       </c>
       <c r="AF26">
-        <v>0.1545308542121212</v>
+        <v>0.1728433768285714</v>
       </c>
       <c r="AG26">
-        <v>0.1684642953333333</v>
+        <v>0.1859806213142857</v>
       </c>
       <c r="AH26">
-        <v>0.1823977364545455</v>
+        <v>0.1991178658</v>
       </c>
       <c r="AI26">
-        <v>0.1963311775757575</v>
+        <v>0.2122551102857143</v>
       </c>
       <c r="AJ26">
-        <v>0.2102646186969697</v>
+        <v>0.2253923547714286</v>
       </c>
       <c r="AK26">
-        <v>0.2241980598181818</v>
+        <v>0.2385295992571428</v>
       </c>
       <c r="AL26">
-        <v>0.2381315009393939</v>
+        <v>0.2516668437428571</v>
       </c>
       <c r="AM26">
-        <v>0.252064942060606</v>
+        <v>0.2648040882285714</v>
       </c>
       <c r="AN26">
-        <v>0.2659983831818181</v>
+        <v>0.2779413327142857</v>
       </c>
       <c r="AO26">
-        <v>0.2799318243030303</v>
+        <v>0.2910785772</v>
       </c>
       <c r="AP26">
-        <v>0.2938652654242425</v>
+        <v>0.3042158216857143</v>
       </c>
       <c r="AQ26">
-        <v>0.3077987065454545</v>
+        <v>0.3173530661714286</v>
       </c>
       <c r="AR26">
-        <v>0.3217321476666666</v>
+        <v>0.3304903106571428</v>
       </c>
       <c r="AS26">
-        <v>0.3356655887878788</v>
+        <v>0.3436275551428571</v>
       </c>
       <c r="AT26">
-        <v>0.3495990299090909</v>
+        <v>0.3567647996285714</v>
       </c>
       <c r="AU26">
-        <v>0.363532471030303</v>
+        <v>0.3699020441142857</v>
       </c>
       <c r="AV26">
-        <v>0.3774659121515151</v>
+        <v>0.3830392886</v>
       </c>
       <c r="AW26">
-        <v>0.3913993532727273</v>
+        <v>0.3961765330857143</v>
       </c>
       <c r="AX26">
-        <v>0.4053327943939394</v>
+        <v>0.4093137775714285</v>
       </c>
       <c r="AY26">
-        <v>0.4192662355151515</v>
+        <v>0.4224510220571428</v>
       </c>
       <c r="AZ26">
-        <v>0.4331996766363636</v>
+        <v>0.4355882665428571</v>
       </c>
       <c r="BA26">
-        <v>0.4471331177575757</v>
+        <v>0.4487255110285714</v>
       </c>
       <c r="BB26">
-        <v>0.4610665588787878</v>
+        <v>0.4618627555142857</v>
       </c>
       <c r="BC26">
         <v>0.475</v>
@@ -40335,106 +40335,106 @@
         <v>0.015196443</v>
       </c>
       <c r="U27">
-        <v>0.015196443</v>
+        <v>0.02833368748571428</v>
       </c>
       <c r="V27">
-        <v>0.015196443</v>
+        <v>0.04147093197142857</v>
       </c>
       <c r="W27">
-        <v>0.02912988412121212</v>
+        <v>0.05460817645714285</v>
       </c>
       <c r="X27">
-        <v>0.04306332524242424</v>
+        <v>0.06774542094285714</v>
       </c>
       <c r="Y27">
-        <v>0.05699676636363636</v>
+        <v>0.08088266542857142</v>
       </c>
       <c r="Z27">
-        <v>0.07093020748484848</v>
+        <v>0.0940199099142857</v>
       </c>
       <c r="AA27">
-        <v>0.08486364860606062</v>
+        <v>0.1071571544</v>
       </c>
       <c r="AB27">
-        <v>0.09879708972727273</v>
+        <v>0.1202943988857143</v>
       </c>
       <c r="AC27">
-        <v>0.1127305308484848</v>
+        <v>0.1334316433714285</v>
       </c>
       <c r="AD27">
-        <v>0.126663971969697</v>
+        <v>0.1465688878571428</v>
       </c>
       <c r="AE27">
-        <v>0.1405974130909091</v>
+        <v>0.1597061323428571</v>
       </c>
       <c r="AF27">
-        <v>0.1545308542121212</v>
+        <v>0.1728433768285714</v>
       </c>
       <c r="AG27">
-        <v>0.1684642953333333</v>
+        <v>0.1859806213142857</v>
       </c>
       <c r="AH27">
-        <v>0.1823977364545455</v>
+        <v>0.1991178658</v>
       </c>
       <c r="AI27">
-        <v>0.1963311775757575</v>
+        <v>0.2122551102857143</v>
       </c>
       <c r="AJ27">
-        <v>0.2102646186969697</v>
+        <v>0.2253923547714286</v>
       </c>
       <c r="AK27">
-        <v>0.2241980598181818</v>
+        <v>0.2385295992571428</v>
       </c>
       <c r="AL27">
-        <v>0.2381315009393939</v>
+        <v>0.2516668437428571</v>
       </c>
       <c r="AM27">
-        <v>0.252064942060606</v>
+        <v>0.2648040882285714</v>
       </c>
       <c r="AN27">
-        <v>0.2659983831818181</v>
+        <v>0.2779413327142857</v>
       </c>
       <c r="AO27">
-        <v>0.2799318243030303</v>
+        <v>0.2910785772</v>
       </c>
       <c r="AP27">
-        <v>0.2938652654242425</v>
+        <v>0.3042158216857143</v>
       </c>
       <c r="AQ27">
-        <v>0.3077987065454545</v>
+        <v>0.3173530661714286</v>
       </c>
       <c r="AR27">
-        <v>0.3217321476666666</v>
+        <v>0.3304903106571428</v>
       </c>
       <c r="AS27">
-        <v>0.3356655887878788</v>
+        <v>0.3436275551428571</v>
       </c>
       <c r="AT27">
-        <v>0.3495990299090909</v>
+        <v>0.3567647996285714</v>
       </c>
       <c r="AU27">
-        <v>0.363532471030303</v>
+        <v>0.3699020441142857</v>
       </c>
       <c r="AV27">
-        <v>0.3774659121515151</v>
+        <v>0.3830392886</v>
       </c>
       <c r="AW27">
-        <v>0.3913993532727273</v>
+        <v>0.3961765330857143</v>
       </c>
       <c r="AX27">
-        <v>0.4053327943939394</v>
+        <v>0.4093137775714285</v>
       </c>
       <c r="AY27">
-        <v>0.4192662355151515</v>
+        <v>0.4224510220571428</v>
       </c>
       <c r="AZ27">
-        <v>0.4331996766363636</v>
+        <v>0.4355882665428571</v>
       </c>
       <c r="BA27">
-        <v>0.4471331177575757</v>
+        <v>0.4487255110285714</v>
       </c>
       <c r="BB27">
-        <v>0.4610665588787878</v>
+        <v>0.4618627555142857</v>
       </c>
       <c r="BC27">
         <v>0.475</v>
@@ -40487,106 +40487,106 @@
         <v>0.015196443</v>
       </c>
       <c r="U28">
-        <v>0.015196443</v>
+        <v>0.02833368748571428</v>
       </c>
       <c r="V28">
-        <v>0.015196443</v>
+        <v>0.04147093197142857</v>
       </c>
       <c r="W28">
-        <v>0.02912988412121212</v>
+        <v>0.05460817645714285</v>
       </c>
       <c r="X28">
-        <v>0.04306332524242424</v>
+        <v>0.06774542094285714</v>
       </c>
       <c r="Y28">
-        <v>0.05699676636363636</v>
+        <v>0.08088266542857142</v>
       </c>
       <c r="Z28">
-        <v>0.07093020748484848</v>
+        <v>0.0940199099142857</v>
       </c>
       <c r="AA28">
-        <v>0.08486364860606062</v>
+        <v>0.1071571544</v>
       </c>
       <c r="AB28">
-        <v>0.09879708972727273</v>
+        <v>0.1202943988857143</v>
       </c>
       <c r="AC28">
-        <v>0.1127305308484848</v>
+        <v>0.1334316433714285</v>
       </c>
       <c r="AD28">
-        <v>0.126663971969697</v>
+        <v>0.1465688878571428</v>
       </c>
       <c r="AE28">
-        <v>0.1405974130909091</v>
+        <v>0.1597061323428571</v>
       </c>
       <c r="AF28">
-        <v>0.1545308542121212</v>
+        <v>0.1728433768285714</v>
       </c>
       <c r="AG28">
-        <v>0.1684642953333333</v>
+        <v>0.1859806213142857</v>
       </c>
       <c r="AH28">
-        <v>0.1823977364545455</v>
+        <v>0.1991178658</v>
       </c>
       <c r="AI28">
-        <v>0.1963311775757575</v>
+        <v>0.2122551102857143</v>
       </c>
       <c r="AJ28">
-        <v>0.2102646186969697</v>
+        <v>0.2253923547714286</v>
       </c>
       <c r="AK28">
-        <v>0.2241980598181818</v>
+        <v>0.2385295992571428</v>
       </c>
       <c r="AL28">
-        <v>0.2381315009393939</v>
+        <v>0.2516668437428571</v>
       </c>
       <c r="AM28">
-        <v>0.252064942060606</v>
+        <v>0.2648040882285714</v>
       </c>
       <c r="AN28">
-        <v>0.2659983831818181</v>
+        <v>0.2779413327142857</v>
       </c>
       <c r="AO28">
-        <v>0.2799318243030303</v>
+        <v>0.2910785772</v>
       </c>
       <c r="AP28">
-        <v>0.2938652654242425</v>
+        <v>0.3042158216857143</v>
       </c>
       <c r="AQ28">
-        <v>0.3077987065454545</v>
+        <v>0.3173530661714286</v>
       </c>
       <c r="AR28">
-        <v>0.3217321476666666</v>
+        <v>0.3304903106571428</v>
       </c>
       <c r="AS28">
-        <v>0.3356655887878788</v>
+        <v>0.3436275551428571</v>
       </c>
       <c r="AT28">
-        <v>0.3495990299090909</v>
+        <v>0.3567647996285714</v>
       </c>
       <c r="AU28">
-        <v>0.363532471030303</v>
+        <v>0.3699020441142857</v>
       </c>
       <c r="AV28">
-        <v>0.3774659121515151</v>
+        <v>0.3830392886</v>
       </c>
       <c r="AW28">
-        <v>0.3913993532727273</v>
+        <v>0.3961765330857143</v>
       </c>
       <c r="AX28">
-        <v>0.4053327943939394</v>
+        <v>0.4093137775714285</v>
       </c>
       <c r="AY28">
-        <v>0.4192662355151515</v>
+        <v>0.4224510220571428</v>
       </c>
       <c r="AZ28">
-        <v>0.4331996766363636</v>
+        <v>0.4355882665428571</v>
       </c>
       <c r="BA28">
-        <v>0.4471331177575757</v>
+        <v>0.4487255110285714</v>
       </c>
       <c r="BB28">
-        <v>0.4610665588787878</v>
+        <v>0.4618627555142857</v>
       </c>
       <c r="BC28">
         <v>0.475</v>
@@ -45883,106 +45883,106 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W16">
-        <v>0.02424242424242425</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X16">
-        <v>0.04848484848484849</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y16">
-        <v>0.07272727272727274</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z16">
-        <v>0.09696969696969698</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA16">
-        <v>0.1212121212121212</v>
+        <v>0.16</v>
       </c>
       <c r="AB16">
-        <v>0.1454545454545455</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC16">
-        <v>0.1696969696969697</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD16">
-        <v>0.193939393939394</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE16">
-        <v>0.2181818181818182</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF16">
-        <v>0.2424242424242424</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG16">
-        <v>0.2666666666666667</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH16">
-        <v>0.290909090909091</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI16">
-        <v>0.3151515151515152</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ16">
-        <v>0.3393939393939394</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK16">
-        <v>0.3636363636363636</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL16">
-        <v>0.3878787878787879</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM16">
-        <v>0.4121212121212121</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN16">
-        <v>0.4363636363636363</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO16">
-        <v>0.4606060606060607</v>
+        <v>0.48</v>
       </c>
       <c r="AP16">
-        <v>0.4848484848484849</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ16">
-        <v>0.5090909090909091</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR16">
-        <v>0.5333333333333333</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS16">
-        <v>0.5575757575757576</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT16">
-        <v>0.5818181818181819</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU16">
-        <v>0.6060606060606061</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV16">
-        <v>0.6303030303030304</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW16">
-        <v>0.6545454545454547</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX16">
-        <v>0.6787878787878788</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY16">
-        <v>0.7030303030303031</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ16">
-        <v>0.7272727272727273</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA16">
-        <v>0.7515151515151516</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB16">
-        <v>0.7757575757575759</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC16">
         <v>0.8</v>
@@ -46038,106 +46038,106 @@
         <v>0.004570438</v>
       </c>
       <c r="U17">
-        <v>0.004570438</v>
+        <v>0.004439854057142856</v>
       </c>
       <c r="V17">
-        <v>0.004570438</v>
+        <v>0.004309270114285714</v>
       </c>
       <c r="W17">
-        <v>0.004431939878787879</v>
+        <v>0.004178686171428571</v>
       </c>
       <c r="X17">
-        <v>0.004293441757575758</v>
+        <v>0.004048102228571428</v>
       </c>
       <c r="Y17">
-        <v>0.004154943636363636</v>
+        <v>0.003917518285714286</v>
       </c>
       <c r="Z17">
-        <v>0.004016445515151515</v>
+        <v>0.003786934342857142</v>
       </c>
       <c r="AA17">
-        <v>0.003877947393939394</v>
+        <v>0.0036563504</v>
       </c>
       <c r="AB17">
-        <v>0.003739449272727272</v>
+        <v>0.003525766457142857</v>
       </c>
       <c r="AC17">
-        <v>0.003600951151515151</v>
+        <v>0.003395182514285714</v>
       </c>
       <c r="AD17">
-        <v>0.00346245303030303</v>
+        <v>0.003264598571428571</v>
       </c>
       <c r="AE17">
-        <v>0.003323954909090909</v>
+        <v>0.003134014628571428</v>
       </c>
       <c r="AF17">
-        <v>0.003185456787878788</v>
+        <v>0.003003430685714285</v>
       </c>
       <c r="AG17">
-        <v>0.003046958666666667</v>
+        <v>0.002872846742857143</v>
       </c>
       <c r="AH17">
-        <v>0.002908460545454545</v>
+        <v>0.002742262799999999</v>
       </c>
       <c r="AI17">
-        <v>0.002769962424242424</v>
+        <v>0.002611678857142857</v>
       </c>
       <c r="AJ17">
-        <v>0.002631464303030303</v>
+        <v>0.002481094914285715</v>
       </c>
       <c r="AK17">
-        <v>0.002492966181818181</v>
+        <v>0.002350510971428571</v>
       </c>
       <c r="AL17">
-        <v>0.00235446806060606</v>
+        <v>0.002219927028571429</v>
       </c>
       <c r="AM17">
-        <v>0.002215969939393939</v>
+        <v>0.002089343085714286</v>
       </c>
       <c r="AN17">
-        <v>0.002077471818181818</v>
+        <v>0.001958759142857143</v>
       </c>
       <c r="AO17">
-        <v>0.001938973696969697</v>
+        <v>0.0018281752</v>
       </c>
       <c r="AP17">
-        <v>0.001800475575757575</v>
+        <v>0.001697591257142857</v>
       </c>
       <c r="AQ17">
-        <v>0.001661977454545454</v>
+        <v>0.001567007314285714</v>
       </c>
       <c r="AR17">
-        <v>0.001523479333333333</v>
+        <v>0.001436423371428571</v>
       </c>
       <c r="AS17">
-        <v>0.001384981212121212</v>
+        <v>0.001305839428571428</v>
       </c>
       <c r="AT17">
-        <v>0.001246483090909091</v>
+        <v>0.001175255485714285</v>
       </c>
       <c r="AU17">
-        <v>0.00110798496969697</v>
+        <v>0.001044671542857143</v>
       </c>
       <c r="AV17">
-        <v>0.0009694868484848486</v>
+        <v>0.0009140875999999997</v>
       </c>
       <c r="AW17">
-        <v>0.000830988727272727</v>
+        <v>0.0007835036571428568</v>
       </c>
       <c r="AX17">
-        <v>0.0006924906060606059</v>
+        <v>0.0006529197142857144</v>
       </c>
       <c r="AY17">
-        <v>0.0005539924848484848</v>
+        <v>0.0005223357714285716</v>
       </c>
       <c r="AZ17">
-        <v>0.0004154943636363637</v>
+        <v>0.0003917518285714287</v>
       </c>
       <c r="BA17">
-        <v>0.0002769962424242421</v>
+        <v>0.0002611678857142858</v>
       </c>
       <c r="BB17">
-        <v>0.0001384981212121211</v>
+        <v>0.0001305839428571429</v>
       </c>
       <c r="BC17">
         <v>0</v>
@@ -46193,106 +46193,106 @@
         <v>0.261553696</v>
       </c>
       <c r="U18">
-        <v>0.261553696</v>
+        <v>0.2569378761142857</v>
       </c>
       <c r="V18">
-        <v>0.261553696</v>
+        <v>0.2523220562285714</v>
       </c>
       <c r="W18">
-        <v>0.2566581294545455</v>
+        <v>0.2477062363428571</v>
       </c>
       <c r="X18">
-        <v>0.2517625629090909</v>
+        <v>0.2430904164571429</v>
       </c>
       <c r="Y18">
-        <v>0.2468669963636363</v>
+        <v>0.2384745965714286</v>
       </c>
       <c r="Z18">
-        <v>0.2419714298181818</v>
+        <v>0.2338587766857143</v>
       </c>
       <c r="AA18">
-        <v>0.2370758632727273</v>
+        <v>0.2292429568</v>
       </c>
       <c r="AB18">
-        <v>0.2321802967272727</v>
+        <v>0.2246271369142857</v>
       </c>
       <c r="AC18">
-        <v>0.2272847301818182</v>
+        <v>0.2200113170285714</v>
       </c>
       <c r="AD18">
-        <v>0.2223891636363636</v>
+        <v>0.2153954971428572</v>
       </c>
       <c r="AE18">
-        <v>0.2174935970909091</v>
+        <v>0.2107796772571429</v>
       </c>
       <c r="AF18">
-        <v>0.2125980305454546</v>
+        <v>0.2061638573714286</v>
       </c>
       <c r="AG18">
-        <v>0.207702464</v>
+        <v>0.2015480374857143</v>
       </c>
       <c r="AH18">
-        <v>0.2028068974545455</v>
+        <v>0.1969322176</v>
       </c>
       <c r="AI18">
-        <v>0.1979113309090909</v>
+        <v>0.1923163977142857</v>
       </c>
       <c r="AJ18">
-        <v>0.1930157643636363</v>
+        <v>0.1877005778285714</v>
       </c>
       <c r="AK18">
-        <v>0.1881201978181818</v>
+        <v>0.1830847579428571</v>
       </c>
       <c r="AL18">
-        <v>0.1832246312727273</v>
+        <v>0.1784689380571429</v>
       </c>
       <c r="AM18">
-        <v>0.1783290647272727</v>
+        <v>0.1738531181714286</v>
       </c>
       <c r="AN18">
-        <v>0.1734334981818182</v>
+        <v>0.1692372982857143</v>
       </c>
       <c r="AO18">
-        <v>0.1685379316363636</v>
+        <v>0.1646214784</v>
       </c>
       <c r="AP18">
-        <v>0.1636423650909091</v>
+        <v>0.1600056585142857</v>
       </c>
       <c r="AQ18">
-        <v>0.1587467985454545</v>
+        <v>0.1553898386285714</v>
       </c>
       <c r="AR18">
-        <v>0.153851232</v>
+        <v>0.1507740187428571</v>
       </c>
       <c r="AS18">
-        <v>0.1489556654545454</v>
+        <v>0.1461581988571429</v>
       </c>
       <c r="AT18">
-        <v>0.1440600989090909</v>
+        <v>0.1415423789714286</v>
       </c>
       <c r="AU18">
-        <v>0.1391645323636364</v>
+        <v>0.1369265590857143</v>
       </c>
       <c r="AV18">
-        <v>0.1342689658181818</v>
+        <v>0.1323107392</v>
       </c>
       <c r="AW18">
-        <v>0.1293733992727273</v>
+        <v>0.1276949193142857</v>
       </c>
       <c r="AX18">
-        <v>0.1244778327272727</v>
+        <v>0.1230790994285714</v>
       </c>
       <c r="AY18">
-        <v>0.1195822661818182</v>
+        <v>0.1184632795428572</v>
       </c>
       <c r="AZ18">
-        <v>0.1146866996363636</v>
+        <v>0.1138474596571429</v>
       </c>
       <c r="BA18">
-        <v>0.1097911330909091</v>
+        <v>0.1092316397714286</v>
       </c>
       <c r="BB18">
-        <v>0.1048955665454546</v>
+        <v>0.1046158198857143</v>
       </c>
       <c r="BC18">
         <v>0.1</v>
@@ -46348,106 +46348,106 @@
         <v>0.261553696</v>
       </c>
       <c r="U19">
-        <v>0.261553696</v>
+        <v>0.2569378761142857</v>
       </c>
       <c r="V19">
-        <v>0.261553696</v>
+        <v>0.2523220562285714</v>
       </c>
       <c r="W19">
-        <v>0.2566581294545455</v>
+        <v>0.2477062363428571</v>
       </c>
       <c r="X19">
-        <v>0.2517625629090909</v>
+        <v>0.2430904164571429</v>
       </c>
       <c r="Y19">
-        <v>0.2468669963636363</v>
+        <v>0.2384745965714286</v>
       </c>
       <c r="Z19">
-        <v>0.2419714298181818</v>
+        <v>0.2338587766857143</v>
       </c>
       <c r="AA19">
-        <v>0.2370758632727273</v>
+        <v>0.2292429568</v>
       </c>
       <c r="AB19">
-        <v>0.2321802967272727</v>
+        <v>0.2246271369142857</v>
       </c>
       <c r="AC19">
-        <v>0.2272847301818182</v>
+        <v>0.2200113170285714</v>
       </c>
       <c r="AD19">
-        <v>0.2223891636363636</v>
+        <v>0.2153954971428572</v>
       </c>
       <c r="AE19">
-        <v>0.2174935970909091</v>
+        <v>0.2107796772571429</v>
       </c>
       <c r="AF19">
-        <v>0.2125980305454546</v>
+        <v>0.2061638573714286</v>
       </c>
       <c r="AG19">
-        <v>0.207702464</v>
+        <v>0.2015480374857143</v>
       </c>
       <c r="AH19">
-        <v>0.2028068974545455</v>
+        <v>0.1969322176</v>
       </c>
       <c r="AI19">
-        <v>0.1979113309090909</v>
+        <v>0.1923163977142857</v>
       </c>
       <c r="AJ19">
-        <v>0.1930157643636363</v>
+        <v>0.1877005778285714</v>
       </c>
       <c r="AK19">
-        <v>0.1881201978181818</v>
+        <v>0.1830847579428571</v>
       </c>
       <c r="AL19">
-        <v>0.1832246312727273</v>
+        <v>0.1784689380571429</v>
       </c>
       <c r="AM19">
-        <v>0.1783290647272727</v>
+        <v>0.1738531181714286</v>
       </c>
       <c r="AN19">
-        <v>0.1734334981818182</v>
+        <v>0.1692372982857143</v>
       </c>
       <c r="AO19">
-        <v>0.1685379316363636</v>
+        <v>0.1646214784</v>
       </c>
       <c r="AP19">
-        <v>0.1636423650909091</v>
+        <v>0.1600056585142857</v>
       </c>
       <c r="AQ19">
-        <v>0.1587467985454545</v>
+        <v>0.1553898386285714</v>
       </c>
       <c r="AR19">
-        <v>0.153851232</v>
+        <v>0.1507740187428571</v>
       </c>
       <c r="AS19">
-        <v>0.1489556654545454</v>
+        <v>0.1461581988571429</v>
       </c>
       <c r="AT19">
-        <v>0.1440600989090909</v>
+        <v>0.1415423789714286</v>
       </c>
       <c r="AU19">
-        <v>0.1391645323636364</v>
+        <v>0.1369265590857143</v>
       </c>
       <c r="AV19">
-        <v>0.1342689658181818</v>
+        <v>0.1323107392</v>
       </c>
       <c r="AW19">
-        <v>0.1293733992727273</v>
+        <v>0.1276949193142857</v>
       </c>
       <c r="AX19">
-        <v>0.1244778327272727</v>
+        <v>0.1230790994285714</v>
       </c>
       <c r="AY19">
-        <v>0.1195822661818182</v>
+        <v>0.1184632795428572</v>
       </c>
       <c r="AZ19">
-        <v>0.1146866996363636</v>
+        <v>0.1138474596571429</v>
       </c>
       <c r="BA19">
-        <v>0.1097911330909091</v>
+        <v>0.1092316397714286</v>
       </c>
       <c r="BB19">
-        <v>0.1048955665454546</v>
+        <v>0.1046158198857143</v>
       </c>
       <c r="BC19">
         <v>0.1</v>
@@ -46503,106 +46503,106 @@
         <v>0.073899806</v>
       </c>
       <c r="U20">
-        <v>0.073899806</v>
+        <v>0.07178838297142857</v>
       </c>
       <c r="V20">
-        <v>0.073899806</v>
+        <v>0.06967695994285714</v>
       </c>
       <c r="W20">
-        <v>0.07166041793939394</v>
+        <v>0.06756553691428571</v>
       </c>
       <c r="X20">
-        <v>0.06942102987878788</v>
+        <v>0.06545411388571429</v>
       </c>
       <c r="Y20">
-        <v>0.06718164181818181</v>
+        <v>0.06334269085714286</v>
       </c>
       <c r="Z20">
-        <v>0.06494225375757576</v>
+        <v>0.06123126782857143</v>
       </c>
       <c r="AA20">
-        <v>0.0627028656969697</v>
+        <v>0.0591198448</v>
       </c>
       <c r="AB20">
-        <v>0.06046347763636363</v>
+        <v>0.05700842177142857</v>
       </c>
       <c r="AC20">
-        <v>0.05822408957575757</v>
+        <v>0.05489699874285715</v>
       </c>
       <c r="AD20">
-        <v>0.05598470151515152</v>
+        <v>0.05278557571428572</v>
       </c>
       <c r="AE20">
-        <v>0.05374531345454545</v>
+        <v>0.05067415268571428</v>
       </c>
       <c r="AF20">
-        <v>0.0515059253939394</v>
+        <v>0.04856272965714285</v>
       </c>
       <c r="AG20">
-        <v>0.04926653733333334</v>
+        <v>0.04645130662857143</v>
       </c>
       <c r="AH20">
-        <v>0.04702714927272727</v>
+        <v>0.0443398836</v>
       </c>
       <c r="AI20">
-        <v>0.04478776121212121</v>
+        <v>0.04222846057142857</v>
       </c>
       <c r="AJ20">
-        <v>0.04254837315151515</v>
+        <v>0.04011703754285715</v>
       </c>
       <c r="AK20">
-        <v>0.04030898509090908</v>
+        <v>0.03800561451428571</v>
       </c>
       <c r="AL20">
-        <v>0.03806959703030303</v>
+        <v>0.03589419148571429</v>
       </c>
       <c r="AM20">
-        <v>0.03583020896969697</v>
+        <v>0.03378276845714286</v>
       </c>
       <c r="AN20">
-        <v>0.03359082090909091</v>
+        <v>0.03167134542857143</v>
       </c>
       <c r="AO20">
-        <v>0.03135143284848484</v>
+        <v>0.0295599224</v>
       </c>
       <c r="AP20">
-        <v>0.02911204478787879</v>
+        <v>0.02744849937142857</v>
       </c>
       <c r="AQ20">
-        <v>0.02687265672727273</v>
+        <v>0.02533707634285714</v>
       </c>
       <c r="AR20">
-        <v>0.02463326866666667</v>
+        <v>0.02322565331428571</v>
       </c>
       <c r="AS20">
-        <v>0.0223938806060606</v>
+        <v>0.02111423028571428</v>
       </c>
       <c r="AT20">
-        <v>0.02015449254545454</v>
+        <v>0.01900280725714286</v>
       </c>
       <c r="AU20">
-        <v>0.01791510448484849</v>
+        <v>0.01689138422857142</v>
       </c>
       <c r="AV20">
-        <v>0.01567571642424243</v>
+        <v>0.0147799612</v>
       </c>
       <c r="AW20">
-        <v>0.01343632836363636</v>
+        <v>0.01266853817142857</v>
       </c>
       <c r="AX20">
-        <v>0.0111969403030303</v>
+        <v>0.01055711514285715</v>
       </c>
       <c r="AY20">
-        <v>0.008957552242424243</v>
+        <v>0.008445692114285717</v>
       </c>
       <c r="AZ20">
-        <v>0.006718164181818184</v>
+        <v>0.006334269085714288</v>
       </c>
       <c r="BA20">
-        <v>0.004478776121212117</v>
+        <v>0.004222846057142859</v>
       </c>
       <c r="BB20">
-        <v>0.002239388060606059</v>
+        <v>0.002111423028571429</v>
       </c>
       <c r="BC20">
         <v>0</v>
@@ -46658,106 +46658,106 @@
         <v>0.398422364</v>
       </c>
       <c r="U21">
-        <v>0.398422364</v>
+        <v>0.3870388678857142</v>
       </c>
       <c r="V21">
-        <v>0.398422364</v>
+        <v>0.3756553717714285</v>
       </c>
       <c r="W21">
-        <v>0.386348959030303</v>
+        <v>0.3642718756571428</v>
       </c>
       <c r="X21">
-        <v>0.374275554060606</v>
+        <v>0.3528883795428571</v>
       </c>
       <c r="Y21">
-        <v>0.362202149090909</v>
+        <v>0.3415048834285714</v>
       </c>
       <c r="Z21">
-        <v>0.3501287441212121</v>
+        <v>0.3301213873142857</v>
       </c>
       <c r="AA21">
-        <v>0.3380553391515151</v>
+        <v>0.3187378912</v>
       </c>
       <c r="AB21">
-        <v>0.3259819341818181</v>
+        <v>0.3073543950857143</v>
       </c>
       <c r="AC21">
-        <v>0.3139085292121212</v>
+        <v>0.2959708989714286</v>
       </c>
       <c r="AD21">
-        <v>0.3018351242424242</v>
+        <v>0.2845874028571428</v>
       </c>
       <c r="AE21">
-        <v>0.2897617192727273</v>
+        <v>0.2732039067428571</v>
       </c>
       <c r="AF21">
-        <v>0.2776883143030303</v>
+        <v>0.2618204106285714</v>
       </c>
       <c r="AG21">
-        <v>0.2656149093333334</v>
+        <v>0.2504369145142857</v>
       </c>
       <c r="AH21">
-        <v>0.2535415043636363</v>
+        <v>0.2390534184</v>
       </c>
       <c r="AI21">
-        <v>0.2414680993939394</v>
+        <v>0.2276699222857143</v>
       </c>
       <c r="AJ21">
-        <v>0.2293946944242424</v>
+        <v>0.2162864261714286</v>
       </c>
       <c r="AK21">
-        <v>0.2173212894545454</v>
+        <v>0.2049029300571428</v>
       </c>
       <c r="AL21">
-        <v>0.2052478844848485</v>
+        <v>0.1935194339428571</v>
       </c>
       <c r="AM21">
-        <v>0.1931744795151515</v>
+        <v>0.1821359378285714</v>
       </c>
       <c r="AN21">
-        <v>0.1811010745454545</v>
+        <v>0.1707524417142857</v>
       </c>
       <c r="AO21">
-        <v>0.1690276695757575</v>
+        <v>0.1593689456</v>
       </c>
       <c r="AP21">
-        <v>0.1569542646060606</v>
+        <v>0.1479854494857143</v>
       </c>
       <c r="AQ21">
-        <v>0.1448808596363636</v>
+        <v>0.1366019533714286</v>
       </c>
       <c r="AR21">
-        <v>0.1328074546666667</v>
+        <v>0.1252184572571428</v>
       </c>
       <c r="AS21">
-        <v>0.1207340496969697</v>
+        <v>0.1138349611428571</v>
       </c>
       <c r="AT21">
-        <v>0.1086606447272727</v>
+        <v>0.1024514650285714</v>
       </c>
       <c r="AU21">
-        <v>0.09658723975757576</v>
+        <v>0.09106796891428569</v>
       </c>
       <c r="AV21">
-        <v>0.0845138347878788</v>
+        <v>0.07968447279999998</v>
       </c>
       <c r="AW21">
-        <v>0.07244042981818179</v>
+        <v>0.06830097668571426</v>
       </c>
       <c r="AX21">
-        <v>0.06036702484848484</v>
+        <v>0.05691748057142858</v>
       </c>
       <c r="AY21">
-        <v>0.04829361987878788</v>
+        <v>0.04553398445714287</v>
       </c>
       <c r="AZ21">
-        <v>0.03622021490909092</v>
+        <v>0.03415048834285715</v>
       </c>
       <c r="BA21">
-        <v>0.02414680993939392</v>
+        <v>0.02276699222857144</v>
       </c>
       <c r="BB21">
-        <v>0.01207340496969696</v>
+        <v>0.01138349611428572</v>
       </c>
       <c r="BC21">
         <v>0</v>
@@ -46962,106 +46962,106 @@
         <v>0.02</v>
       </c>
       <c r="U23">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="V23">
-        <v>0.02</v>
+        <v>0.046</v>
       </c>
       <c r="W23">
-        <v>0.03378787878787878</v>
+        <v>0.059</v>
       </c>
       <c r="X23">
-        <v>0.04757575757575758</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y23">
-        <v>0.06136363636363636</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="Z23">
-        <v>0.07515151515151515</v>
+        <v>0.09799999999999999</v>
       </c>
       <c r="AA23">
-        <v>0.08893939393939394</v>
+        <v>0.111</v>
       </c>
       <c r="AB23">
-        <v>0.1027272727272727</v>
+        <v>0.124</v>
       </c>
       <c r="AC23">
-        <v>0.1165151515151515</v>
+        <v>0.137</v>
       </c>
       <c r="AD23">
-        <v>0.1303030303030303</v>
+        <v>0.15</v>
       </c>
       <c r="AE23">
-        <v>0.1440909090909091</v>
+        <v>0.163</v>
       </c>
       <c r="AF23">
-        <v>0.1578787878787879</v>
+        <v>0.176</v>
       </c>
       <c r="AG23">
-        <v>0.1716666666666667</v>
+        <v>0.189</v>
       </c>
       <c r="AH23">
-        <v>0.1854545454545455</v>
+        <v>0.202</v>
       </c>
       <c r="AI23">
-        <v>0.1992424242424242</v>
+        <v>0.215</v>
       </c>
       <c r="AJ23">
-        <v>0.213030303030303</v>
+        <v>0.228</v>
       </c>
       <c r="AK23">
-        <v>0.2268181818181818</v>
+        <v>0.241</v>
       </c>
       <c r="AL23">
-        <v>0.2406060606060606</v>
+        <v>0.2539999999999999</v>
       </c>
       <c r="AM23">
-        <v>0.2543939393939394</v>
+        <v>0.267</v>
       </c>
       <c r="AN23">
-        <v>0.2681818181818181</v>
+        <v>0.28</v>
       </c>
       <c r="AO23">
-        <v>0.281969696969697</v>
+        <v>0.293</v>
       </c>
       <c r="AP23">
-        <v>0.2957575757575758</v>
+        <v>0.306</v>
       </c>
       <c r="AQ23">
-        <v>0.3095454545454545</v>
+        <v>0.319</v>
       </c>
       <c r="AR23">
-        <v>0.3233333333333333</v>
+        <v>0.332</v>
       </c>
       <c r="AS23">
-        <v>0.3371212121212121</v>
+        <v>0.345</v>
       </c>
       <c r="AT23">
-        <v>0.3509090909090909</v>
+        <v>0.358</v>
       </c>
       <c r="AU23">
-        <v>0.3646969696969696</v>
+        <v>0.371</v>
       </c>
       <c r="AV23">
-        <v>0.3784848484848485</v>
+        <v>0.384</v>
       </c>
       <c r="AW23">
-        <v>0.3922727272727273</v>
+        <v>0.397</v>
       </c>
       <c r="AX23">
-        <v>0.4060606060606061</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="AY23">
-        <v>0.4198484848484849</v>
+        <v>0.4229999999999999</v>
       </c>
       <c r="AZ23">
-        <v>0.4336363636363636</v>
+        <v>0.436</v>
       </c>
       <c r="BA23">
-        <v>0.4474242424242424</v>
+        <v>0.449</v>
       </c>
       <c r="BB23">
-        <v>0.4612121212121212</v>
+        <v>0.462</v>
       </c>
       <c r="BC23">
         <v>0.475</v>
@@ -47114,106 +47114,106 @@
         <v>0.4</v>
       </c>
       <c r="U24">
-        <v>0.4</v>
+        <v>0.4021428571428571</v>
       </c>
       <c r="V24">
-        <v>0.4</v>
+        <v>0.4042857142857143</v>
       </c>
       <c r="W24">
-        <v>0.4022727272727273</v>
+        <v>0.4064285714285714</v>
       </c>
       <c r="X24">
-        <v>0.4045454545454546</v>
+        <v>0.4085714285714286</v>
       </c>
       <c r="Y24">
-        <v>0.4068181818181819</v>
+        <v>0.4107142857142858</v>
       </c>
       <c r="Z24">
-        <v>0.4090909090909091</v>
+        <v>0.4128571428571428</v>
       </c>
       <c r="AA24">
-        <v>0.4113636363636364</v>
+        <v>0.415</v>
       </c>
       <c r="AB24">
-        <v>0.4136363636363636</v>
+        <v>0.4171428571428571</v>
       </c>
       <c r="AC24">
-        <v>0.415909090909091</v>
+        <v>0.4192857142857143</v>
       </c>
       <c r="AD24">
-        <v>0.4181818181818182</v>
+        <v>0.4214285714285715</v>
       </c>
       <c r="AE24">
-        <v>0.4204545454545455</v>
+        <v>0.4235714285714286</v>
       </c>
       <c r="AF24">
-        <v>0.4227272727272727</v>
+        <v>0.4257142857142857</v>
       </c>
       <c r="AG24">
-        <v>0.425</v>
+        <v>0.4278571428571429</v>
       </c>
       <c r="AH24">
-        <v>0.4272727272727273</v>
+        <v>0.43</v>
       </c>
       <c r="AI24">
-        <v>0.4295454545454546</v>
+        <v>0.4321428571428571</v>
       </c>
       <c r="AJ24">
-        <v>0.4318181818181818</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AK24">
-        <v>0.4340909090909091</v>
+        <v>0.4364285714285714</v>
       </c>
       <c r="AL24">
-        <v>0.4363636363636363</v>
+        <v>0.4385714285714286</v>
       </c>
       <c r="AM24">
-        <v>0.4386363636363637</v>
+        <v>0.4407142857142857</v>
       </c>
       <c r="AN24">
-        <v>0.4409090909090909</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="AO24">
-        <v>0.4431818181818182</v>
+        <v>0.445</v>
       </c>
       <c r="AP24">
-        <v>0.4454545454545455</v>
+        <v>0.4471428571428571</v>
       </c>
       <c r="AQ24">
-        <v>0.4477272727272728</v>
+        <v>0.4492857142857143</v>
       </c>
       <c r="AR24">
-        <v>0.45</v>
+        <v>0.4514285714285714</v>
       </c>
       <c r="AS24">
-        <v>0.4522727272727273</v>
+        <v>0.4535714285714286</v>
       </c>
       <c r="AT24">
-        <v>0.4545454545454545</v>
+        <v>0.4557142857142857</v>
       </c>
       <c r="AU24">
-        <v>0.4568181818181818</v>
+        <v>0.4578571428571429</v>
       </c>
       <c r="AV24">
-        <v>0.4590909090909091</v>
+        <v>0.46</v>
       </c>
       <c r="AW24">
-        <v>0.4613636363636364</v>
+        <v>0.4621428571428571</v>
       </c>
       <c r="AX24">
-        <v>0.4636363636363636</v>
+        <v>0.4642857142857142</v>
       </c>
       <c r="AY24">
-        <v>0.4659090909090909</v>
+        <v>0.4664285714285714</v>
       </c>
       <c r="AZ24">
-        <v>0.4681818181818181</v>
+        <v>0.4685714285714286</v>
       </c>
       <c r="BA24">
-        <v>0.4704545454545455</v>
+        <v>0.4707142857142857</v>
       </c>
       <c r="BB24">
-        <v>0.4727272727272727</v>
+        <v>0.4728571428571429</v>
       </c>
       <c r="BC24">
         <v>0.475</v>
@@ -47266,106 +47266,106 @@
         <v>0.02</v>
       </c>
       <c r="U25">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="V25">
-        <v>0.02</v>
+        <v>0.046</v>
       </c>
       <c r="W25">
-        <v>0.03378787878787878</v>
+        <v>0.059</v>
       </c>
       <c r="X25">
-        <v>0.04757575757575758</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y25">
-        <v>0.06136363636363636</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="Z25">
-        <v>0.07515151515151515</v>
+        <v>0.09799999999999999</v>
       </c>
       <c r="AA25">
-        <v>0.08893939393939394</v>
+        <v>0.111</v>
       </c>
       <c r="AB25">
-        <v>0.1027272727272727</v>
+        <v>0.124</v>
       </c>
       <c r="AC25">
-        <v>0.1165151515151515</v>
+        <v>0.137</v>
       </c>
       <c r="AD25">
-        <v>0.1303030303030303</v>
+        <v>0.15</v>
       </c>
       <c r="AE25">
-        <v>0.1440909090909091</v>
+        <v>0.163</v>
       </c>
       <c r="AF25">
-        <v>0.1578787878787879</v>
+        <v>0.176</v>
       </c>
       <c r="AG25">
-        <v>0.1716666666666667</v>
+        <v>0.189</v>
       </c>
       <c r="AH25">
-        <v>0.1854545454545455</v>
+        <v>0.202</v>
       </c>
       <c r="AI25">
-        <v>0.1992424242424242</v>
+        <v>0.215</v>
       </c>
       <c r="AJ25">
-        <v>0.213030303030303</v>
+        <v>0.228</v>
       </c>
       <c r="AK25">
-        <v>0.2268181818181818</v>
+        <v>0.241</v>
       </c>
       <c r="AL25">
-        <v>0.2406060606060606</v>
+        <v>0.2539999999999999</v>
       </c>
       <c r="AM25">
-        <v>0.2543939393939394</v>
+        <v>0.267</v>
       </c>
       <c r="AN25">
-        <v>0.2681818181818181</v>
+        <v>0.28</v>
       </c>
       <c r="AO25">
-        <v>0.281969696969697</v>
+        <v>0.293</v>
       </c>
       <c r="AP25">
-        <v>0.2957575757575758</v>
+        <v>0.306</v>
       </c>
       <c r="AQ25">
-        <v>0.3095454545454545</v>
+        <v>0.319</v>
       </c>
       <c r="AR25">
-        <v>0.3233333333333333</v>
+        <v>0.332</v>
       </c>
       <c r="AS25">
-        <v>0.3371212121212121</v>
+        <v>0.345</v>
       </c>
       <c r="AT25">
-        <v>0.3509090909090909</v>
+        <v>0.358</v>
       </c>
       <c r="AU25">
-        <v>0.3646969696969696</v>
+        <v>0.371</v>
       </c>
       <c r="AV25">
-        <v>0.3784848484848485</v>
+        <v>0.384</v>
       </c>
       <c r="AW25">
-        <v>0.3922727272727273</v>
+        <v>0.397</v>
       </c>
       <c r="AX25">
-        <v>0.4060606060606061</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="AY25">
-        <v>0.4198484848484849</v>
+        <v>0.4229999999999999</v>
       </c>
       <c r="AZ25">
-        <v>0.4336363636363636</v>
+        <v>0.436</v>
       </c>
       <c r="BA25">
-        <v>0.4474242424242424</v>
+        <v>0.449</v>
       </c>
       <c r="BB25">
-        <v>0.4612121212121212</v>
+        <v>0.462</v>
       </c>
       <c r="BC25">
         <v>0.475</v>
@@ -47418,106 +47418,106 @@
         <v>0.015196443</v>
       </c>
       <c r="U26">
-        <v>0.015196443</v>
+        <v>0.02833368748571428</v>
       </c>
       <c r="V26">
-        <v>0.015196443</v>
+        <v>0.04147093197142857</v>
       </c>
       <c r="W26">
-        <v>0.02912988412121212</v>
+        <v>0.05460817645714285</v>
       </c>
       <c r="X26">
-        <v>0.04306332524242424</v>
+        <v>0.06774542094285714</v>
       </c>
       <c r="Y26">
-        <v>0.05699676636363636</v>
+        <v>0.08088266542857142</v>
       </c>
       <c r="Z26">
-        <v>0.07093020748484848</v>
+        <v>0.0940199099142857</v>
       </c>
       <c r="AA26">
-        <v>0.08486364860606062</v>
+        <v>0.1071571544</v>
       </c>
       <c r="AB26">
-        <v>0.09879708972727273</v>
+        <v>0.1202943988857143</v>
       </c>
       <c r="AC26">
-        <v>0.1127305308484848</v>
+        <v>0.1334316433714285</v>
       </c>
       <c r="AD26">
-        <v>0.126663971969697</v>
+        <v>0.1465688878571428</v>
       </c>
       <c r="AE26">
-        <v>0.1405974130909091</v>
+        <v>0.1597061323428571</v>
       </c>
       <c r="AF26">
-        <v>0.1545308542121212</v>
+        <v>0.1728433768285714</v>
       </c>
       <c r="AG26">
-        <v>0.1684642953333333</v>
+        <v>0.1859806213142857</v>
       </c>
       <c r="AH26">
-        <v>0.1823977364545455</v>
+        <v>0.1991178658</v>
       </c>
       <c r="AI26">
-        <v>0.1963311775757575</v>
+        <v>0.2122551102857143</v>
       </c>
       <c r="AJ26">
-        <v>0.2102646186969697</v>
+        <v>0.2253923547714286</v>
       </c>
       <c r="AK26">
-        <v>0.2241980598181818</v>
+        <v>0.2385295992571428</v>
       </c>
       <c r="AL26">
-        <v>0.2381315009393939</v>
+        <v>0.2516668437428571</v>
       </c>
       <c r="AM26">
-        <v>0.252064942060606</v>
+        <v>0.2648040882285714</v>
       </c>
       <c r="AN26">
-        <v>0.2659983831818181</v>
+        <v>0.2779413327142857</v>
       </c>
       <c r="AO26">
-        <v>0.2799318243030303</v>
+        <v>0.2910785772</v>
       </c>
       <c r="AP26">
-        <v>0.2938652654242425</v>
+        <v>0.3042158216857143</v>
       </c>
       <c r="AQ26">
-        <v>0.3077987065454545</v>
+        <v>0.3173530661714286</v>
       </c>
       <c r="AR26">
-        <v>0.3217321476666666</v>
+        <v>0.3304903106571428</v>
       </c>
       <c r="AS26">
-        <v>0.3356655887878788</v>
+        <v>0.3436275551428571</v>
       </c>
       <c r="AT26">
-        <v>0.3495990299090909</v>
+        <v>0.3567647996285714</v>
       </c>
       <c r="AU26">
-        <v>0.363532471030303</v>
+        <v>0.3699020441142857</v>
       </c>
       <c r="AV26">
-        <v>0.3774659121515151</v>
+        <v>0.3830392886</v>
       </c>
       <c r="AW26">
-        <v>0.3913993532727273</v>
+        <v>0.3961765330857143</v>
       </c>
       <c r="AX26">
-        <v>0.4053327943939394</v>
+        <v>0.4093137775714285</v>
       </c>
       <c r="AY26">
-        <v>0.4192662355151515</v>
+        <v>0.4224510220571428</v>
       </c>
       <c r="AZ26">
-        <v>0.4331996766363636</v>
+        <v>0.4355882665428571</v>
       </c>
       <c r="BA26">
-        <v>0.4471331177575757</v>
+        <v>0.4487255110285714</v>
       </c>
       <c r="BB26">
-        <v>0.4610665588787878</v>
+        <v>0.4618627555142857</v>
       </c>
       <c r="BC26">
         <v>0.475</v>
@@ -47570,106 +47570,106 @@
         <v>0.015196443</v>
       </c>
       <c r="U27">
-        <v>0.015196443</v>
+        <v>0.02833368748571428</v>
       </c>
       <c r="V27">
-        <v>0.015196443</v>
+        <v>0.04147093197142857</v>
       </c>
       <c r="W27">
-        <v>0.02912988412121212</v>
+        <v>0.05460817645714285</v>
       </c>
       <c r="X27">
-        <v>0.04306332524242424</v>
+        <v>0.06774542094285714</v>
       </c>
       <c r="Y27">
-        <v>0.05699676636363636</v>
+        <v>0.08088266542857142</v>
       </c>
       <c r="Z27">
-        <v>0.07093020748484848</v>
+        <v>0.0940199099142857</v>
       </c>
       <c r="AA27">
-        <v>0.08486364860606062</v>
+        <v>0.1071571544</v>
       </c>
       <c r="AB27">
-        <v>0.09879708972727273</v>
+        <v>0.1202943988857143</v>
       </c>
       <c r="AC27">
-        <v>0.1127305308484848</v>
+        <v>0.1334316433714285</v>
       </c>
       <c r="AD27">
-        <v>0.126663971969697</v>
+        <v>0.1465688878571428</v>
       </c>
       <c r="AE27">
-        <v>0.1405974130909091</v>
+        <v>0.1597061323428571</v>
       </c>
       <c r="AF27">
-        <v>0.1545308542121212</v>
+        <v>0.1728433768285714</v>
       </c>
       <c r="AG27">
-        <v>0.1684642953333333</v>
+        <v>0.1859806213142857</v>
       </c>
       <c r="AH27">
-        <v>0.1823977364545455</v>
+        <v>0.1991178658</v>
       </c>
       <c r="AI27">
-        <v>0.1963311775757575</v>
+        <v>0.2122551102857143</v>
       </c>
       <c r="AJ27">
-        <v>0.2102646186969697</v>
+        <v>0.2253923547714286</v>
       </c>
       <c r="AK27">
-        <v>0.2241980598181818</v>
+        <v>0.2385295992571428</v>
       </c>
       <c r="AL27">
-        <v>0.2381315009393939</v>
+        <v>0.2516668437428571</v>
       </c>
       <c r="AM27">
-        <v>0.252064942060606</v>
+        <v>0.2648040882285714</v>
       </c>
       <c r="AN27">
-        <v>0.2659983831818181</v>
+        <v>0.2779413327142857</v>
       </c>
       <c r="AO27">
-        <v>0.2799318243030303</v>
+        <v>0.2910785772</v>
       </c>
       <c r="AP27">
-        <v>0.2938652654242425</v>
+        <v>0.3042158216857143</v>
       </c>
       <c r="AQ27">
-        <v>0.3077987065454545</v>
+        <v>0.3173530661714286</v>
       </c>
       <c r="AR27">
-        <v>0.3217321476666666</v>
+        <v>0.3304903106571428</v>
       </c>
       <c r="AS27">
-        <v>0.3356655887878788</v>
+        <v>0.3436275551428571</v>
       </c>
       <c r="AT27">
-        <v>0.3495990299090909</v>
+        <v>0.3567647996285714</v>
       </c>
       <c r="AU27">
-        <v>0.363532471030303</v>
+        <v>0.3699020441142857</v>
       </c>
       <c r="AV27">
-        <v>0.3774659121515151</v>
+        <v>0.3830392886</v>
       </c>
       <c r="AW27">
-        <v>0.3913993532727273</v>
+        <v>0.3961765330857143</v>
       </c>
       <c r="AX27">
-        <v>0.4053327943939394</v>
+        <v>0.4093137775714285</v>
       </c>
       <c r="AY27">
-        <v>0.4192662355151515</v>
+        <v>0.4224510220571428</v>
       </c>
       <c r="AZ27">
-        <v>0.4331996766363636</v>
+        <v>0.4355882665428571</v>
       </c>
       <c r="BA27">
-        <v>0.4471331177575757</v>
+        <v>0.4487255110285714</v>
       </c>
       <c r="BB27">
-        <v>0.4610665588787878</v>
+        <v>0.4618627555142857</v>
       </c>
       <c r="BC27">
         <v>0.475</v>
@@ -47722,106 +47722,106 @@
         <v>0.015196443</v>
       </c>
       <c r="U28">
-        <v>0.015196443</v>
+        <v>0.02833368748571428</v>
       </c>
       <c r="V28">
-        <v>0.015196443</v>
+        <v>0.04147093197142857</v>
       </c>
       <c r="W28">
-        <v>0.02912988412121212</v>
+        <v>0.05460817645714285</v>
       </c>
       <c r="X28">
-        <v>0.04306332524242424</v>
+        <v>0.06774542094285714</v>
       </c>
       <c r="Y28">
-        <v>0.05699676636363636</v>
+        <v>0.08088266542857142</v>
       </c>
       <c r="Z28">
-        <v>0.07093020748484848</v>
+        <v>0.0940199099142857</v>
       </c>
       <c r="AA28">
-        <v>0.08486364860606062</v>
+        <v>0.1071571544</v>
       </c>
       <c r="AB28">
-        <v>0.09879708972727273</v>
+        <v>0.1202943988857143</v>
       </c>
       <c r="AC28">
-        <v>0.1127305308484848</v>
+        <v>0.1334316433714285</v>
       </c>
       <c r="AD28">
-        <v>0.126663971969697</v>
+        <v>0.1465688878571428</v>
       </c>
       <c r="AE28">
-        <v>0.1405974130909091</v>
+        <v>0.1597061323428571</v>
       </c>
       <c r="AF28">
-        <v>0.1545308542121212</v>
+        <v>0.1728433768285714</v>
       </c>
       <c r="AG28">
-        <v>0.1684642953333333</v>
+        <v>0.1859806213142857</v>
       </c>
       <c r="AH28">
-        <v>0.1823977364545455</v>
+        <v>0.1991178658</v>
       </c>
       <c r="AI28">
-        <v>0.1963311775757575</v>
+        <v>0.2122551102857143</v>
       </c>
       <c r="AJ28">
-        <v>0.2102646186969697</v>
+        <v>0.2253923547714286</v>
       </c>
       <c r="AK28">
-        <v>0.2241980598181818</v>
+        <v>0.2385295992571428</v>
       </c>
       <c r="AL28">
-        <v>0.2381315009393939</v>
+        <v>0.2516668437428571</v>
       </c>
       <c r="AM28">
-        <v>0.252064942060606</v>
+        <v>0.2648040882285714</v>
       </c>
       <c r="AN28">
-        <v>0.2659983831818181</v>
+        <v>0.2779413327142857</v>
       </c>
       <c r="AO28">
-        <v>0.2799318243030303</v>
+        <v>0.2910785772</v>
       </c>
       <c r="AP28">
-        <v>0.2938652654242425</v>
+        <v>0.3042158216857143</v>
       </c>
       <c r="AQ28">
-        <v>0.3077987065454545</v>
+        <v>0.3173530661714286</v>
       </c>
       <c r="AR28">
-        <v>0.3217321476666666</v>
+        <v>0.3304903106571428</v>
       </c>
       <c r="AS28">
-        <v>0.3356655887878788</v>
+        <v>0.3436275551428571</v>
       </c>
       <c r="AT28">
-        <v>0.3495990299090909</v>
+        <v>0.3567647996285714</v>
       </c>
       <c r="AU28">
-        <v>0.363532471030303</v>
+        <v>0.3699020441142857</v>
       </c>
       <c r="AV28">
-        <v>0.3774659121515151</v>
+        <v>0.3830392886</v>
       </c>
       <c r="AW28">
-        <v>0.3913993532727273</v>
+        <v>0.3961765330857143</v>
       </c>
       <c r="AX28">
-        <v>0.4053327943939394</v>
+        <v>0.4093137775714285</v>
       </c>
       <c r="AY28">
-        <v>0.4192662355151515</v>
+        <v>0.4224510220571428</v>
       </c>
       <c r="AZ28">
-        <v>0.4331996766363636</v>
+        <v>0.4355882665428571</v>
       </c>
       <c r="BA28">
-        <v>0.4471331177575757</v>
+        <v>0.4487255110285714</v>
       </c>
       <c r="BB28">
-        <v>0.4610665588787878</v>
+        <v>0.4618627555142857</v>
       </c>
       <c r="BC28">
         <v>0.475</v>
